--- a/outputs/Block5B_Senate_Competitive_Races.xlsx
+++ b/outputs/Block5B_Senate_Competitive_Races.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="91">
   <si>
     <t>STATE</t>
   </si>
@@ -190,34 +190,40 @@
     <t>Mean Comparability Weight</t>
   </si>
   <si>
+    <t>Ohio</t>
+  </si>
+  <si>
     <t>Michigan</t>
   </si>
   <si>
-    <t>Ohio</t>
+    <t>Alaska</t>
+  </si>
+  <si>
+    <t>Texas</t>
   </si>
   <si>
     <t>Maine</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Texas</t>
-  </si>
-  <si>
     <t>Iowa</t>
   </si>
   <si>
+    <t>Nebraska</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
     <t>D</t>
   </si>
   <si>
-    <t>R</t>
+    <t>RSenLeanPollLD (&gt;1&lt;=5%)</t>
   </si>
   <si>
     <t>DSenLeanPollH (&gt;1&lt;=5%)</t>
   </si>
   <si>
-    <t>RSenLeanPollLD (&gt;1&lt;=5%)</t>
+    <t>RSenTosPoll (&lt;=1%)</t>
   </si>
   <si>
     <t>RSenLeanPollH (&gt;1&lt;=5%)</t>
@@ -226,55 +232,61 @@
     <t>D Lean</t>
   </si>
   <si>
+    <t>Toss-Up</t>
+  </si>
+  <si>
     <t>R Lean</t>
   </si>
   <si>
     <t>Lean</t>
   </si>
   <si>
-    <t>Toss-Up</t>
+    <t>Democratic Flip</t>
   </si>
   <si>
     <t>Democratic Hold</t>
   </si>
   <si>
-    <t>Democratic Flip</t>
-  </si>
-  <si>
     <t>Republican Hold</t>
   </si>
   <si>
     <t>Polling-error correction retained — inner LOEO improved MAE</t>
   </si>
   <si>
+    <t>R+5</t>
+  </si>
+  <si>
     <t>EVEN</t>
   </si>
   <si>
-    <t>R+5</t>
+    <t>R+6</t>
   </si>
   <si>
     <t>D+4</t>
   </si>
   <si>
-    <t>R+6</t>
+    <t>R+10</t>
+  </si>
+  <si>
+    <t>Appointed (2025)[p]</t>
   </si>
   <si>
     <t>49.90% D</t>
   </si>
   <si>
-    <t>Appointed (2025)[p]</t>
+    <t>53.90% R</t>
+  </si>
+  <si>
+    <t>53.51% R</t>
   </si>
   <si>
     <t>50.98% R</t>
   </si>
   <si>
-    <t>53.90% R</t>
-  </si>
-  <si>
-    <t>53.51% R</t>
-  </si>
-  <si>
     <t>51.74% R</t>
+  </si>
+  <si>
+    <t>62.58% R (2024 sp.)[o]</t>
   </si>
 </sst>
 </file>
@@ -632,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BF7"/>
+  <dimension ref="A1:BF8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:58">
@@ -816,43 +828,43 @@
         <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2">
-        <v>47.92</v>
+        <v>48.4</v>
       </c>
       <c r="D2">
-        <v>44.95</v>
+        <v>44.82</v>
       </c>
       <c r="E2">
-        <v>2.97</v>
+        <v>3.58</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I2">
-        <v>51.6</v>
+        <v>51.92</v>
       </c>
       <c r="J2">
-        <v>48.4</v>
+        <v>48.08</v>
       </c>
       <c r="K2">
-        <v>3.2</v>
+        <v>3.83</v>
       </c>
       <c r="L2">
-        <v>0.12</v>
+        <v>-0.3</v>
       </c>
       <c r="M2">
-        <v>3.32</v>
+        <v>3.54</v>
       </c>
       <c r="N2">
-        <v>3.32</v>
+        <v>3.54</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -861,130 +873,118 @@
         <v>1</v>
       </c>
       <c r="Q2">
-        <v>51.66</v>
+        <v>51.77</v>
       </c>
       <c r="R2">
-        <v>48.34</v>
+        <v>48.23</v>
       </c>
       <c r="S2">
-        <v>0.12</v>
+        <v>-0.3</v>
       </c>
       <c r="T2">
-        <v>3.32</v>
+        <v>3.54</v>
       </c>
       <c r="U2">
-        <v>3.32</v>
+        <v>3.54</v>
       </c>
       <c r="V2">
-        <v>69.5</v>
+        <v>71.27</v>
       </c>
       <c r="W2">
-        <v>30.5</v>
+        <v>28.73</v>
       </c>
       <c r="X2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Y2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Z2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AA2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AB2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AC2">
-        <v>30.5</v>
+        <v>71.27</v>
       </c>
       <c r="AD2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AE2">
-        <v>7.27</v>
+        <v>7.86</v>
       </c>
       <c r="AF2">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AG2">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AH2">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AI2">
+        <v>3.51</v>
+      </c>
+      <c r="AJ2">
         <v>3.24</v>
       </c>
-      <c r="AJ2">
-        <v>-0.34</v>
-      </c>
       <c r="AK2">
         <v>0</v>
       </c>
       <c r="AL2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AN2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AP2">
-        <v>0.499</v>
-      </c>
-      <c r="AQ2">
-        <v>-0.2000000000000028</v>
+        <v>84</v>
       </c>
       <c r="AR2">
-        <v>3.322364192499973</v>
-      </c>
-      <c r="AS2">
-        <v>3.522364192499976</v>
+        <v>8.536611196062932</v>
       </c>
       <c r="AT2">
-        <v>3.422364192499974</v>
+        <v>8.536611196062932</v>
       </c>
       <c r="AU2">
-        <v>0.8555910481249935</v>
+        <v>2.134152799015733</v>
       </c>
       <c r="AV2">
-        <v>4.72</v>
+        <v>4.15</v>
       </c>
       <c r="AW2">
-        <v>5.73</v>
+        <v>5.49</v>
       </c>
       <c r="AX2">
-        <v>6.51</v>
+        <v>6.3</v>
       </c>
       <c r="AY2">
         <v>1.11</v>
       </c>
       <c r="AZ2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA2">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="BB2">
-        <v>-0.6899999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="BC2">
-        <v>1.19</v>
+        <v>2.96</v>
       </c>
       <c r="BD2">
-        <v>0</v>
+        <v>17.49</v>
       </c>
       <c r="BE2">
         <v>0</v>
       </c>
       <c r="BF2">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="3" spans="1:58">
@@ -992,43 +992,43 @@
         <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3">
-        <v>49.92</v>
+        <v>47.98</v>
       </c>
       <c r="D3">
-        <v>46.55</v>
+        <v>45.52</v>
       </c>
       <c r="E3">
-        <v>3.38</v>
+        <v>2.45</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I3">
-        <v>51.75</v>
+        <v>51.31</v>
       </c>
       <c r="J3">
-        <v>48.25</v>
+        <v>48.69</v>
       </c>
       <c r="K3">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="L3">
-        <v>-0.47</v>
+        <v>2.32</v>
       </c>
       <c r="M3">
-        <v>3.03</v>
+        <v>4.94</v>
       </c>
       <c r="N3">
-        <v>3.03</v>
+        <v>4.94</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1037,118 +1037,130 @@
         <v>1</v>
       </c>
       <c r="Q3">
-        <v>51.51</v>
+        <v>51.31</v>
       </c>
       <c r="R3">
-        <v>48.49</v>
+        <v>48.69</v>
       </c>
       <c r="S3">
-        <v>-0.47</v>
+        <v>2.32</v>
       </c>
       <c r="T3">
-        <v>3.03</v>
+        <v>4.94</v>
       </c>
       <c r="U3">
-        <v>3.03</v>
+        <v>2.62</v>
       </c>
       <c r="V3">
-        <v>68.7</v>
+        <v>65.48</v>
       </c>
       <c r="W3">
-        <v>31.3</v>
+        <v>34.52</v>
       </c>
       <c r="X3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Y3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Z3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AA3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AB3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AC3">
-        <v>68.7</v>
+        <v>34.52</v>
       </c>
       <c r="AD3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AE3">
-        <v>7.27</v>
+        <v>7.86</v>
       </c>
       <c r="AF3">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AG3">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AH3">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AI3">
-        <v>3.24</v>
+        <v>3.51</v>
       </c>
       <c r="AJ3">
-        <v>2.9</v>
+        <v>-0.28</v>
       </c>
       <c r="AK3">
         <v>0</v>
       </c>
       <c r="AL3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AM3">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="s">
-        <v>82</v>
+        <v>85</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP3">
+        <v>0.499</v>
+      </c>
+      <c r="AQ3">
+        <v>-0.2000000000000028</v>
       </c>
       <c r="AR3">
-        <v>8.027335204854857</v>
+        <v>4.943406372496832</v>
+      </c>
+      <c r="AS3">
+        <v>5.143406372496835</v>
       </c>
       <c r="AT3">
-        <v>8.027335204854857</v>
+        <v>5.043406372496833</v>
       </c>
       <c r="AU3">
-        <v>2.006833801213714</v>
+        <v>1.260851593124208</v>
       </c>
       <c r="AV3">
-        <v>4.15</v>
+        <v>4.72</v>
       </c>
       <c r="AW3">
-        <v>5.39</v>
+        <v>5.81</v>
       </c>
       <c r="AX3">
-        <v>6.21</v>
+        <v>6.58</v>
       </c>
       <c r="AY3">
         <v>1.11</v>
       </c>
       <c r="AZ3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA3">
-        <v>2.8</v>
+        <v>1.93</v>
       </c>
       <c r="BB3">
-        <v>0.17</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="BC3">
-        <v>2.96</v>
+        <v>1.19</v>
       </c>
       <c r="BD3">
-        <v>17.49</v>
+        <v>0</v>
       </c>
       <c r="BE3">
         <v>0</v>
       </c>
       <c r="BF3">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:58">
@@ -1159,40 +1171,40 @@
         <v>65</v>
       </c>
       <c r="C4">
-        <v>49.4</v>
+        <v>50.15</v>
       </c>
       <c r="D4">
-        <v>47.7</v>
+        <v>48.38</v>
       </c>
       <c r="E4">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="F4" t="s">
         <v>67</v>
       </c>
       <c r="G4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I4">
-        <v>50.88</v>
+        <v>50.9</v>
       </c>
       <c r="J4">
-        <v>49.12</v>
+        <v>49.1</v>
       </c>
       <c r="K4">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="L4">
-        <v>-0.5</v>
+        <v>2.04</v>
       </c>
       <c r="M4">
-        <v>1.25</v>
+        <v>3.84</v>
       </c>
       <c r="N4">
-        <v>1.25</v>
+        <v>3.84</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -1201,106 +1213,106 @@
         <v>1</v>
       </c>
       <c r="Q4">
-        <v>50.63</v>
+        <v>50.58</v>
       </c>
       <c r="R4">
-        <v>49.37</v>
+        <v>49.42</v>
       </c>
       <c r="S4">
-        <v>-0.5</v>
+        <v>2.04</v>
       </c>
       <c r="T4">
-        <v>1.25</v>
+        <v>3.84</v>
       </c>
       <c r="U4">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="V4">
-        <v>56.37</v>
+        <v>56.21</v>
       </c>
       <c r="W4">
-        <v>43.63</v>
+        <v>43.79</v>
       </c>
       <c r="X4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Y4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Z4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AB4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC4">
-        <v>56.37</v>
+        <v>56.21</v>
       </c>
       <c r="AD4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AE4">
-        <v>7.27</v>
+        <v>7.86</v>
       </c>
       <c r="AF4">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AG4">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AH4">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AI4">
+        <v>3.51</v>
+      </c>
+      <c r="AJ4">
         <v>3.24</v>
       </c>
-      <c r="AJ4">
-        <v>2.9</v>
-      </c>
       <c r="AK4">
         <v>0</v>
       </c>
       <c r="AL4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AM4">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="AN4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AO4" t="s">
         <v>65</v>
       </c>
       <c r="AP4">
-        <v>0.5097999999999999</v>
+        <v>0.539</v>
       </c>
       <c r="AQ4">
-        <v>-1.95999999999998</v>
+        <v>-7.800000000000011</v>
       </c>
       <c r="AR4">
-        <v>2.74770982501213</v>
+        <v>9.840986553974432</v>
       </c>
       <c r="AS4">
-        <v>3.212290174987849</v>
+        <v>11.64098655397444</v>
       </c>
       <c r="AT4">
-        <v>2.97999999999999</v>
+        <v>10.74098655397444</v>
       </c>
       <c r="AU4">
-        <v>0.7449999999999974</v>
+        <v>2.685246638493609</v>
       </c>
       <c r="AV4">
-        <v>6.17</v>
+        <v>5.31</v>
       </c>
       <c r="AW4">
-        <v>7.17</v>
+        <v>6.76</v>
       </c>
       <c r="AX4">
-        <v>7.8</v>
+        <v>7.43</v>
       </c>
       <c r="AY4">
         <v>1.11</v>
@@ -1309,22 +1321,22 @@
         <v>3</v>
       </c>
       <c r="BA4">
-        <v>1.88</v>
+        <v>1.54</v>
       </c>
       <c r="BB4">
-        <v>1.02</v>
+        <v>-4.01</v>
       </c>
       <c r="BC4">
-        <v>7.45</v>
+        <v>11.42</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>42.06</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>23.64</v>
       </c>
       <c r="BF4">
-        <v>0.92</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:58">
@@ -1335,40 +1347,40 @@
         <v>65</v>
       </c>
       <c r="C5">
-        <v>50</v>
+        <v>48.42</v>
       </c>
       <c r="D5">
-        <v>48.52</v>
+        <v>45.85</v>
       </c>
       <c r="E5">
-        <v>1.48</v>
+        <v>2.58</v>
       </c>
       <c r="F5" t="s">
         <v>67</v>
       </c>
       <c r="G5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I5">
-        <v>50.75</v>
+        <v>51.37</v>
       </c>
       <c r="J5">
-        <v>49.25</v>
+        <v>48.63</v>
       </c>
       <c r="K5">
-        <v>1.5</v>
+        <v>2.73</v>
       </c>
       <c r="L5">
-        <v>0.19</v>
+        <v>0.02</v>
       </c>
       <c r="M5">
-        <v>1.69</v>
+        <v>2.76</v>
       </c>
       <c r="N5">
-        <v>1.69</v>
+        <v>2.76</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1377,106 +1389,106 @@
         <v>1</v>
       </c>
       <c r="Q5">
-        <v>50.32</v>
+        <v>50.19</v>
       </c>
       <c r="R5">
-        <v>49.68</v>
+        <v>49.81</v>
       </c>
       <c r="S5">
-        <v>0.19</v>
+        <v>0.02</v>
       </c>
       <c r="T5">
-        <v>1.69</v>
+        <v>2.76</v>
       </c>
       <c r="U5">
-        <v>0.64</v>
+        <v>0.37</v>
       </c>
       <c r="V5">
-        <v>53.53</v>
+        <v>52.35</v>
       </c>
       <c r="W5">
-        <v>46.47</v>
+        <v>47.65</v>
       </c>
       <c r="X5" t="s">
         <v>72</v>
       </c>
       <c r="Y5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Z5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AB5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC5">
-        <v>53.53</v>
+        <v>52.35</v>
       </c>
       <c r="AD5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AE5">
-        <v>7.27</v>
+        <v>7.86</v>
       </c>
       <c r="AF5">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AG5">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AH5">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AI5">
+        <v>3.51</v>
+      </c>
+      <c r="AJ5">
         <v>3.24</v>
       </c>
-      <c r="AJ5">
-        <v>2.9</v>
-      </c>
       <c r="AK5">
         <v>0</v>
       </c>
       <c r="AL5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AM5">
         <v>-6</v>
       </c>
       <c r="AN5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AO5" t="s">
         <v>65</v>
       </c>
       <c r="AP5">
-        <v>0.539</v>
+        <v>0.5351</v>
       </c>
       <c r="AQ5">
-        <v>-7.800000000000011</v>
+        <v>-7.02000000000001</v>
       </c>
       <c r="AR5">
-        <v>7.686016982113116</v>
+        <v>8.755412717885292</v>
       </c>
       <c r="AS5">
-        <v>9.486016982113126</v>
+        <v>9.775412717885303</v>
       </c>
       <c r="AT5">
-        <v>8.58601698211312</v>
+        <v>9.265412717885297</v>
       </c>
       <c r="AU5">
-        <v>2.14650424552828</v>
+        <v>2.316353179471324</v>
       </c>
       <c r="AV5">
-        <v>5.31</v>
+        <v>4.14</v>
       </c>
       <c r="AW5">
-        <v>6.57</v>
+        <v>5.55</v>
       </c>
       <c r="AX5">
-        <v>7.26</v>
+        <v>6.35</v>
       </c>
       <c r="AY5">
         <v>1.11</v>
@@ -1485,22 +1497,22 @@
         <v>3</v>
       </c>
       <c r="BA5">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="BB5">
-        <v>-4.01</v>
+        <v>1.35</v>
       </c>
       <c r="BC5">
-        <v>11.42</v>
+        <v>5.75</v>
       </c>
       <c r="BD5">
-        <v>42.06</v>
+        <v>0</v>
       </c>
       <c r="BE5">
-        <v>23.64</v>
+        <v>0</v>
       </c>
       <c r="BF5">
-        <v>0.6899999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:58">
@@ -1511,40 +1523,40 @@
         <v>65</v>
       </c>
       <c r="C6">
-        <v>47.32</v>
+        <v>48.32</v>
       </c>
       <c r="D6">
-        <v>45.6</v>
+        <v>46.18</v>
       </c>
       <c r="E6">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="F6" t="s">
         <v>67</v>
       </c>
       <c r="G6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I6">
-        <v>50.93</v>
+        <v>51.14</v>
       </c>
       <c r="J6">
-        <v>49.07</v>
+        <v>48.86</v>
       </c>
       <c r="K6">
-        <v>1.86</v>
+        <v>2.28</v>
       </c>
       <c r="L6">
-        <v>-2.64</v>
+        <v>0.05</v>
       </c>
       <c r="M6">
-        <v>-0.78</v>
+        <v>2.32</v>
       </c>
       <c r="N6">
-        <v>-0.78</v>
+        <v>2.32</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1553,25 +1565,25 @@
         <v>1</v>
       </c>
       <c r="Q6">
-        <v>49.61</v>
+        <v>49.98</v>
       </c>
       <c r="R6">
-        <v>50.39</v>
+        <v>50.02</v>
       </c>
       <c r="S6">
-        <v>-2.64</v>
+        <v>0.05</v>
       </c>
       <c r="T6">
-        <v>-0.78</v>
+        <v>2.32</v>
       </c>
       <c r="U6">
-        <v>-0.78</v>
+        <v>-0.05</v>
       </c>
       <c r="V6">
-        <v>44.91</v>
+        <v>49.76</v>
       </c>
       <c r="W6">
-        <v>55.09</v>
+        <v>50.24</v>
       </c>
       <c r="X6" t="s">
         <v>72</v>
@@ -1580,79 +1592,79 @@
         <v>65</v>
       </c>
       <c r="Z6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB6" t="s">
         <v>75</v>
       </c>
-      <c r="AA6" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>74</v>
-      </c>
       <c r="AC6">
-        <v>44.91</v>
+        <v>49.76</v>
       </c>
       <c r="AD6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AE6">
-        <v>7.27</v>
+        <v>7.86</v>
       </c>
       <c r="AF6">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AG6">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AH6">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AI6">
+        <v>3.51</v>
+      </c>
+      <c r="AJ6">
         <v>3.24</v>
       </c>
-      <c r="AJ6">
-        <v>2.9</v>
-      </c>
       <c r="AK6">
         <v>0</v>
       </c>
       <c r="AL6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AM6">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="AN6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AO6" t="s">
         <v>65</v>
       </c>
       <c r="AP6">
-        <v>0.5351</v>
+        <v>0.5097999999999999</v>
       </c>
       <c r="AQ6">
-        <v>-7.02000000000001</v>
+        <v>-1.95999999999998</v>
       </c>
       <c r="AR6">
-        <v>5.215620294959367</v>
+        <v>1.675966859360293</v>
       </c>
       <c r="AS6">
-        <v>6.235620294959377</v>
+        <v>4.284033140639687</v>
       </c>
       <c r="AT6">
-        <v>5.725620294959372</v>
+        <v>2.97999999999999</v>
       </c>
       <c r="AU6">
-        <v>1.431405073739843</v>
+        <v>0.7449999999999974</v>
       </c>
       <c r="AV6">
-        <v>4.14</v>
+        <v>6.17</v>
       </c>
       <c r="AW6">
-        <v>5.29</v>
+        <v>7.2</v>
       </c>
       <c r="AX6">
-        <v>6.13</v>
+        <v>7.83</v>
       </c>
       <c r="AY6">
         <v>1.11</v>
@@ -1661,13 +1673,13 @@
         <v>3</v>
       </c>
       <c r="BA6">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="BB6">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="BC6">
-        <v>5.75</v>
+        <v>7.45</v>
       </c>
       <c r="BD6">
         <v>0</v>
@@ -1676,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="BF6">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="7" spans="1:58">
@@ -1687,40 +1699,40 @@
         <v>65</v>
       </c>
       <c r="C7">
-        <v>46.05</v>
+        <v>45.4</v>
       </c>
       <c r="D7">
-        <v>48.32</v>
+        <v>46.12</v>
       </c>
       <c r="E7">
-        <v>-2.28</v>
+        <v>-0.73</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I7">
-        <v>48.79</v>
+        <v>49.6</v>
       </c>
       <c r="J7">
-        <v>51.21</v>
+        <v>50.4</v>
       </c>
       <c r="K7">
-        <v>-2.41</v>
+        <v>-0.79</v>
       </c>
       <c r="L7">
-        <v>-1.72</v>
+        <v>-1.77</v>
       </c>
       <c r="M7">
-        <v>-4.13</v>
+        <v>-2.56</v>
       </c>
       <c r="N7">
-        <v>-4.13</v>
+        <v>-2.56</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1729,76 +1741,76 @@
         <v>1</v>
       </c>
       <c r="Q7">
-        <v>47.93</v>
+        <v>48.72</v>
       </c>
       <c r="R7">
-        <v>52.07</v>
+        <v>51.28</v>
       </c>
       <c r="S7">
-        <v>-1.72</v>
+        <v>-1.77</v>
       </c>
       <c r="T7">
-        <v>-4.13</v>
+        <v>-2.56</v>
       </c>
       <c r="U7">
-        <v>-4.13</v>
+        <v>-2.56</v>
       </c>
       <c r="V7">
-        <v>28.76</v>
+        <v>36.52</v>
       </c>
       <c r="W7">
-        <v>71.23999999999999</v>
+        <v>63.48</v>
       </c>
       <c r="X7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Y7" t="s">
         <v>65</v>
       </c>
       <c r="Z7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AA7" t="s">
         <v>65</v>
       </c>
       <c r="AB7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AC7">
-        <v>28.76</v>
+        <v>36.52</v>
       </c>
       <c r="AD7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AE7">
-        <v>7.27</v>
+        <v>7.86</v>
       </c>
       <c r="AF7">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AG7">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AH7">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AI7">
+        <v>3.51</v>
+      </c>
+      <c r="AJ7">
         <v>3.24</v>
       </c>
-      <c r="AJ7">
-        <v>2.9</v>
-      </c>
       <c r="AK7">
         <v>0</v>
       </c>
       <c r="AL7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AM7">
         <v>-6</v>
       </c>
       <c r="AN7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AO7" t="s">
         <v>65</v>
@@ -1810,25 +1822,25 @@
         <v>-3.47999999999999</v>
       </c>
       <c r="AR7">
-        <v>1.86896365369746</v>
+        <v>3.435838333780036</v>
       </c>
       <c r="AS7">
-        <v>0.6510363463025506</v>
+        <v>0.9158383337800258</v>
       </c>
       <c r="AT7">
-        <v>1.260000000000005</v>
+        <v>2.175838333780031</v>
       </c>
       <c r="AU7">
-        <v>0.3150000000000013</v>
+        <v>0.5439595834450077</v>
       </c>
       <c r="AV7">
         <v>5.7</v>
       </c>
       <c r="AW7">
-        <v>6.69</v>
+        <v>6.77</v>
       </c>
       <c r="AX7">
-        <v>7.37</v>
+        <v>7.44</v>
       </c>
       <c r="AY7">
         <v>1.11</v>
@@ -1853,6 +1865,182 @@
       </c>
       <c r="BF7">
         <v>0.95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:58">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8">
+        <v>47.27</v>
+      </c>
+      <c r="D8">
+        <v>50.17</v>
+      </c>
+      <c r="E8">
+        <v>-2.9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8">
+        <v>48.51</v>
+      </c>
+      <c r="J8">
+        <v>51.49</v>
+      </c>
+      <c r="K8">
+        <v>-2.98</v>
+      </c>
+      <c r="L8">
+        <v>1.78</v>
+      </c>
+      <c r="M8">
+        <v>-1.2</v>
+      </c>
+      <c r="N8">
+        <v>-1.2</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>48.13</v>
+      </c>
+      <c r="R8">
+        <v>51.87</v>
+      </c>
+      <c r="S8">
+        <v>1.78</v>
+      </c>
+      <c r="T8">
+        <v>-1.2</v>
+      </c>
+      <c r="U8">
+        <v>-3.74</v>
+      </c>
+      <c r="V8">
+        <v>30.07</v>
+      </c>
+      <c r="W8">
+        <v>69.93000000000001</v>
+      </c>
+      <c r="X8" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC8">
+        <v>30.07</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE8">
+        <v>7.86</v>
+      </c>
+      <c r="AF8">
+        <v>0.28</v>
+      </c>
+      <c r="AG8">
+        <v>3.24</v>
+      </c>
+      <c r="AH8">
+        <v>2.96</v>
+      </c>
+      <c r="AI8">
+        <v>3.51</v>
+      </c>
+      <c r="AJ8">
+        <v>3.24</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AM8">
+        <v>-10</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP8">
+        <v>0.6258</v>
+      </c>
+      <c r="AQ8">
+        <v>-25.16000000000001</v>
+      </c>
+      <c r="AR8">
+        <v>8.804477444369347</v>
+      </c>
+      <c r="AS8">
+        <v>23.96447744436936</v>
+      </c>
+      <c r="AT8">
+        <v>16.38447744436935</v>
+      </c>
+      <c r="AU8">
+        <v>4.096119361092338</v>
+      </c>
+      <c r="AV8">
+        <v>4.13</v>
+      </c>
+      <c r="AW8">
+        <v>6.47</v>
+      </c>
+      <c r="AX8">
+        <v>7.17</v>
+      </c>
+      <c r="AY8">
+        <v>1.11</v>
+      </c>
+      <c r="AZ8">
+        <v>3</v>
+      </c>
+      <c r="BA8">
+        <v>1.91</v>
+      </c>
+      <c r="BB8">
+        <v>-1.37</v>
+      </c>
+      <c r="BC8">
+        <v>5.41</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0.93</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block5B_Senate_Competitive_Races.xlsx
+++ b/outputs/Block5B_Senate_Competitive_Races.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="89">
   <si>
     <t>STATE</t>
   </si>
@@ -190,18 +190,15 @@
     <t>Mean Comparability Weight</t>
   </si>
   <si>
+    <t>Texas</t>
+  </si>
+  <si>
     <t>Ohio</t>
   </si>
   <si>
-    <t>Michigan</t>
-  </si>
-  <si>
     <t>Alaska</t>
   </si>
   <si>
-    <t>Texas</t>
-  </si>
-  <si>
     <t>Maine</t>
   </si>
   <si>
@@ -211,75 +208,69 @@
     <t>Nebraska</t>
   </si>
   <si>
+    <t>Kansas</t>
+  </si>
+  <si>
     <t>R</t>
   </si>
   <si>
+    <t>RSenLeanPollLD (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>RSenTosPoll (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>RSenLeanPollH (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>D Lean</t>
+  </si>
+  <si>
+    <t>Toss-Up</t>
+  </si>
+  <si>
+    <t>R Lean</t>
+  </si>
+  <si>
+    <t>Lean</t>
+  </si>
+  <si>
     <t>D</t>
   </si>
   <si>
-    <t>RSenLeanPollLD (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>DSenLeanPollH (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>RSenTosPoll (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>RSenLeanPollH (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>D Lean</t>
-  </si>
-  <si>
-    <t>Toss-Up</t>
-  </si>
-  <si>
-    <t>R Lean</t>
-  </si>
-  <si>
-    <t>Lean</t>
-  </si>
-  <si>
     <t>Democratic Flip</t>
   </si>
   <si>
-    <t>Democratic Hold</t>
-  </si>
-  <si>
     <t>Republican Hold</t>
   </si>
   <si>
     <t>Polling-error correction retained — inner LOEO improved MAE</t>
   </si>
   <si>
+    <t>R+6</t>
+  </si>
+  <si>
     <t>R+5</t>
   </si>
   <si>
-    <t>EVEN</t>
-  </si>
-  <si>
-    <t>R+6</t>
-  </si>
-  <si>
     <t>D+4</t>
   </si>
   <si>
     <t>R+10</t>
   </si>
   <si>
+    <t>R+8</t>
+  </si>
+  <si>
+    <t>53.51% R</t>
+  </si>
+  <si>
     <t>Appointed (2025)[p]</t>
   </si>
   <si>
-    <t>49.90% D</t>
-  </si>
-  <si>
     <t>53.90% R</t>
   </si>
   <si>
-    <t>53.51% R</t>
-  </si>
-  <si>
     <t>50.98% R</t>
   </si>
   <si>
@@ -287,6 +278,9 @@
   </si>
   <si>
     <t>62.58% R (2024 sp.)[o]</t>
+  </si>
+  <si>
+    <t>53.22% R</t>
   </si>
 </sst>
 </file>
@@ -831,160 +825,172 @@
         <v>65</v>
       </c>
       <c r="C2">
-        <v>48.4</v>
+        <v>48.675</v>
       </c>
       <c r="D2">
-        <v>44.82</v>
+        <v>45.65</v>
       </c>
       <c r="E2">
-        <v>3.58</v>
+        <v>3.025</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2">
+        <v>51.60349854227405</v>
+      </c>
+      <c r="J2">
+        <v>48.39650145772595</v>
+      </c>
+      <c r="K2">
+        <v>3.206997084548107</v>
+      </c>
+      <c r="L2">
+        <v>-1.2681457739171</v>
+      </c>
+      <c r="M2">
+        <v>1.938851310631006</v>
+      </c>
+      <c r="N2">
+        <v>1.938851310631006</v>
+      </c>
+      <c r="O2">
+        <v>0.25</v>
+      </c>
+      <c r="P2">
+        <v>0.75</v>
+      </c>
+      <c r="Q2">
+        <v>51.12794387705514</v>
+      </c>
+      <c r="R2">
+        <v>48.87205612294486</v>
+      </c>
+      <c r="S2">
+        <v>-0.9511093304378253</v>
+      </c>
+      <c r="T2">
+        <v>2.255887754110281</v>
+      </c>
+      <c r="U2">
+        <v>2.255887754110281</v>
+      </c>
+      <c r="V2">
+        <v>67.08308487070286</v>
+      </c>
+      <c r="W2">
+        <v>32.91691512929713</v>
+      </c>
+      <c r="X2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z2" t="s">
         <v>74</v>
       </c>
-      <c r="I2">
-        <v>51.92</v>
-      </c>
-      <c r="J2">
-        <v>48.08</v>
-      </c>
-      <c r="K2">
-        <v>3.83</v>
-      </c>
-      <c r="L2">
-        <v>-0.3</v>
-      </c>
-      <c r="M2">
-        <v>3.54</v>
-      </c>
-      <c r="N2">
-        <v>3.54</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
-      <c r="Q2">
-        <v>51.77</v>
-      </c>
-      <c r="R2">
-        <v>48.23</v>
-      </c>
-      <c r="S2">
-        <v>-0.3</v>
-      </c>
-      <c r="T2">
-        <v>3.54</v>
-      </c>
-      <c r="U2">
-        <v>3.54</v>
-      </c>
-      <c r="V2">
-        <v>71.27</v>
-      </c>
-      <c r="W2">
-        <v>28.73</v>
-      </c>
-      <c r="X2" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>75</v>
-      </c>
       <c r="AA2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="AB2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AC2">
-        <v>71.27</v>
+        <v>67.08308487070286</v>
       </c>
       <c r="AD2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AE2">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF2">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>0.549123227957043</v>
       </c>
       <c r="AL2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AM2">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="AN2" t="s">
-        <v>84</v>
+        <v>82</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP2">
+        <v>0.5351</v>
+      </c>
+      <c r="AQ2">
+        <v>-7.02000000000001</v>
       </c>
       <c r="AR2">
-        <v>8.536611196062932</v>
+        <v>8.255887754110281</v>
+      </c>
+      <c r="AS2">
+        <v>9.275887754110292</v>
       </c>
       <c r="AT2">
-        <v>8.536611196062932</v>
+        <v>8.765887754110286</v>
       </c>
       <c r="AU2">
-        <v>2.134152799015733</v>
+        <v>2.191471938527572</v>
       </c>
       <c r="AV2">
-        <v>4.15</v>
+        <v>4.345503062353619</v>
       </c>
       <c r="AW2">
-        <v>5.49</v>
+        <v>4.362627316035638</v>
       </c>
       <c r="AX2">
-        <v>6.3</v>
+        <v>5.101411483891715</v>
       </c>
       <c r="AY2">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA2">
-        <v>2.8</v>
+        <v>1.930645252303767</v>
       </c>
       <c r="BB2">
-        <v>0.17</v>
+        <v>1.354753062157686</v>
       </c>
       <c r="BC2">
-        <v>2.96</v>
+        <v>5.754964092348529</v>
       </c>
       <c r="BD2">
-        <v>17.49</v>
+        <v>0</v>
       </c>
       <c r="BE2">
         <v>0</v>
       </c>
       <c r="BF2">
-        <v>0.96</v>
+        <v>0.9442145399410329</v>
       </c>
     </row>
     <row r="3" spans="1:58">
@@ -992,175 +998,163 @@
         <v>59</v>
       </c>
       <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3">
+        <v>48.225</v>
+      </c>
+      <c r="D3">
+        <v>45.1</v>
+      </c>
+      <c r="E3">
+        <v>3.125</v>
+      </c>
+      <c r="F3" t="s">
         <v>66</v>
       </c>
-      <c r="C3">
-        <v>47.98</v>
-      </c>
-      <c r="D3">
-        <v>45.52</v>
-      </c>
-      <c r="E3">
-        <v>2.45</v>
-      </c>
-      <c r="F3" t="s">
-        <v>68</v>
-      </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3">
+        <v>51.67425663005626</v>
+      </c>
+      <c r="J3">
+        <v>48.32574336994374</v>
+      </c>
+      <c r="K3">
+        <v>3.348513260112512</v>
+      </c>
+      <c r="L3">
+        <v>-1.794861267366732</v>
+      </c>
+      <c r="M3">
+        <v>1.553651992745779</v>
+      </c>
+      <c r="N3">
+        <v>1.553651992745779</v>
+      </c>
+      <c r="O3">
+        <v>0.25</v>
+      </c>
+      <c r="P3">
+        <v>0.75</v>
+      </c>
+      <c r="Q3">
+        <v>51.00118365479373</v>
+      </c>
+      <c r="R3">
+        <v>48.99881634520627</v>
+      </c>
+      <c r="S3">
+        <v>-1.346145950525049</v>
+      </c>
+      <c r="T3">
+        <v>2.002367309587462</v>
+      </c>
+      <c r="U3">
+        <v>2.002367309587462</v>
+      </c>
+      <c r="V3">
+        <v>65.26388699510164</v>
+      </c>
+      <c r="W3">
+        <v>34.73611300489836</v>
+      </c>
+      <c r="X3" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z3" t="s">
         <v>74</v>
       </c>
-      <c r="I3">
-        <v>51.31</v>
-      </c>
-      <c r="J3">
-        <v>48.69</v>
-      </c>
-      <c r="K3">
-        <v>2.62</v>
-      </c>
-      <c r="L3">
-        <v>2.32</v>
-      </c>
-      <c r="M3">
-        <v>4.94</v>
-      </c>
-      <c r="N3">
-        <v>4.94</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
-      <c r="Q3">
-        <v>51.31</v>
-      </c>
-      <c r="R3">
-        <v>48.69</v>
-      </c>
-      <c r="S3">
-        <v>2.32</v>
-      </c>
-      <c r="T3">
-        <v>4.94</v>
-      </c>
-      <c r="U3">
-        <v>2.62</v>
-      </c>
-      <c r="V3">
-        <v>65.48</v>
-      </c>
-      <c r="W3">
-        <v>34.52</v>
-      </c>
-      <c r="X3" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z3" t="s">
+      <c r="AA3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC3">
+        <v>65.26388699510164</v>
+      </c>
+      <c r="AD3" t="s">
         <v>76</v>
       </c>
-      <c r="AA3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AC3">
-        <v>34.52</v>
-      </c>
-      <c r="AD3" t="s">
+      <c r="AE3">
+        <v>8.73527450544567</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0.7771977269041618</v>
+      </c>
+      <c r="AL3" t="s">
         <v>78</v>
       </c>
-      <c r="AE3">
-        <v>7.86</v>
-      </c>
-      <c r="AF3">
-        <v>0.28</v>
-      </c>
-      <c r="AG3">
-        <v>3.24</v>
-      </c>
-      <c r="AH3">
-        <v>2.96</v>
-      </c>
-      <c r="AI3">
-        <v>3.51</v>
-      </c>
-      <c r="AJ3">
-        <v>-0.28</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>80</v>
-      </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AN3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP3">
-        <v>0.499</v>
-      </c>
-      <c r="AQ3">
-        <v>-0.2000000000000028</v>
+        <v>83</v>
       </c>
       <c r="AR3">
-        <v>4.943406372496832</v>
-      </c>
-      <c r="AS3">
-        <v>5.143406372496835</v>
+        <v>7.002367309587463</v>
       </c>
       <c r="AT3">
-        <v>5.043406372496833</v>
+        <v>7.002367309587463</v>
       </c>
       <c r="AU3">
-        <v>1.260851593124208</v>
+        <v>1.750591827396866</v>
       </c>
       <c r="AV3">
-        <v>4.72</v>
+        <v>4.567515257270437</v>
       </c>
       <c r="AW3">
-        <v>5.81</v>
+        <v>4.363504132448985</v>
       </c>
       <c r="AX3">
-        <v>6.58</v>
+        <v>5.102161340379323</v>
       </c>
       <c r="AY3">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA3">
-        <v>1.93</v>
+        <v>2.797261014127842</v>
       </c>
       <c r="BB3">
-        <v>-0.6899999999999999</v>
+        <v>0.1730167113317724</v>
       </c>
       <c r="BC3">
-        <v>1.19</v>
+        <v>2.956526743070407</v>
       </c>
       <c r="BD3">
-        <v>0</v>
+        <v>17.4915896825486</v>
       </c>
       <c r="BE3">
         <v>0</v>
       </c>
       <c r="BF3">
-        <v>0.9399999999999999</v>
+        <v>0.956231216651788</v>
       </c>
     </row>
     <row r="4" spans="1:58">
@@ -1171,118 +1165,118 @@
         <v>65</v>
       </c>
       <c r="C4">
-        <v>50.15</v>
+        <v>49.325</v>
       </c>
       <c r="D4">
-        <v>48.38</v>
+        <v>47.475</v>
       </c>
       <c r="E4">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I4">
+        <v>50.95557851239669</v>
+      </c>
+      <c r="J4">
+        <v>49.0444214876033</v>
+      </c>
+      <c r="K4">
+        <v>1.91115702479339</v>
+      </c>
+      <c r="L4">
+        <v>-0.1172224213495152</v>
+      </c>
+      <c r="M4">
+        <v>1.793934603443875</v>
+      </c>
+      <c r="N4">
+        <v>1.793934603443875</v>
+      </c>
+      <c r="O4">
+        <v>0.25</v>
+      </c>
+      <c r="P4">
+        <v>0.75</v>
+      </c>
+      <c r="Q4">
+        <v>50.91162010439063</v>
+      </c>
+      <c r="R4">
+        <v>49.08837989560937</v>
+      </c>
+      <c r="S4">
+        <v>-0.08791681601213641</v>
+      </c>
+      <c r="T4">
+        <v>1.823240208781253</v>
+      </c>
+      <c r="U4">
+        <v>1.823240208781253</v>
+      </c>
+      <c r="V4">
+        <v>61.79014903031504</v>
+      </c>
+      <c r="W4">
+        <v>38.20985096968496</v>
+      </c>
+      <c r="X4" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z4" t="s">
         <v>74</v>
       </c>
-      <c r="I4">
-        <v>50.9</v>
-      </c>
-      <c r="J4">
-        <v>49.1</v>
-      </c>
-      <c r="K4">
-        <v>1.8</v>
-      </c>
-      <c r="L4">
-        <v>2.04</v>
-      </c>
-      <c r="M4">
-        <v>3.84</v>
-      </c>
-      <c r="N4">
-        <v>3.84</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
-      <c r="Q4">
-        <v>50.58</v>
-      </c>
-      <c r="R4">
-        <v>49.42</v>
-      </c>
-      <c r="S4">
-        <v>2.04</v>
-      </c>
-      <c r="T4">
-        <v>3.84</v>
-      </c>
-      <c r="U4">
-        <v>1.16</v>
-      </c>
-      <c r="V4">
-        <v>56.21</v>
-      </c>
-      <c r="W4">
-        <v>43.79</v>
-      </c>
-      <c r="X4" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>75</v>
-      </c>
       <c r="AA4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="AB4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AC4">
-        <v>56.21</v>
+        <v>61.79014903031504</v>
       </c>
       <c r="AD4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AE4">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF4">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>0.05075879739090176</v>
       </c>
       <c r="AL4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AM4">
         <v>-6</v>
       </c>
       <c r="AN4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AO4" t="s">
         <v>65</v>
@@ -1294,49 +1288,49 @@
         <v>-7.800000000000011</v>
       </c>
       <c r="AR4">
-        <v>9.840986553974432</v>
+        <v>7.823240208781254</v>
       </c>
       <c r="AS4">
-        <v>11.64098655397444</v>
+        <v>9.623240208781265</v>
       </c>
       <c r="AT4">
-        <v>10.74098655397444</v>
+        <v>8.723240208781259</v>
       </c>
       <c r="AU4">
-        <v>2.685246638493609</v>
+        <v>2.180810052195315</v>
       </c>
       <c r="AV4">
-        <v>5.31</v>
+        <v>5.898436507750732</v>
       </c>
       <c r="AW4">
-        <v>6.76</v>
+        <v>5.472672171724974</v>
       </c>
       <c r="AX4">
-        <v>7.43</v>
+        <v>6.077994959568073</v>
       </c>
       <c r="AY4">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ4">
         <v>3</v>
       </c>
       <c r="BA4">
-        <v>1.54</v>
+        <v>1.541161542643699</v>
       </c>
       <c r="BB4">
-        <v>-4.01</v>
+        <v>-4.006524474852094</v>
       </c>
       <c r="BC4">
-        <v>11.42</v>
+        <v>11.41694912221213</v>
       </c>
       <c r="BD4">
-        <v>42.06</v>
+        <v>42.06393827345702</v>
       </c>
       <c r="BE4">
-        <v>23.64</v>
+        <v>23.63541255450272</v>
       </c>
       <c r="BF4">
-        <v>0.6899999999999999</v>
+        <v>0.6873186760847522</v>
       </c>
     </row>
     <row r="5" spans="1:58">
@@ -1347,163 +1341,163 @@
         <v>65</v>
       </c>
       <c r="C5">
-        <v>48.42</v>
+        <v>48.25</v>
       </c>
       <c r="D5">
-        <v>45.85</v>
+        <v>46.575</v>
       </c>
       <c r="E5">
-        <v>2.58</v>
+        <v>1.675</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I5">
+        <v>50.8832059056156</v>
+      </c>
+      <c r="J5">
+        <v>49.11679409438439</v>
+      </c>
+      <c r="K5">
+        <v>1.766411811231215</v>
+      </c>
+      <c r="L5">
+        <v>-1.225993544904167</v>
+      </c>
+      <c r="M5">
+        <v>0.5404182663270487</v>
+      </c>
+      <c r="N5">
+        <v>0.5404182663270487</v>
+      </c>
+      <c r="O5">
+        <v>0.25</v>
+      </c>
+      <c r="P5">
+        <v>0.75</v>
+      </c>
+      <c r="Q5">
+        <v>50.42345832627655</v>
+      </c>
+      <c r="R5">
+        <v>49.57654167372345</v>
+      </c>
+      <c r="S5">
+        <v>-0.9194951586781249</v>
+      </c>
+      <c r="T5">
+        <v>0.8469166525530903</v>
+      </c>
+      <c r="U5">
+        <v>0.8469166525530903</v>
+      </c>
+      <c r="V5">
+        <v>55.65418073718285</v>
+      </c>
+      <c r="W5">
+        <v>44.34581926281715</v>
+      </c>
+      <c r="X5" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z5" t="s">
         <v>74</v>
       </c>
-      <c r="I5">
-        <v>51.37</v>
-      </c>
-      <c r="J5">
-        <v>48.63</v>
-      </c>
-      <c r="K5">
-        <v>2.73</v>
-      </c>
-      <c r="L5">
-        <v>0.02</v>
-      </c>
-      <c r="M5">
-        <v>2.76</v>
-      </c>
-      <c r="N5">
-        <v>2.76</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>50.19</v>
-      </c>
-      <c r="R5">
-        <v>49.81</v>
-      </c>
-      <c r="S5">
-        <v>0.02</v>
-      </c>
-      <c r="T5">
-        <v>2.76</v>
-      </c>
-      <c r="U5">
-        <v>0.37</v>
-      </c>
-      <c r="V5">
-        <v>52.35</v>
-      </c>
-      <c r="W5">
-        <v>47.65</v>
-      </c>
-      <c r="X5" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>75</v>
-      </c>
       <c r="AA5" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="AB5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AC5">
-        <v>52.35</v>
+        <v>55.65418073718285</v>
       </c>
       <c r="AD5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AE5">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF5">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>0.530870777381373</v>
       </c>
       <c r="AL5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AM5">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="AN5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AO5" t="s">
         <v>65</v>
       </c>
       <c r="AP5">
-        <v>0.5351</v>
+        <v>0.5097999999999999</v>
       </c>
       <c r="AQ5">
-        <v>-7.02000000000001</v>
+        <v>-1.95999999999998</v>
       </c>
       <c r="AR5">
-        <v>8.755412717885292</v>
+        <v>3.15308334744691</v>
       </c>
       <c r="AS5">
-        <v>9.775412717885303</v>
+        <v>2.80691665255307</v>
       </c>
       <c r="AT5">
-        <v>9.265412717885297</v>
+        <v>2.97999999999999</v>
       </c>
       <c r="AU5">
-        <v>2.316353179471324</v>
+        <v>0.7449999999999974</v>
       </c>
       <c r="AV5">
-        <v>4.14</v>
+        <v>6.166256775636249</v>
       </c>
       <c r="AW5">
-        <v>5.55</v>
+        <v>5.33631557212084</v>
       </c>
       <c r="AX5">
-        <v>6.35</v>
+        <v>5.955513908523875</v>
       </c>
       <c r="AY5">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ5">
         <v>3</v>
       </c>
       <c r="BA5">
-        <v>1.93</v>
+        <v>1.878161728442779</v>
       </c>
       <c r="BB5">
-        <v>1.35</v>
+        <v>1.021885173756878</v>
       </c>
       <c r="BC5">
-        <v>5.75</v>
+        <v>7.445671083211828</v>
       </c>
       <c r="BD5">
         <v>0</v>
@@ -1512,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="BF5">
-        <v>0.9399999999999999</v>
+        <v>0.9207631564477893</v>
       </c>
     </row>
     <row r="6" spans="1:58">
@@ -1523,172 +1517,172 @@
         <v>65</v>
       </c>
       <c r="C6">
-        <v>48.32</v>
+        <v>46.075</v>
       </c>
       <c r="D6">
-        <v>46.18</v>
+        <v>46.2</v>
       </c>
       <c r="E6">
-        <v>2.15</v>
+        <v>-0.125</v>
       </c>
       <c r="F6" t="s">
         <v>67</v>
       </c>
       <c r="G6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I6">
+        <v>49.932267678136</v>
+      </c>
+      <c r="J6">
+        <v>50.06773232186399</v>
+      </c>
+      <c r="K6">
+        <v>-0.1354646437279925</v>
+      </c>
+      <c r="L6">
+        <v>-2.883221219172162</v>
+      </c>
+      <c r="M6">
+        <v>-3.018685862900155</v>
+      </c>
+      <c r="N6">
+        <v>-3.018685862900155</v>
+      </c>
+      <c r="O6">
+        <v>0.25</v>
+      </c>
+      <c r="P6">
+        <v>0.75</v>
+      </c>
+      <c r="Q6">
+        <v>48.85105972094644</v>
+      </c>
+      <c r="R6">
+        <v>51.14894027905356</v>
+      </c>
+      <c r="S6">
+        <v>-2.162415914379122</v>
+      </c>
+      <c r="T6">
+        <v>-2.297880558107114</v>
+      </c>
+      <c r="U6">
+        <v>-2.297880558107114</v>
+      </c>
+      <c r="V6">
+        <v>34.57168958828296</v>
+      </c>
+      <c r="W6">
+        <v>65.42831041171704</v>
+      </c>
+      <c r="X6" t="s">
         <v>71</v>
-      </c>
-      <c r="H6" t="s">
-        <v>74</v>
-      </c>
-      <c r="I6">
-        <v>51.14</v>
-      </c>
-      <c r="J6">
-        <v>48.86</v>
-      </c>
-      <c r="K6">
-        <v>2.28</v>
-      </c>
-      <c r="L6">
-        <v>0.05</v>
-      </c>
-      <c r="M6">
-        <v>2.32</v>
-      </c>
-      <c r="N6">
-        <v>2.32</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>1</v>
-      </c>
-      <c r="Q6">
-        <v>49.98</v>
-      </c>
-      <c r="R6">
-        <v>50.02</v>
-      </c>
-      <c r="S6">
-        <v>0.05</v>
-      </c>
-      <c r="T6">
-        <v>2.32</v>
-      </c>
-      <c r="U6">
-        <v>-0.05</v>
-      </c>
-      <c r="V6">
-        <v>49.76</v>
-      </c>
-      <c r="W6">
-        <v>50.24</v>
-      </c>
-      <c r="X6" t="s">
-        <v>72</v>
       </c>
       <c r="Y6" t="s">
         <v>65</v>
       </c>
       <c r="Z6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AA6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AB6" t="s">
         <v>75</v>
       </c>
       <c r="AC6">
-        <v>49.76</v>
+        <v>34.57168958828296</v>
       </c>
       <c r="AD6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AE6">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF6">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.248471410266716</v>
       </c>
       <c r="AL6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AM6">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="AN6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AO6" t="s">
         <v>65</v>
       </c>
       <c r="AP6">
-        <v>0.5097999999999999</v>
+        <v>0.5174</v>
       </c>
       <c r="AQ6">
-        <v>-1.95999999999998</v>
+        <v>-3.47999999999999</v>
       </c>
       <c r="AR6">
-        <v>1.675966859360293</v>
+        <v>3.702119441892886</v>
       </c>
       <c r="AS6">
-        <v>4.284033140639687</v>
+        <v>1.182119441892876</v>
       </c>
       <c r="AT6">
-        <v>2.97999999999999</v>
+        <v>2.442119441892881</v>
       </c>
       <c r="AU6">
-        <v>0.7449999999999974</v>
+        <v>0.6105298604732202</v>
       </c>
       <c r="AV6">
-        <v>6.17</v>
+        <v>5.775280601260435</v>
       </c>
       <c r="AW6">
-        <v>7.2</v>
+        <v>5.150295879788892</v>
       </c>
       <c r="AX6">
-        <v>7.83</v>
+        <v>5.789423950509446</v>
       </c>
       <c r="AY6">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ6">
         <v>3</v>
       </c>
       <c r="BA6">
-        <v>1.88</v>
+        <v>2.193175026846863</v>
       </c>
       <c r="BB6">
-        <v>1.02</v>
+        <v>-2.886112316484782</v>
       </c>
       <c r="BC6">
-        <v>7.45</v>
+        <v>6.837360120673064</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>30.49114883433812</v>
       </c>
       <c r="BE6">
         <v>0</v>
       </c>
       <c r="BF6">
-        <v>0.92</v>
+        <v>0.9513390040572299</v>
       </c>
     </row>
     <row r="7" spans="1:58">
@@ -1699,172 +1693,172 @@
         <v>65</v>
       </c>
       <c r="C7">
-        <v>45.4</v>
+        <v>47.3</v>
       </c>
       <c r="D7">
-        <v>46.12</v>
+        <v>50.16666667000001</v>
       </c>
       <c r="E7">
-        <v>-0.73</v>
+        <v>-2.866666667</v>
       </c>
       <c r="F7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H7" t="s">
         <v>72</v>
       </c>
       <c r="I7">
-        <v>49.6</v>
+        <v>48.52941176304619</v>
       </c>
       <c r="J7">
-        <v>50.4</v>
+        <v>51.47058823695382</v>
       </c>
       <c r="K7">
-        <v>-0.79</v>
+        <v>-2.941176473907625</v>
       </c>
       <c r="L7">
-        <v>-1.77</v>
+        <v>0.5792673114617315</v>
       </c>
       <c r="M7">
-        <v>-2.56</v>
+        <v>-2.361909162445893</v>
       </c>
       <c r="N7">
-        <v>-2.56</v>
+        <v>-2.361909162445893</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q7">
-        <v>48.72</v>
+        <v>48.74663700484434</v>
       </c>
       <c r="R7">
-        <v>51.28</v>
+        <v>51.25336299515566</v>
       </c>
       <c r="S7">
-        <v>-1.77</v>
+        <v>0.434450483596299</v>
       </c>
       <c r="T7">
-        <v>-2.56</v>
+        <v>-2.506725990311326</v>
       </c>
       <c r="U7">
-        <v>-2.56</v>
+        <v>-2.506725990311326</v>
       </c>
       <c r="V7">
-        <v>36.52</v>
+        <v>33.66396774649345</v>
       </c>
       <c r="W7">
-        <v>63.48</v>
+        <v>66.33603225350654</v>
       </c>
       <c r="X7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="Y7" t="s">
         <v>65</v>
       </c>
       <c r="Z7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AA7" t="s">
         <v>65</v>
       </c>
       <c r="AB7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AC7">
-        <v>36.52</v>
+        <v>33.66396774649345</v>
       </c>
       <c r="AD7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AE7">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF7">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH7">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>0.2508301036538862</v>
       </c>
       <c r="AL7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AM7">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="AN7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AO7" t="s">
         <v>65</v>
       </c>
       <c r="AP7">
-        <v>0.5174</v>
+        <v>0.6258</v>
       </c>
       <c r="AQ7">
-        <v>-3.47999999999999</v>
+        <v>-25.16000000000001</v>
       </c>
       <c r="AR7">
-        <v>3.435838333780036</v>
+        <v>7.493274009688674</v>
       </c>
       <c r="AS7">
-        <v>0.9158383337800258</v>
+        <v>22.65327400968869</v>
       </c>
       <c r="AT7">
-        <v>2.175838333780031</v>
+        <v>15.07327400968868</v>
       </c>
       <c r="AU7">
-        <v>0.5439595834450077</v>
+        <v>3.76831850242217</v>
       </c>
       <c r="AV7">
-        <v>5.7</v>
+        <v>4.390437171606355</v>
       </c>
       <c r="AW7">
-        <v>6.77</v>
+        <v>5.324598663427484</v>
       </c>
       <c r="AX7">
-        <v>7.44</v>
+        <v>5.945017489960455</v>
       </c>
       <c r="AY7">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ7">
         <v>3</v>
       </c>
       <c r="BA7">
-        <v>2.19</v>
+        <v>1.906296723190152</v>
       </c>
       <c r="BB7">
-        <v>-2.89</v>
+        <v>-1.372324784465838</v>
       </c>
       <c r="BC7">
-        <v>6.84</v>
+        <v>5.414780435479317</v>
       </c>
       <c r="BD7">
-        <v>30.49</v>
+        <v>0</v>
       </c>
       <c r="BE7">
         <v>0</v>
       </c>
       <c r="BF7">
-        <v>0.95</v>
+        <v>0.9325238981752073</v>
       </c>
     </row>
     <row r="8" spans="1:58">
@@ -1875,172 +1869,172 @@
         <v>65</v>
       </c>
       <c r="C8">
-        <v>47.27</v>
+        <v>45.875</v>
       </c>
       <c r="D8">
-        <v>50.17</v>
+        <v>49.675</v>
       </c>
       <c r="E8">
-        <v>-2.9</v>
+        <v>-3.8</v>
       </c>
       <c r="F8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I8">
-        <v>48.51</v>
+        <v>48.01151229722657</v>
       </c>
       <c r="J8">
-        <v>51.49</v>
+        <v>51.98848770277341</v>
       </c>
       <c r="K8">
-        <v>-2.98</v>
+        <v>-3.976975405546838</v>
       </c>
       <c r="L8">
-        <v>1.78</v>
+        <v>-0.2491280460552653</v>
       </c>
       <c r="M8">
-        <v>-1.2</v>
+        <v>-4.226103451602103</v>
       </c>
       <c r="N8">
-        <v>-1.2</v>
+        <v>-4.226103451602103</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P8">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q8">
-        <v>48.13</v>
+        <v>47.91808927995586</v>
       </c>
       <c r="R8">
-        <v>51.87</v>
+        <v>52.08191072004414</v>
       </c>
       <c r="S8">
-        <v>1.78</v>
+        <v>-0.1868460345414489</v>
       </c>
       <c r="T8">
-        <v>-1.2</v>
+        <v>-4.163821440088287</v>
       </c>
       <c r="U8">
-        <v>-3.74</v>
+        <v>-4.163821440088287</v>
       </c>
       <c r="V8">
-        <v>30.07</v>
+        <v>21.63743754626992</v>
       </c>
       <c r="W8">
-        <v>69.93000000000001</v>
+        <v>78.36256245373008</v>
       </c>
       <c r="X8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="Y8" t="s">
         <v>65</v>
       </c>
       <c r="Z8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AA8" t="s">
         <v>65</v>
       </c>
       <c r="AB8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AC8">
-        <v>30.07</v>
+        <v>21.63743754626992</v>
       </c>
       <c r="AD8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AE8">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF8">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>0.1078756083395196</v>
       </c>
       <c r="AL8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AM8">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="AN8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AO8" t="s">
         <v>65</v>
       </c>
       <c r="AP8">
-        <v>0.6258</v>
+        <v>0.5322</v>
       </c>
       <c r="AQ8">
-        <v>-25.16000000000001</v>
+        <v>-6.439999999999998</v>
       </c>
       <c r="AR8">
-        <v>8.804477444369347</v>
+        <v>3.836178559911713</v>
       </c>
       <c r="AS8">
-        <v>23.96447744436936</v>
+        <v>2.276178559911711</v>
       </c>
       <c r="AT8">
-        <v>16.38447744436935</v>
+        <v>3.056178559911712</v>
       </c>
       <c r="AU8">
-        <v>4.096119361092338</v>
+        <v>0.7640446399779279</v>
       </c>
       <c r="AV8">
-        <v>4.13</v>
+        <v>5.314982794026658</v>
       </c>
       <c r="AW8">
-        <v>6.47</v>
+        <v>4.602075819872517</v>
       </c>
       <c r="AX8">
-        <v>7.17</v>
+        <v>5.307634490167654</v>
       </c>
       <c r="AY8">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA8">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>-1.37</v>
+        <v>-0.3706239798868902</v>
       </c>
       <c r="BC8">
-        <v>5.41</v>
+        <v>5.000892084631056</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>8.823529411764707</v>
       </c>
       <c r="BF8">
-        <v>0.93</v>
+        <v>0.9238036867710117</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block5B_Senate_Competitive_Races.xlsx
+++ b/outputs/Block5B_Senate_Competitive_Races.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="96">
   <si>
     <t>STATE</t>
   </si>
@@ -190,6 +190,9 @@
     <t>Mean Comparability Weight</t>
   </si>
   <si>
+    <t>Michigan</t>
+  </si>
+  <si>
     <t>Texas</t>
   </si>
   <si>
@@ -211,9 +214,15 @@
     <t>Kansas</t>
   </si>
   <si>
+    <t>D</t>
+  </si>
+  <si>
     <t>R</t>
   </si>
   <si>
+    <t>DSenLeanPollH (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
     <t>RSenLeanPollLD (&gt;1&lt;=5%)</t>
   </si>
   <si>
@@ -235,7 +244,13 @@
     <t>Lean</t>
   </si>
   <si>
-    <t>D</t>
+    <t>D Tilt</t>
+  </si>
+  <si>
+    <t>R Tilt</t>
+  </si>
+  <si>
+    <t>Democratic Hold</t>
   </si>
   <si>
     <t>Democratic Flip</t>
@@ -247,6 +262,9 @@
     <t>Polling-error correction retained — inner LOEO improved MAE</t>
   </si>
   <si>
+    <t>EVEN</t>
+  </si>
+  <si>
     <t>R+6</t>
   </si>
   <si>
@@ -260,6 +278,9 @@
   </si>
   <si>
     <t>R+8</t>
+  </si>
+  <si>
+    <t>49.90% D</t>
   </si>
   <si>
     <t>53.51% R</t>
@@ -638,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BF8"/>
+  <dimension ref="A1:BF9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:58">
@@ -822,43 +843,43 @@
         <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2">
-        <v>48.675</v>
+        <v>48.175</v>
       </c>
       <c r="D2">
-        <v>45.65</v>
+        <v>45</v>
       </c>
       <c r="E2">
-        <v>3.025</v>
+        <v>3.175</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I2">
-        <v>51.60349854227405</v>
+        <v>51.70378320364904</v>
       </c>
       <c r="J2">
-        <v>48.39650145772595</v>
+        <v>48.29621679635095</v>
       </c>
       <c r="K2">
-        <v>3.206997084548107</v>
+        <v>3.407566407298091</v>
       </c>
       <c r="L2">
-        <v>-1.2681457739171</v>
+        <v>2.219283990383333</v>
       </c>
       <c r="M2">
-        <v>1.938851310631006</v>
+        <v>5.626850397681425</v>
       </c>
       <c r="N2">
-        <v>1.938851310631006</v>
+        <v>5.626850397681425</v>
       </c>
       <c r="O2">
         <v>0.25</v>
@@ -867,46 +888,46 @@
         <v>0.75</v>
       </c>
       <c r="Q2">
-        <v>51.12794387705514</v>
+        <v>52.5360147000428</v>
       </c>
       <c r="R2">
-        <v>48.87205612294486</v>
+        <v>47.4639852999572</v>
       </c>
       <c r="S2">
-        <v>-0.9511093304378253</v>
+        <v>1.664462992787501</v>
       </c>
       <c r="T2">
-        <v>2.255887754110281</v>
+        <v>5.072029400085592</v>
       </c>
       <c r="U2">
-        <v>2.255887754110281</v>
+        <v>5.072029400085592</v>
       </c>
       <c r="V2">
-        <v>67.08308487070286</v>
+        <v>83.72921551043582</v>
       </c>
       <c r="W2">
-        <v>32.91691512929713</v>
+        <v>16.27078448956417</v>
       </c>
       <c r="X2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="Z2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AA2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="AB2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AC2">
-        <v>67.08308487070286</v>
+        <v>16.27078448956417</v>
       </c>
       <c r="AD2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AE2">
         <v>8.73527450544567</v>
@@ -924,49 +945,49 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2">
-        <v>0.549123227957043</v>
+        <v>0.9609781569420333</v>
       </c>
       <c r="AL2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AM2">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="AO2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AP2">
-        <v>0.5351</v>
+        <v>0.499</v>
       </c>
       <c r="AQ2">
-        <v>-7.02000000000001</v>
+        <v>-0.2000000000000028</v>
       </c>
       <c r="AR2">
-        <v>8.255887754110281</v>
+        <v>5.072029400085592</v>
       </c>
       <c r="AS2">
-        <v>9.275887754110292</v>
+        <v>5.272029400085595</v>
       </c>
       <c r="AT2">
-        <v>8.765887754110286</v>
+        <v>5.172029400085593</v>
       </c>
       <c r="AU2">
-        <v>2.191471938527572</v>
+        <v>1.293007350021398</v>
       </c>
       <c r="AV2">
-        <v>4.345503062353619</v>
+        <v>4.890566271054463</v>
       </c>
       <c r="AW2">
-        <v>4.362627316035638</v>
+        <v>4.428317085264829</v>
       </c>
       <c r="AX2">
-        <v>5.101411483891715</v>
+        <v>5.157700479575209</v>
       </c>
       <c r="AY2">
         <v>0.8436468628413508</v>
@@ -975,13 +996,13 @@
         <v>3</v>
       </c>
       <c r="BA2">
-        <v>1.930645252303767</v>
+        <v>1.928319091839648</v>
       </c>
       <c r="BB2">
-        <v>1.354753062157686</v>
+        <v>-0.6920346275003579</v>
       </c>
       <c r="BC2">
-        <v>5.754964092348529</v>
+        <v>1.192072171556674</v>
       </c>
       <c r="BD2">
         <v>0</v>
@@ -990,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="BF2">
-        <v>0.9442145399410329</v>
+        <v>0.9413992011197729</v>
       </c>
     </row>
     <row r="3" spans="1:58">
@@ -998,43 +1019,43 @@
         <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C3">
-        <v>48.225</v>
+        <v>48.675</v>
       </c>
       <c r="D3">
-        <v>45.1</v>
+        <v>45.65</v>
       </c>
       <c r="E3">
-        <v>3.125</v>
+        <v>3.025</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I3">
-        <v>51.67425663005626</v>
+        <v>51.60349854227405</v>
       </c>
       <c r="J3">
-        <v>48.32574336994374</v>
+        <v>48.39650145772595</v>
       </c>
       <c r="K3">
-        <v>3.348513260112512</v>
+        <v>3.206997084548107</v>
       </c>
       <c r="L3">
-        <v>-1.794861267366732</v>
+        <v>-1.2681457739171</v>
       </c>
       <c r="M3">
-        <v>1.553651992745779</v>
+        <v>1.938851310631006</v>
       </c>
       <c r="N3">
-        <v>1.553651992745779</v>
+        <v>1.938851310631006</v>
       </c>
       <c r="O3">
         <v>0.25</v>
@@ -1043,46 +1064,46 @@
         <v>0.75</v>
       </c>
       <c r="Q3">
-        <v>51.00118365479373</v>
+        <v>51.12794387705514</v>
       </c>
       <c r="R3">
-        <v>48.99881634520627</v>
+        <v>48.87205612294486</v>
       </c>
       <c r="S3">
-        <v>-1.346145950525049</v>
+        <v>-0.9511093304378253</v>
       </c>
       <c r="T3">
-        <v>2.002367309587462</v>
+        <v>2.255887754110281</v>
       </c>
       <c r="U3">
-        <v>2.002367309587462</v>
+        <v>2.255887754110281</v>
       </c>
       <c r="V3">
-        <v>65.26388699510164</v>
+        <v>67.08308487070286</v>
       </c>
       <c r="W3">
-        <v>34.73611300489836</v>
+        <v>32.91691512929713</v>
       </c>
       <c r="X3" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="Y3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="Z3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AA3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="AB3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AC3">
-        <v>65.26388699510164</v>
+        <v>67.08308487070286</v>
       </c>
       <c r="AD3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AE3">
         <v>8.73527450544567</v>
@@ -1103,58 +1124,70 @@
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>0.7771977269041618</v>
+        <v>0.549123227957043</v>
       </c>
       <c r="AL3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="AM3">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="AN3" t="s">
-        <v>83</v>
+        <v>89</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AP3">
+        <v>0.5351</v>
+      </c>
+      <c r="AQ3">
+        <v>-7.02000000000001</v>
       </c>
       <c r="AR3">
-        <v>7.002367309587463</v>
+        <v>8.255887754110281</v>
+      </c>
+      <c r="AS3">
+        <v>9.275887754110292</v>
       </c>
       <c r="AT3">
-        <v>7.002367309587463</v>
+        <v>8.765887754110286</v>
       </c>
       <c r="AU3">
-        <v>1.750591827396866</v>
+        <v>2.191471938527572</v>
       </c>
       <c r="AV3">
-        <v>4.567515257270437</v>
+        <v>4.345503062353619</v>
       </c>
       <c r="AW3">
-        <v>4.363504132448985</v>
+        <v>4.362627316035638</v>
       </c>
       <c r="AX3">
-        <v>5.102161340379323</v>
+        <v>5.101411483891715</v>
       </c>
       <c r="AY3">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA3">
-        <v>2.797261014127842</v>
+        <v>1.930645252303767</v>
       </c>
       <c r="BB3">
-        <v>0.1730167113317724</v>
+        <v>1.354753062157686</v>
       </c>
       <c r="BC3">
-        <v>2.956526743070407</v>
+        <v>5.754964092348529</v>
       </c>
       <c r="BD3">
-        <v>17.4915896825486</v>
+        <v>0</v>
       </c>
       <c r="BE3">
         <v>0</v>
       </c>
       <c r="BF3">
-        <v>0.956231216651788</v>
+        <v>0.9442145399410329</v>
       </c>
     </row>
     <row r="4" spans="1:58">
@@ -1162,43 +1195,43 @@
         <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C4">
-        <v>49.325</v>
+        <v>48.225</v>
       </c>
       <c r="D4">
-        <v>47.475</v>
+        <v>45.1</v>
       </c>
       <c r="E4">
-        <v>1.85</v>
+        <v>3.125</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I4">
-        <v>50.95557851239669</v>
+        <v>51.67425663005626</v>
       </c>
       <c r="J4">
-        <v>49.0444214876033</v>
+        <v>48.32574336994374</v>
       </c>
       <c r="K4">
-        <v>1.91115702479339</v>
+        <v>3.348513260112512</v>
       </c>
       <c r="L4">
-        <v>-0.1172224213495152</v>
+        <v>-1.794861267366732</v>
       </c>
       <c r="M4">
-        <v>1.793934603443875</v>
+        <v>1.553651992745779</v>
       </c>
       <c r="N4">
-        <v>1.793934603443875</v>
+        <v>1.553651992745779</v>
       </c>
       <c r="O4">
         <v>0.25</v>
@@ -1207,46 +1240,46 @@
         <v>0.75</v>
       </c>
       <c r="Q4">
-        <v>50.91162010439063</v>
+        <v>51.00118365479373</v>
       </c>
       <c r="R4">
-        <v>49.08837989560937</v>
+        <v>48.99881634520627</v>
       </c>
       <c r="S4">
-        <v>-0.08791681601213641</v>
+        <v>-1.346145950525049</v>
       </c>
       <c r="T4">
-        <v>1.823240208781253</v>
+        <v>2.002367309587462</v>
       </c>
       <c r="U4">
-        <v>1.823240208781253</v>
+        <v>2.002367309587462</v>
       </c>
       <c r="V4">
-        <v>61.79014903031504</v>
+        <v>65.26388699510164</v>
       </c>
       <c r="W4">
-        <v>38.20985096968496</v>
+        <v>34.73611300489836</v>
       </c>
       <c r="X4" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="Y4" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="Z4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AA4" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="AB4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AC4">
-        <v>61.79014903031504</v>
+        <v>65.26388699510164</v>
       </c>
       <c r="AD4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AE4">
         <v>8.73527450544567</v>
@@ -1267,70 +1300,58 @@
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>0.05075879739090176</v>
+        <v>0.7771977269041618</v>
       </c>
       <c r="AL4" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AM4">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="AN4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>65</v>
-      </c>
-      <c r="AP4">
-        <v>0.539</v>
-      </c>
-      <c r="AQ4">
-        <v>-7.800000000000011</v>
+        <v>90</v>
       </c>
       <c r="AR4">
-        <v>7.823240208781254</v>
-      </c>
-      <c r="AS4">
-        <v>9.623240208781265</v>
+        <v>7.002367309587463</v>
       </c>
       <c r="AT4">
-        <v>8.723240208781259</v>
+        <v>7.002367309587463</v>
       </c>
       <c r="AU4">
-        <v>2.180810052195315</v>
+        <v>1.750591827396866</v>
       </c>
       <c r="AV4">
-        <v>5.898436507750732</v>
+        <v>4.567515257270437</v>
       </c>
       <c r="AW4">
-        <v>5.472672171724974</v>
+        <v>4.363504132448985</v>
       </c>
       <c r="AX4">
-        <v>6.077994959568073</v>
+        <v>5.102161340379323</v>
       </c>
       <c r="AY4">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA4">
-        <v>1.541161542643699</v>
+        <v>2.797261014127842</v>
       </c>
       <c r="BB4">
-        <v>-4.006524474852094</v>
+        <v>0.1730167113317724</v>
       </c>
       <c r="BC4">
-        <v>11.41694912221213</v>
+        <v>2.956526743070407</v>
       </c>
       <c r="BD4">
-        <v>42.06393827345702</v>
+        <v>17.4915896825486</v>
       </c>
       <c r="BE4">
-        <v>23.63541255450272</v>
+        <v>0</v>
       </c>
       <c r="BF4">
-        <v>0.6873186760847522</v>
+        <v>0.956231216651788</v>
       </c>
     </row>
     <row r="5" spans="1:58">
@@ -1338,43 +1359,43 @@
         <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C5">
-        <v>48.25</v>
+        <v>49.325</v>
       </c>
       <c r="D5">
-        <v>46.575</v>
+        <v>47.475</v>
       </c>
       <c r="E5">
-        <v>1.675</v>
+        <v>1.85</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I5">
-        <v>50.8832059056156</v>
+        <v>50.95557851239669</v>
       </c>
       <c r="J5">
-        <v>49.11679409438439</v>
+        <v>49.0444214876033</v>
       </c>
       <c r="K5">
-        <v>1.766411811231215</v>
+        <v>1.91115702479339</v>
       </c>
       <c r="L5">
-        <v>-1.225993544904167</v>
+        <v>-0.1172224213495152</v>
       </c>
       <c r="M5">
-        <v>0.5404182663270487</v>
+        <v>1.793934603443875</v>
       </c>
       <c r="N5">
-        <v>0.5404182663270487</v>
+        <v>1.793934603443875</v>
       </c>
       <c r="O5">
         <v>0.25</v>
@@ -1383,46 +1404,46 @@
         <v>0.75</v>
       </c>
       <c r="Q5">
-        <v>50.42345832627655</v>
+        <v>50.91162010439063</v>
       </c>
       <c r="R5">
-        <v>49.57654167372345</v>
+        <v>49.08837989560937</v>
       </c>
       <c r="S5">
-        <v>-0.9194951586781249</v>
+        <v>-0.08791681601213641</v>
       </c>
       <c r="T5">
-        <v>0.8469166525530903</v>
+        <v>1.823240208781253</v>
       </c>
       <c r="U5">
-        <v>0.8469166525530903</v>
+        <v>1.823240208781253</v>
       </c>
       <c r="V5">
-        <v>55.65418073718285</v>
+        <v>61.79014903031504</v>
       </c>
       <c r="W5">
-        <v>44.34581926281715</v>
+        <v>38.20985096968496</v>
       </c>
       <c r="X5" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="Y5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="Z5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AA5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="AB5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AC5">
-        <v>55.65418073718285</v>
+        <v>61.79014903031504</v>
       </c>
       <c r="AD5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AE5">
         <v>8.73527450544567</v>
@@ -1443,46 +1464,46 @@
         <v>0</v>
       </c>
       <c r="AK5">
-        <v>0.530870777381373</v>
+        <v>0.05075879739090176</v>
       </c>
       <c r="AL5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AM5">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="AN5" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="AO5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AP5">
-        <v>0.5097999999999999</v>
+        <v>0.539</v>
       </c>
       <c r="AQ5">
-        <v>-1.95999999999998</v>
+        <v>-7.800000000000011</v>
       </c>
       <c r="AR5">
-        <v>3.15308334744691</v>
+        <v>7.823240208781254</v>
       </c>
       <c r="AS5">
-        <v>2.80691665255307</v>
+        <v>9.623240208781265</v>
       </c>
       <c r="AT5">
-        <v>2.97999999999999</v>
+        <v>8.723240208781259</v>
       </c>
       <c r="AU5">
-        <v>0.7449999999999974</v>
+        <v>2.180810052195315</v>
       </c>
       <c r="AV5">
-        <v>6.166256775636249</v>
+        <v>5.898436507750732</v>
       </c>
       <c r="AW5">
-        <v>5.33631557212084</v>
+        <v>5.472672171724974</v>
       </c>
       <c r="AX5">
-        <v>5.955513908523875</v>
+        <v>6.077994959568073</v>
       </c>
       <c r="AY5">
         <v>0.8436468628413508</v>
@@ -1491,22 +1512,22 @@
         <v>3</v>
       </c>
       <c r="BA5">
-        <v>1.878161728442779</v>
+        <v>1.541161542643699</v>
       </c>
       <c r="BB5">
-        <v>1.021885173756878</v>
+        <v>-4.006524474852094</v>
       </c>
       <c r="BC5">
-        <v>7.445671083211828</v>
+        <v>11.41694912221213</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>42.06393827345702</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>23.63541255450272</v>
       </c>
       <c r="BF5">
-        <v>0.9207631564477893</v>
+        <v>0.6873186760847522</v>
       </c>
     </row>
     <row r="6" spans="1:58">
@@ -1514,43 +1535,43 @@
         <v>62</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C6">
-        <v>46.075</v>
+        <v>48.25</v>
       </c>
       <c r="D6">
-        <v>46.2</v>
+        <v>46.575</v>
       </c>
       <c r="E6">
-        <v>-0.125</v>
+        <v>1.675</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I6">
-        <v>49.932267678136</v>
+        <v>50.8832059056156</v>
       </c>
       <c r="J6">
-        <v>50.06773232186399</v>
+        <v>49.11679409438439</v>
       </c>
       <c r="K6">
-        <v>-0.1354646437279925</v>
+        <v>1.766411811231215</v>
       </c>
       <c r="L6">
-        <v>-2.883221219172162</v>
+        <v>-1.225993544904167</v>
       </c>
       <c r="M6">
-        <v>-3.018685862900155</v>
+        <v>0.5404182663270487</v>
       </c>
       <c r="N6">
-        <v>-3.018685862900155</v>
+        <v>0.5404182663270487</v>
       </c>
       <c r="O6">
         <v>0.25</v>
@@ -1559,46 +1580,46 @@
         <v>0.75</v>
       </c>
       <c r="Q6">
-        <v>48.85105972094644</v>
+        <v>50.42345832627655</v>
       </c>
       <c r="R6">
-        <v>51.14894027905356</v>
+        <v>49.57654167372345</v>
       </c>
       <c r="S6">
-        <v>-2.162415914379122</v>
+        <v>-0.9194951586781249</v>
       </c>
       <c r="T6">
-        <v>-2.297880558107114</v>
+        <v>0.8469166525530903</v>
       </c>
       <c r="U6">
-        <v>-2.297880558107114</v>
+        <v>0.8469166525530903</v>
       </c>
       <c r="V6">
-        <v>34.57168958828296</v>
+        <v>55.65418073718285</v>
       </c>
       <c r="W6">
-        <v>65.42831041171704</v>
+        <v>44.34581926281715</v>
       </c>
       <c r="X6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Y6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Z6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AA6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AB6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AC6">
-        <v>34.57168958828296</v>
+        <v>55.65418073718285</v>
       </c>
       <c r="AD6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AE6">
         <v>8.73527450544567</v>
@@ -1619,46 +1640,46 @@
         <v>0</v>
       </c>
       <c r="AK6">
-        <v>1.248471410266716</v>
+        <v>0.530870777381373</v>
       </c>
       <c r="AL6" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AM6">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="AN6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="AO6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AP6">
-        <v>0.5174</v>
+        <v>0.5097999999999999</v>
       </c>
       <c r="AQ6">
-        <v>-3.47999999999999</v>
+        <v>-1.95999999999998</v>
       </c>
       <c r="AR6">
-        <v>3.702119441892886</v>
+        <v>3.15308334744691</v>
       </c>
       <c r="AS6">
-        <v>1.182119441892876</v>
+        <v>2.80691665255307</v>
       </c>
       <c r="AT6">
-        <v>2.442119441892881</v>
+        <v>2.97999999999999</v>
       </c>
       <c r="AU6">
-        <v>0.6105298604732202</v>
+        <v>0.7449999999999974</v>
       </c>
       <c r="AV6">
-        <v>5.775280601260435</v>
+        <v>6.166256775636249</v>
       </c>
       <c r="AW6">
-        <v>5.150295879788892</v>
+        <v>5.33631557212084</v>
       </c>
       <c r="AX6">
-        <v>5.789423950509446</v>
+        <v>5.955513908523875</v>
       </c>
       <c r="AY6">
         <v>0.8436468628413508</v>
@@ -1667,22 +1688,22 @@
         <v>3</v>
       </c>
       <c r="BA6">
-        <v>2.193175026846863</v>
+        <v>1.878161728442779</v>
       </c>
       <c r="BB6">
-        <v>-2.886112316484782</v>
+        <v>1.021885173756878</v>
       </c>
       <c r="BC6">
-        <v>6.837360120673064</v>
+        <v>7.445671083211828</v>
       </c>
       <c r="BD6">
-        <v>30.49114883433812</v>
+        <v>0</v>
       </c>
       <c r="BE6">
         <v>0</v>
       </c>
       <c r="BF6">
-        <v>0.9513390040572299</v>
+        <v>0.9207631564477893</v>
       </c>
     </row>
     <row r="7" spans="1:58">
@@ -1690,43 +1711,43 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C7">
-        <v>47.3</v>
+        <v>46.075</v>
       </c>
       <c r="D7">
-        <v>50.16666667000001</v>
+        <v>46.2</v>
       </c>
       <c r="E7">
-        <v>-2.866666667</v>
+        <v>-0.125</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I7">
-        <v>48.52941176304619</v>
+        <v>49.932267678136</v>
       </c>
       <c r="J7">
-        <v>51.47058823695382</v>
+        <v>50.06773232186399</v>
       </c>
       <c r="K7">
-        <v>-2.941176473907625</v>
+        <v>-0.1354646437279925</v>
       </c>
       <c r="L7">
-        <v>0.5792673114617315</v>
+        <v>-2.883221219172162</v>
       </c>
       <c r="M7">
-        <v>-2.361909162445893</v>
+        <v>-3.018685862900155</v>
       </c>
       <c r="N7">
-        <v>-2.361909162445893</v>
+        <v>-3.018685862900155</v>
       </c>
       <c r="O7">
         <v>0.25</v>
@@ -1735,46 +1756,46 @@
         <v>0.75</v>
       </c>
       <c r="Q7">
-        <v>48.74663700484434</v>
+        <v>48.85105972094644</v>
       </c>
       <c r="R7">
-        <v>51.25336299515566</v>
+        <v>51.14894027905356</v>
       </c>
       <c r="S7">
-        <v>0.434450483596299</v>
+        <v>-2.162415914379122</v>
       </c>
       <c r="T7">
-        <v>-2.506725990311326</v>
+        <v>-2.297880558107114</v>
       </c>
       <c r="U7">
-        <v>-2.506725990311326</v>
+        <v>-2.297880558107114</v>
       </c>
       <c r="V7">
-        <v>33.66396774649345</v>
+        <v>34.57168958828296</v>
       </c>
       <c r="W7">
-        <v>66.33603225350654</v>
+        <v>65.42831041171704</v>
       </c>
       <c r="X7" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Y7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AB7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AC7">
-        <v>33.66396774649345</v>
+        <v>34.57168958828296</v>
       </c>
       <c r="AD7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AE7">
         <v>8.73527450544567</v>
@@ -1795,46 +1816,46 @@
         <v>0</v>
       </c>
       <c r="AK7">
-        <v>0.2508301036538862</v>
+        <v>1.248471410266716</v>
       </c>
       <c r="AL7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AM7">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="AN7" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="AO7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AP7">
-        <v>0.6258</v>
+        <v>0.5174</v>
       </c>
       <c r="AQ7">
-        <v>-25.16000000000001</v>
+        <v>-3.47999999999999</v>
       </c>
       <c r="AR7">
-        <v>7.493274009688674</v>
+        <v>3.702119441892886</v>
       </c>
       <c r="AS7">
-        <v>22.65327400968869</v>
+        <v>1.182119441892876</v>
       </c>
       <c r="AT7">
-        <v>15.07327400968868</v>
+        <v>2.442119441892881</v>
       </c>
       <c r="AU7">
-        <v>3.76831850242217</v>
+        <v>0.6105298604732202</v>
       </c>
       <c r="AV7">
-        <v>4.390437171606355</v>
+        <v>5.775280601260435</v>
       </c>
       <c r="AW7">
-        <v>5.324598663427484</v>
+        <v>5.150295879788892</v>
       </c>
       <c r="AX7">
-        <v>5.945017489960455</v>
+        <v>5.789423950509446</v>
       </c>
       <c r="AY7">
         <v>0.8436468628413508</v>
@@ -1843,22 +1864,22 @@
         <v>3</v>
       </c>
       <c r="BA7">
-        <v>1.906296723190152</v>
+        <v>2.193175026846863</v>
       </c>
       <c r="BB7">
-        <v>-1.372324784465838</v>
+        <v>-2.886112316484782</v>
       </c>
       <c r="BC7">
-        <v>5.414780435479317</v>
+        <v>6.837360120673064</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>30.49114883433812</v>
       </c>
       <c r="BE7">
         <v>0</v>
       </c>
       <c r="BF7">
-        <v>0.9325238981752073</v>
+        <v>0.9513390040572299</v>
       </c>
     </row>
     <row r="8" spans="1:58">
@@ -1866,43 +1887,43 @@
         <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C8">
-        <v>45.875</v>
+        <v>47.3</v>
       </c>
       <c r="D8">
-        <v>49.675</v>
+        <v>50.16666667000001</v>
       </c>
       <c r="E8">
-        <v>-3.8</v>
+        <v>-2.866666667</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I8">
-        <v>48.01151229722657</v>
+        <v>48.52941176304619</v>
       </c>
       <c r="J8">
-        <v>51.98848770277341</v>
+        <v>51.47058823695382</v>
       </c>
       <c r="K8">
-        <v>-3.976975405546838</v>
+        <v>-2.941176473907625</v>
       </c>
       <c r="L8">
-        <v>-0.2491280460552653</v>
+        <v>0.5792673114617315</v>
       </c>
       <c r="M8">
-        <v>-4.226103451602103</v>
+        <v>-2.361909162445893</v>
       </c>
       <c r="N8">
-        <v>-4.226103451602103</v>
+        <v>-2.361909162445893</v>
       </c>
       <c r="O8">
         <v>0.25</v>
@@ -1911,46 +1932,46 @@
         <v>0.75</v>
       </c>
       <c r="Q8">
-        <v>47.91808927995586</v>
+        <v>48.74663700484434</v>
       </c>
       <c r="R8">
-        <v>52.08191072004414</v>
+        <v>51.25336299515566</v>
       </c>
       <c r="S8">
-        <v>-0.1868460345414489</v>
+        <v>0.434450483596299</v>
       </c>
       <c r="T8">
-        <v>-4.163821440088287</v>
+        <v>-2.506725990311326</v>
       </c>
       <c r="U8">
-        <v>-4.163821440088287</v>
+        <v>-2.506725990311326</v>
       </c>
       <c r="V8">
-        <v>21.63743754626992</v>
+        <v>33.66396774649345</v>
       </c>
       <c r="W8">
-        <v>78.36256245373008</v>
+        <v>66.33603225350654</v>
       </c>
       <c r="X8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Y8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z8" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AB8" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AC8">
-        <v>21.63743754626992</v>
+        <v>33.66396774649345</v>
       </c>
       <c r="AD8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AE8">
         <v>8.73527450544567</v>
@@ -1971,69 +1992,245 @@
         <v>0</v>
       </c>
       <c r="AK8">
-        <v>0.1078756083395196</v>
+        <v>0.2508301036538862</v>
       </c>
       <c r="AL8" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="AM8">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="AN8" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AO8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AP8">
-        <v>0.5322</v>
+        <v>0.6258</v>
       </c>
       <c r="AQ8">
-        <v>-6.439999999999998</v>
+        <v>-25.16000000000001</v>
       </c>
       <c r="AR8">
-        <v>3.836178559911713</v>
+        <v>7.493274009688674</v>
       </c>
       <c r="AS8">
-        <v>2.276178559911711</v>
+        <v>22.65327400968869</v>
       </c>
       <c r="AT8">
-        <v>3.056178559911712</v>
+        <v>15.07327400968868</v>
       </c>
       <c r="AU8">
-        <v>0.7640446399779279</v>
+        <v>3.76831850242217</v>
       </c>
       <c r="AV8">
-        <v>5.314982794026658</v>
+        <v>4.390437171606355</v>
       </c>
       <c r="AW8">
-        <v>4.602075819872517</v>
+        <v>5.324598663427484</v>
       </c>
       <c r="AX8">
-        <v>5.307634490167654</v>
+        <v>5.945017489960455</v>
       </c>
       <c r="AY8">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.906296723190152</v>
       </c>
       <c r="BB8">
+        <v>-1.372324784465838</v>
+      </c>
+      <c r="BC8">
+        <v>5.414780435479317</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0.9325238981752073</v>
+      </c>
+    </row>
+    <row r="9" spans="1:58">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9">
+        <v>45.875</v>
+      </c>
+      <c r="D9">
+        <v>49.675</v>
+      </c>
+      <c r="E9">
+        <v>-3.8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9">
+        <v>48.01151229722657</v>
+      </c>
+      <c r="J9">
+        <v>51.98848770277341</v>
+      </c>
+      <c r="K9">
+        <v>-3.976975405546838</v>
+      </c>
+      <c r="L9">
+        <v>-0.2491280460552653</v>
+      </c>
+      <c r="M9">
+        <v>-4.226103451602103</v>
+      </c>
+      <c r="N9">
+        <v>-4.226103451602103</v>
+      </c>
+      <c r="O9">
+        <v>0.25</v>
+      </c>
+      <c r="P9">
+        <v>0.75</v>
+      </c>
+      <c r="Q9">
+        <v>47.91808927995586</v>
+      </c>
+      <c r="R9">
+        <v>52.08191072004414</v>
+      </c>
+      <c r="S9">
+        <v>-0.1868460345414489</v>
+      </c>
+      <c r="T9">
+        <v>-4.163821440088287</v>
+      </c>
+      <c r="U9">
+        <v>-4.163821440088287</v>
+      </c>
+      <c r="V9">
+        <v>21.63743754626992</v>
+      </c>
+      <c r="W9">
+        <v>78.36256245373008</v>
+      </c>
+      <c r="X9" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC9">
+        <v>21.63743754626992</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE9">
+        <v>8.73527450544567</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0.1078756083395196</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM9">
+        <v>-8</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>95</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AP9">
+        <v>0.5322</v>
+      </c>
+      <c r="AQ9">
+        <v>-6.439999999999998</v>
+      </c>
+      <c r="AR9">
+        <v>3.836178559911713</v>
+      </c>
+      <c r="AS9">
+        <v>2.276178559911711</v>
+      </c>
+      <c r="AT9">
+        <v>3.056178559911712</v>
+      </c>
+      <c r="AU9">
+        <v>0.7640446399779279</v>
+      </c>
+      <c r="AV9">
+        <v>5.314982794026658</v>
+      </c>
+      <c r="AW9">
+        <v>4.602075819872517</v>
+      </c>
+      <c r="AX9">
+        <v>5.307634490167654</v>
+      </c>
+      <c r="AY9">
+        <v>0.8436468628413508</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
         <v>-0.3706239798868902</v>
       </c>
-      <c r="BC8">
+      <c r="BC9">
         <v>5.000892084631056</v>
       </c>
-      <c r="BD8">
+      <c r="BD9">
         <v>17.64705882352941</v>
       </c>
-      <c r="BE8">
+      <c r="BE9">
         <v>8.823529411764707</v>
       </c>
-      <c r="BF8">
+      <c r="BF9">
         <v>0.9238036867710117</v>
       </c>
     </row>

--- a/outputs/Block5B_Senate_Competitive_Races.xlsx
+++ b/outputs/Block5B_Senate_Competitive_Races.xlsx
@@ -193,27 +193,27 @@
     <t>Michigan</t>
   </si>
   <si>
+    <t>Alaska</t>
+  </si>
+  <si>
+    <t>Ohio</t>
+  </si>
+  <si>
     <t>Texas</t>
   </si>
   <si>
-    <t>Ohio</t>
-  </si>
-  <si>
-    <t>Alaska</t>
-  </si>
-  <si>
     <t>Maine</t>
   </si>
   <si>
     <t>Iowa</t>
   </si>
   <si>
+    <t>Kansas</t>
+  </si>
+  <si>
     <t>Nebraska</t>
   </si>
   <si>
-    <t>Kansas</t>
-  </si>
-  <si>
     <t>D</t>
   </si>
   <si>
@@ -274,34 +274,34 @@
     <t>D+4</t>
   </si>
   <si>
+    <t>R+8</t>
+  </si>
+  <si>
     <t>R+10</t>
   </si>
   <si>
-    <t>R+8</t>
-  </si>
-  <si>
     <t>49.90% D</t>
   </si>
   <si>
+    <t>53.90% R</t>
+  </si>
+  <si>
+    <t>Appointed (2025)[p]</t>
+  </si>
+  <si>
     <t>53.51% R</t>
   </si>
   <si>
-    <t>Appointed (2025)[p]</t>
-  </si>
-  <si>
-    <t>53.90% R</t>
-  </si>
-  <si>
     <t>50.98% R</t>
   </si>
   <si>
     <t>51.74% R</t>
   </si>
   <si>
+    <t>53.22% R</t>
+  </si>
+  <si>
     <t>62.58% R (2024 sp.)[o]</t>
-  </si>
-  <si>
-    <t>53.22% R</t>
   </si>
 </sst>
 </file>
@@ -846,13 +846,13 @@
         <v>66</v>
       </c>
       <c r="C2">
-        <v>48.175</v>
+        <v>48.825</v>
       </c>
       <c r="D2">
-        <v>45</v>
+        <v>45.275</v>
       </c>
       <c r="E2">
-        <v>3.175</v>
+        <v>3.55</v>
       </c>
       <c r="F2" t="s">
         <v>68</v>
@@ -864,22 +864,22 @@
         <v>75</v>
       </c>
       <c r="I2">
-        <v>51.70378320364904</v>
+        <v>51.88629117959618</v>
       </c>
       <c r="J2">
-        <v>48.29621679635095</v>
+        <v>48.11370882040383</v>
       </c>
       <c r="K2">
-        <v>3.407566407298091</v>
+        <v>3.772582359192349</v>
       </c>
       <c r="L2">
-        <v>2.219283990383333</v>
+        <v>2.784312428859241</v>
       </c>
       <c r="M2">
-        <v>5.626850397681425</v>
+        <v>6.55689478805159</v>
       </c>
       <c r="N2">
-        <v>5.626850397681425</v>
+        <v>6.55689478805159</v>
       </c>
       <c r="O2">
         <v>0.25</v>
@@ -888,25 +888,25 @@
         <v>0.75</v>
       </c>
       <c r="Q2">
-        <v>52.5360147000428</v>
+        <v>52.93040834041839</v>
       </c>
       <c r="R2">
-        <v>47.4639852999572</v>
+        <v>47.06959165958161</v>
       </c>
       <c r="S2">
-        <v>1.664462992787501</v>
+        <v>2.088234321644431</v>
       </c>
       <c r="T2">
-        <v>5.072029400085592</v>
+        <v>5.86081668083678</v>
       </c>
       <c r="U2">
-        <v>5.072029400085592</v>
+        <v>5.86081668083678</v>
       </c>
       <c r="V2">
-        <v>83.72921551043582</v>
+        <v>86.78566705347262</v>
       </c>
       <c r="W2">
-        <v>16.27078448956417</v>
+        <v>13.21433294652739</v>
       </c>
       <c r="X2" t="s">
         <v>72</v>
@@ -924,13 +924,13 @@
         <v>78</v>
       </c>
       <c r="AC2">
-        <v>16.27078448956417</v>
+        <v>13.21433294652739</v>
       </c>
       <c r="AD2" t="s">
         <v>81</v>
       </c>
       <c r="AE2">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF2">
         <v>0</v>
@@ -948,7 +948,7 @@
         <v>-0</v>
       </c>
       <c r="AK2">
-        <v>0.9609781569420333</v>
+        <v>1.205642647732428</v>
       </c>
       <c r="AL2" t="s">
         <v>82</v>
@@ -969,25 +969,25 @@
         <v>-0.2000000000000028</v>
       </c>
       <c r="AR2">
-        <v>5.072029400085592</v>
+        <v>5.86081668083678</v>
       </c>
       <c r="AS2">
-        <v>5.272029400085595</v>
+        <v>6.060816680836782</v>
       </c>
       <c r="AT2">
-        <v>5.172029400085593</v>
+        <v>5.960816680836781</v>
       </c>
       <c r="AU2">
-        <v>1.293007350021398</v>
+        <v>1.490204170209195</v>
       </c>
       <c r="AV2">
         <v>4.890566271054463</v>
       </c>
       <c r="AW2">
-        <v>4.428317085264829</v>
+        <v>4.535644811700211</v>
       </c>
       <c r="AX2">
-        <v>5.157700479575209</v>
+        <v>5.250138654099052</v>
       </c>
       <c r="AY2">
         <v>0.8436468628413508</v>
@@ -1022,13 +1022,13 @@
         <v>67</v>
       </c>
       <c r="C3">
-        <v>48.675</v>
+        <v>50.55</v>
       </c>
       <c r="D3">
-        <v>45.65</v>
+        <v>48.25</v>
       </c>
       <c r="E3">
-        <v>3.025</v>
+        <v>2.3</v>
       </c>
       <c r="F3" t="s">
         <v>69</v>
@@ -1040,22 +1040,22 @@
         <v>75</v>
       </c>
       <c r="I3">
-        <v>51.60349854227405</v>
+        <v>51.16396761133603</v>
       </c>
       <c r="J3">
-        <v>48.39650145772595</v>
+        <v>48.83603238866397</v>
       </c>
       <c r="K3">
-        <v>3.206997084548107</v>
+        <v>2.327935222672068</v>
       </c>
       <c r="L3">
-        <v>-1.2681457739171</v>
+        <v>1.046950541341876</v>
       </c>
       <c r="M3">
-        <v>1.938851310631006</v>
+        <v>3.374885764013944</v>
       </c>
       <c r="N3">
-        <v>1.938851310631006</v>
+        <v>3.374885764013944</v>
       </c>
       <c r="O3">
         <v>0.25</v>
@@ -1064,28 +1064,28 @@
         <v>0.75</v>
       </c>
       <c r="Q3">
-        <v>51.12794387705514</v>
+        <v>51.55657406433924</v>
       </c>
       <c r="R3">
-        <v>48.87205612294486</v>
+        <v>48.44342593566076</v>
       </c>
       <c r="S3">
-        <v>-0.9511093304378253</v>
+        <v>0.7852129060064073</v>
       </c>
       <c r="T3">
-        <v>2.255887754110281</v>
+        <v>3.113148128678475</v>
       </c>
       <c r="U3">
-        <v>2.255887754110281</v>
+        <v>3.113148128678475</v>
       </c>
       <c r="V3">
-        <v>67.08308487070286</v>
+        <v>69.21939506969498</v>
       </c>
       <c r="W3">
-        <v>32.91691512929713</v>
+        <v>30.78060493030502</v>
       </c>
       <c r="X3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="Y3" t="s">
         <v>66</v>
@@ -1100,13 +1100,13 @@
         <v>79</v>
       </c>
       <c r="AC3">
-        <v>67.08308487070286</v>
+        <v>69.21939506969498</v>
       </c>
       <c r="AD3" t="s">
         <v>81</v>
       </c>
       <c r="AE3">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>0.549123227957043</v>
+        <v>0.4533428826539674</v>
       </c>
       <c r="AL3" t="s">
         <v>83</v>
@@ -1139,31 +1139,31 @@
         <v>67</v>
       </c>
       <c r="AP3">
-        <v>0.5351</v>
+        <v>0.539</v>
       </c>
       <c r="AQ3">
-        <v>-7.02000000000001</v>
+        <v>-7.800000000000011</v>
       </c>
       <c r="AR3">
-        <v>8.255887754110281</v>
+        <v>9.113148128678475</v>
       </c>
       <c r="AS3">
-        <v>9.275887754110292</v>
+        <v>10.91314812867849</v>
       </c>
       <c r="AT3">
-        <v>8.765887754110286</v>
+        <v>10.01314812867848</v>
       </c>
       <c r="AU3">
-        <v>2.191471938527572</v>
+        <v>2.50328703216962</v>
       </c>
       <c r="AV3">
-        <v>4.345503062353619</v>
+        <v>5.898436507750732</v>
       </c>
       <c r="AW3">
-        <v>4.362627316035638</v>
+        <v>5.60843385395642</v>
       </c>
       <c r="AX3">
-        <v>5.101411483891715</v>
+        <v>6.200517101304247</v>
       </c>
       <c r="AY3">
         <v>0.8436468628413508</v>
@@ -1172,22 +1172,22 @@
         <v>3</v>
       </c>
       <c r="BA3">
-        <v>1.930645252303767</v>
+        <v>1.541161542643699</v>
       </c>
       <c r="BB3">
-        <v>1.354753062157686</v>
+        <v>-4.006524474852094</v>
       </c>
       <c r="BC3">
-        <v>5.754964092348529</v>
+        <v>11.41694912221213</v>
       </c>
       <c r="BD3">
-        <v>0</v>
+        <v>42.06393827345702</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>23.63541255450272</v>
       </c>
       <c r="BF3">
-        <v>0.9442145399410329</v>
+        <v>0.6873186760847522</v>
       </c>
     </row>
     <row r="4" spans="1:58">
@@ -1198,13 +1198,13 @@
         <v>67</v>
       </c>
       <c r="C4">
-        <v>48.225</v>
+        <v>47.8</v>
       </c>
       <c r="D4">
-        <v>45.1</v>
+        <v>43.7</v>
       </c>
       <c r="E4">
-        <v>3.125</v>
+        <v>4.100000000000001</v>
       </c>
       <c r="F4" t="s">
         <v>69</v>
@@ -1216,22 +1216,22 @@
         <v>75</v>
       </c>
       <c r="I4">
-        <v>51.67425663005626</v>
+        <v>52.24043715846994</v>
       </c>
       <c r="J4">
-        <v>48.32574336994374</v>
+        <v>47.75956284153006</v>
       </c>
       <c r="K4">
-        <v>3.348513260112512</v>
+        <v>4.480874316939889</v>
       </c>
       <c r="L4">
-        <v>-1.794861267366732</v>
+        <v>-2.617231028609809</v>
       </c>
       <c r="M4">
-        <v>1.553651992745779</v>
+        <v>1.86364328833008</v>
       </c>
       <c r="N4">
-        <v>1.553651992745779</v>
+        <v>1.86364328833008</v>
       </c>
       <c r="O4">
         <v>0.25</v>
@@ -1240,25 +1240,25 @@
         <v>0.75</v>
       </c>
       <c r="Q4">
-        <v>51.00118365479373</v>
+        <v>51.25897552274127</v>
       </c>
       <c r="R4">
-        <v>48.99881634520627</v>
+        <v>48.74102447725873</v>
       </c>
       <c r="S4">
-        <v>-1.346145950525049</v>
+        <v>-1.962923271457357</v>
       </c>
       <c r="T4">
-        <v>2.002367309587462</v>
+        <v>2.517951045482532</v>
       </c>
       <c r="U4">
-        <v>2.002367309587462</v>
+        <v>2.517951045482532</v>
       </c>
       <c r="V4">
-        <v>65.26388699510164</v>
+        <v>68.55458229868631</v>
       </c>
       <c r="W4">
-        <v>34.73611300489836</v>
+        <v>31.44541770131368</v>
       </c>
       <c r="X4" t="s">
         <v>76</v>
@@ -1276,13 +1276,13 @@
         <v>79</v>
       </c>
       <c r="AC4">
-        <v>65.26388699510164</v>
+        <v>68.55458229868631</v>
       </c>
       <c r="AD4" t="s">
         <v>81</v>
       </c>
       <c r="AE4">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF4">
         <v>0</v>
@@ -1300,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>0.7771977269041618</v>
+        <v>1.133294279174486</v>
       </c>
       <c r="AL4" t="s">
         <v>84</v>
@@ -1312,22 +1312,22 @@
         <v>90</v>
       </c>
       <c r="AR4">
-        <v>7.002367309587463</v>
+        <v>7.517951045482532</v>
       </c>
       <c r="AT4">
-        <v>7.002367309587463</v>
+        <v>7.517951045482532</v>
       </c>
       <c r="AU4">
-        <v>1.750591827396866</v>
+        <v>1.879487761370633</v>
       </c>
       <c r="AV4">
         <v>4.567515257270437</v>
       </c>
       <c r="AW4">
-        <v>4.363504132448985</v>
+        <v>4.489472846184185</v>
       </c>
       <c r="AX4">
-        <v>5.102161340379323</v>
+        <v>5.210302147283503</v>
       </c>
       <c r="AY4">
         <v>0.8436468628413508</v>
@@ -1362,13 +1362,13 @@
         <v>67</v>
       </c>
       <c r="C5">
-        <v>49.325</v>
+        <v>48.675</v>
       </c>
       <c r="D5">
-        <v>47.475</v>
+        <v>46.1</v>
       </c>
       <c r="E5">
-        <v>1.85</v>
+        <v>2.575</v>
       </c>
       <c r="F5" t="s">
         <v>69</v>
@@ -1380,22 +1380,22 @@
         <v>75</v>
       </c>
       <c r="I5">
-        <v>50.95557851239669</v>
+        <v>51.35848061197573</v>
       </c>
       <c r="J5">
-        <v>49.0444214876033</v>
+        <v>48.64151938802426</v>
       </c>
       <c r="K5">
-        <v>1.91115702479339</v>
+        <v>2.716961223951465</v>
       </c>
       <c r="L5">
-        <v>-0.1172224213495152</v>
+        <v>-1.102239597745279</v>
       </c>
       <c r="M5">
-        <v>1.793934603443875</v>
+        <v>1.614721626206186</v>
       </c>
       <c r="N5">
-        <v>1.793934603443875</v>
+        <v>1.614721626206186</v>
       </c>
       <c r="O5">
         <v>0.25</v>
@@ -1404,25 +1404,25 @@
         <v>0.75</v>
       </c>
       <c r="Q5">
-        <v>50.91162010439063</v>
+        <v>50.94514076282125</v>
       </c>
       <c r="R5">
-        <v>49.08837989560937</v>
+        <v>49.05485923717875</v>
       </c>
       <c r="S5">
-        <v>-0.08791681601213641</v>
+        <v>-0.8266796983089593</v>
       </c>
       <c r="T5">
-        <v>1.823240208781253</v>
+        <v>1.890281525642506</v>
       </c>
       <c r="U5">
-        <v>1.823240208781253</v>
+        <v>1.890281525642506</v>
       </c>
       <c r="V5">
-        <v>61.79014903031504</v>
+        <v>64.5725196739622</v>
       </c>
       <c r="W5">
-        <v>38.20985096968496</v>
+        <v>35.4274803260378</v>
       </c>
       <c r="X5" t="s">
         <v>76</v>
@@ -1440,13 +1440,13 @@
         <v>79</v>
       </c>
       <c r="AC5">
-        <v>61.79014903031504</v>
+        <v>64.5725196739622</v>
       </c>
       <c r="AD5" t="s">
         <v>81</v>
       </c>
       <c r="AE5">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="AK5">
-        <v>0.05075879739090176</v>
+        <v>0.4772837463522762</v>
       </c>
       <c r="AL5" t="s">
         <v>83</v>
@@ -1479,31 +1479,31 @@
         <v>67</v>
       </c>
       <c r="AP5">
-        <v>0.539</v>
+        <v>0.5351</v>
       </c>
       <c r="AQ5">
-        <v>-7.800000000000011</v>
+        <v>-7.02000000000001</v>
       </c>
       <c r="AR5">
-        <v>7.823240208781254</v>
+        <v>7.890281525642505</v>
       </c>
       <c r="AS5">
-        <v>9.623240208781265</v>
+        <v>8.910281525642516</v>
       </c>
       <c r="AT5">
-        <v>8.723240208781259</v>
+        <v>8.400281525642511</v>
       </c>
       <c r="AU5">
-        <v>2.180810052195315</v>
+        <v>2.100070381410628</v>
       </c>
       <c r="AV5">
-        <v>5.898436507750732</v>
+        <v>4.345503062353619</v>
       </c>
       <c r="AW5">
-        <v>5.472672171724974</v>
+        <v>4.310457345837744</v>
       </c>
       <c r="AX5">
-        <v>6.077994959568073</v>
+        <v>5.056869047112899</v>
       </c>
       <c r="AY5">
         <v>0.8436468628413508</v>
@@ -1512,22 +1512,22 @@
         <v>3</v>
       </c>
       <c r="BA5">
-        <v>1.541161542643699</v>
+        <v>1.930645252303767</v>
       </c>
       <c r="BB5">
-        <v>-4.006524474852094</v>
+        <v>1.354753062157686</v>
       </c>
       <c r="BC5">
-        <v>11.41694912221213</v>
+        <v>5.754964092348529</v>
       </c>
       <c r="BD5">
-        <v>42.06393827345702</v>
+        <v>0</v>
       </c>
       <c r="BE5">
-        <v>23.63541255450272</v>
+        <v>0</v>
       </c>
       <c r="BF5">
-        <v>0.6873186760847522</v>
+        <v>0.9442145399410329</v>
       </c>
     </row>
     <row r="6" spans="1:58">
@@ -1538,13 +1538,13 @@
         <v>67</v>
       </c>
       <c r="C6">
-        <v>48.25</v>
+        <v>48.825</v>
       </c>
       <c r="D6">
-        <v>46.575</v>
+        <v>47.5</v>
       </c>
       <c r="E6">
-        <v>1.675</v>
+        <v>1.325</v>
       </c>
       <c r="F6" t="s">
         <v>69</v>
@@ -1556,22 +1556,22 @@
         <v>75</v>
       </c>
       <c r="I6">
-        <v>50.8832059056156</v>
+        <v>50.68777575914871</v>
       </c>
       <c r="J6">
-        <v>49.11679409438439</v>
+        <v>49.31222424085129</v>
       </c>
       <c r="K6">
-        <v>1.766411811231215</v>
+        <v>1.375551518297428</v>
       </c>
       <c r="L6">
-        <v>-1.225993544904167</v>
+        <v>-0.4670255429338032</v>
       </c>
       <c r="M6">
-        <v>0.5404182663270487</v>
+        <v>0.9085259753636247</v>
       </c>
       <c r="N6">
-        <v>0.5404182663270487</v>
+        <v>0.9085259753636247</v>
       </c>
       <c r="O6">
         <v>0.25</v>
@@ -1580,28 +1580,28 @@
         <v>0.75</v>
       </c>
       <c r="Q6">
-        <v>50.42345832627655</v>
+        <v>50.51264118054853</v>
       </c>
       <c r="R6">
-        <v>49.57654167372345</v>
+        <v>49.48735881945147</v>
       </c>
       <c r="S6">
-        <v>-0.9194951586781249</v>
+        <v>-0.3502691572003522</v>
       </c>
       <c r="T6">
-        <v>0.8469166525530903</v>
+        <v>1.025282361097076</v>
       </c>
       <c r="U6">
-        <v>0.8469166525530903</v>
+        <v>1.025282361097076</v>
       </c>
       <c r="V6">
-        <v>55.65418073718285</v>
+        <v>56.86396059822987</v>
       </c>
       <c r="W6">
-        <v>44.34581926281715</v>
+        <v>43.13603940177013</v>
       </c>
       <c r="X6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="Y6" t="s">
         <v>66</v>
@@ -1616,13 +1616,13 @@
         <v>79</v>
       </c>
       <c r="AC6">
-        <v>55.65418073718285</v>
+        <v>56.86396059822987</v>
       </c>
       <c r="AD6" t="s">
         <v>81</v>
       </c>
       <c r="AE6">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="AK6">
-        <v>0.530870777381373</v>
+        <v>0.2022279921984468</v>
       </c>
       <c r="AL6" t="s">
         <v>85</v>
@@ -1661,10 +1661,10 @@
         <v>-1.95999999999998</v>
       </c>
       <c r="AR6">
-        <v>3.15308334744691</v>
+        <v>2.974717638902924</v>
       </c>
       <c r="AS6">
-        <v>2.80691665255307</v>
+        <v>2.985282361097055</v>
       </c>
       <c r="AT6">
         <v>2.97999999999999</v>
@@ -1676,10 +1676,10 @@
         <v>6.166256775636249</v>
       </c>
       <c r="AW6">
-        <v>5.33631557212084</v>
+        <v>5.307280945654573</v>
       </c>
       <c r="AX6">
-        <v>5.955513908523875</v>
+        <v>5.929512042779748</v>
       </c>
       <c r="AY6">
         <v>0.8436468628413508</v>
@@ -1714,13 +1714,13 @@
         <v>67</v>
       </c>
       <c r="C7">
-        <v>46.075</v>
+        <v>47.025</v>
       </c>
       <c r="D7">
-        <v>46.2</v>
+        <v>46.55</v>
       </c>
       <c r="E7">
-        <v>-0.125</v>
+        <v>0.475</v>
       </c>
       <c r="F7" t="s">
         <v>70</v>
@@ -1732,22 +1732,22 @@
         <v>73</v>
       </c>
       <c r="I7">
-        <v>49.932267678136</v>
+        <v>50.25380710659898</v>
       </c>
       <c r="J7">
-        <v>50.06773232186399</v>
+        <v>49.74619289340102</v>
       </c>
       <c r="K7">
-        <v>-0.1354646437279925</v>
+        <v>0.507614213197968</v>
       </c>
       <c r="L7">
-        <v>-2.883221219172162</v>
+        <v>-2.118496098593954</v>
       </c>
       <c r="M7">
-        <v>-3.018685862900155</v>
+        <v>-1.610881885395986</v>
       </c>
       <c r="N7">
-        <v>-3.018685862900155</v>
+        <v>-1.610881885395986</v>
       </c>
       <c r="O7">
         <v>0.25</v>
@@ -1756,25 +1756,25 @@
         <v>0.75</v>
       </c>
       <c r="Q7">
-        <v>48.85105972094644</v>
+        <v>49.45937106962625</v>
       </c>
       <c r="R7">
-        <v>51.14894027905356</v>
+        <v>50.54062893037375</v>
       </c>
       <c r="S7">
-        <v>-2.162415914379122</v>
+        <v>-1.588872073945465</v>
       </c>
       <c r="T7">
-        <v>-2.297880558107114</v>
+        <v>-1.081257860747497</v>
       </c>
       <c r="U7">
-        <v>-2.297880558107114</v>
+        <v>-1.081257860747497</v>
       </c>
       <c r="V7">
-        <v>34.57168958828296</v>
+        <v>42.55353044592097</v>
       </c>
       <c r="W7">
-        <v>65.42831041171704</v>
+        <v>57.44646955407903</v>
       </c>
       <c r="X7" t="s">
         <v>77</v>
@@ -1786,19 +1786,19 @@
         <v>80</v>
       </c>
       <c r="AA7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AB7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC7">
-        <v>34.57168958828296</v>
+        <v>42.55353044592097</v>
       </c>
       <c r="AD7" t="s">
         <v>81</v>
       </c>
       <c r="AE7">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF7">
         <v>0</v>
@@ -1816,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="AK7">
-        <v>1.248471410266716</v>
+        <v>0.9173357196002934</v>
       </c>
       <c r="AL7" t="s">
         <v>83</v>
@@ -1837,25 +1837,25 @@
         <v>-3.47999999999999</v>
       </c>
       <c r="AR7">
-        <v>3.702119441892886</v>
+        <v>4.918742139252503</v>
       </c>
       <c r="AS7">
-        <v>1.182119441892876</v>
+        <v>2.398742139252493</v>
       </c>
       <c r="AT7">
-        <v>2.442119441892881</v>
+        <v>3.658742139252498</v>
       </c>
       <c r="AU7">
-        <v>0.6105298604732202</v>
+        <v>0.9146855348131244</v>
       </c>
       <c r="AV7">
         <v>5.775280601260435</v>
       </c>
       <c r="AW7">
-        <v>5.150295879788892</v>
+        <v>5.116017109818188</v>
       </c>
       <c r="AX7">
-        <v>5.789423950509446</v>
+        <v>5.758950694120796</v>
       </c>
       <c r="AY7">
         <v>0.8436468628413508</v>
@@ -1890,13 +1890,13 @@
         <v>67</v>
       </c>
       <c r="C8">
-        <v>47.3</v>
+        <v>46.025</v>
       </c>
       <c r="D8">
-        <v>50.16666667000001</v>
+        <v>49.52500000000001</v>
       </c>
       <c r="E8">
-        <v>-2.866666667</v>
+        <v>-3.5</v>
       </c>
       <c r="F8" t="s">
         <v>71</v>
@@ -1908,22 +1908,22 @@
         <v>75</v>
       </c>
       <c r="I8">
-        <v>48.52941176304619</v>
+        <v>48.16849816849816</v>
       </c>
       <c r="J8">
-        <v>51.47058823695382</v>
+        <v>51.83150183150183</v>
       </c>
       <c r="K8">
-        <v>-2.941176473907625</v>
+        <v>-3.663003663003671</v>
       </c>
       <c r="L8">
-        <v>0.5792673114617315</v>
+        <v>-0.319579423669317</v>
       </c>
       <c r="M8">
-        <v>-2.361909162445893</v>
+        <v>-3.982583086672988</v>
       </c>
       <c r="N8">
-        <v>-2.361909162445893</v>
+        <v>-3.982583086672988</v>
       </c>
       <c r="O8">
         <v>0.25</v>
@@ -1932,28 +1932,28 @@
         <v>0.75</v>
       </c>
       <c r="Q8">
-        <v>48.74663700484434</v>
+        <v>48.04865588462217</v>
       </c>
       <c r="R8">
-        <v>51.25336299515566</v>
+        <v>51.95134411537783</v>
       </c>
       <c r="S8">
-        <v>0.434450483596299</v>
+        <v>-0.2396845677519877</v>
       </c>
       <c r="T8">
-        <v>-2.506725990311326</v>
+        <v>-3.902688230755659</v>
       </c>
       <c r="U8">
-        <v>-2.506725990311326</v>
+        <v>-3.902688230755659</v>
       </c>
       <c r="V8">
-        <v>33.66396774649345</v>
+        <v>23.15815969257593</v>
       </c>
       <c r="W8">
-        <v>66.33603225350654</v>
+        <v>76.84184030742406</v>
       </c>
       <c r="X8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Y8" t="s">
         <v>67</v>
@@ -1968,13 +1968,13 @@
         <v>80</v>
       </c>
       <c r="AC8">
-        <v>33.66396774649345</v>
+        <v>23.15815969257593</v>
       </c>
       <c r="AD8" t="s">
         <v>81</v>
       </c>
       <c r="AE8">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="AK8">
-        <v>0.2508301036538862</v>
+        <v>0.1383819497122092</v>
       </c>
       <c r="AL8" t="s">
         <v>86</v>
       </c>
       <c r="AM8">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="AN8" t="s">
         <v>94</v>
@@ -2007,55 +2007,55 @@
         <v>67</v>
       </c>
       <c r="AP8">
-        <v>0.6258</v>
+        <v>0.5322</v>
       </c>
       <c r="AQ8">
-        <v>-25.16000000000001</v>
+        <v>-6.439999999999998</v>
       </c>
       <c r="AR8">
-        <v>7.493274009688674</v>
+        <v>4.097311769244341</v>
       </c>
       <c r="AS8">
-        <v>22.65327400968869</v>
+        <v>2.537311769244339</v>
       </c>
       <c r="AT8">
-        <v>15.07327400968868</v>
+        <v>3.317311769244339</v>
       </c>
       <c r="AU8">
-        <v>3.76831850242217</v>
+        <v>0.8293279423110849</v>
       </c>
       <c r="AV8">
-        <v>4.390437171606355</v>
+        <v>5.314982794026658</v>
       </c>
       <c r="AW8">
-        <v>5.324598663427484</v>
+        <v>4.615828922128182</v>
       </c>
       <c r="AX8">
-        <v>5.945017489960455</v>
+        <v>5.319563766674573</v>
       </c>
       <c r="AY8">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA8">
-        <v>1.906296723190152</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>-1.372324784465838</v>
+        <v>-0.3706239798868902</v>
       </c>
       <c r="BC8">
-        <v>5.414780435479317</v>
+        <v>5.000892084631056</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>8.823529411764707</v>
       </c>
       <c r="BF8">
-        <v>0.9325238981752073</v>
+        <v>0.9238036867710117</v>
       </c>
     </row>
     <row r="9" spans="1:58">
@@ -2066,13 +2066,13 @@
         <v>67</v>
       </c>
       <c r="C9">
-        <v>45.875</v>
+        <v>46.3</v>
       </c>
       <c r="D9">
-        <v>49.675</v>
+        <v>51.16666667000001</v>
       </c>
       <c r="E9">
-        <v>-3.8</v>
+        <v>-4.866666667</v>
       </c>
       <c r="F9" t="s">
         <v>71</v>
@@ -2084,22 +2084,22 @@
         <v>75</v>
       </c>
       <c r="I9">
-        <v>48.01151229722657</v>
+        <v>47.50341997101561</v>
       </c>
       <c r="J9">
-        <v>51.98848770277341</v>
+        <v>52.49658002898438</v>
       </c>
       <c r="K9">
-        <v>-3.976975405546838</v>
+        <v>-4.993160057968772</v>
       </c>
       <c r="L9">
-        <v>-0.2491280460552653</v>
+        <v>1.022628397888314</v>
       </c>
       <c r="M9">
-        <v>-4.226103451602103</v>
+        <v>-3.970531660080458</v>
       </c>
       <c r="N9">
-        <v>-4.226103451602103</v>
+        <v>-3.970531660080458</v>
       </c>
       <c r="O9">
         <v>0.25</v>
@@ -2108,25 +2108,25 @@
         <v>0.75</v>
       </c>
       <c r="Q9">
-        <v>47.91808927995586</v>
+        <v>47.88690562022373</v>
       </c>
       <c r="R9">
-        <v>52.08191072004414</v>
+        <v>52.11309437977627</v>
       </c>
       <c r="S9">
-        <v>-0.1868460345414489</v>
+        <v>0.7669712984162356</v>
       </c>
       <c r="T9">
-        <v>-4.163821440088287</v>
+        <v>-4.226188759552537</v>
       </c>
       <c r="U9">
-        <v>-4.163821440088287</v>
+        <v>-4.226188759552537</v>
       </c>
       <c r="V9">
-        <v>21.63743754626992</v>
+        <v>22.86059118815288</v>
       </c>
       <c r="W9">
-        <v>78.36256245373008</v>
+        <v>77.13940881184712</v>
       </c>
       <c r="X9" t="s">
         <v>74</v>
@@ -2144,13 +2144,13 @@
         <v>80</v>
       </c>
       <c r="AC9">
-        <v>21.63743754626992</v>
+        <v>22.86059118815288</v>
       </c>
       <c r="AD9" t="s">
         <v>81</v>
       </c>
       <c r="AE9">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF9">
         <v>0</v>
@@ -2168,13 +2168,13 @@
         <v>0</v>
       </c>
       <c r="AK9">
-        <v>0.1078756083395196</v>
+        <v>0.4428110856013305</v>
       </c>
       <c r="AL9" t="s">
         <v>87</v>
       </c>
       <c r="AM9">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="AN9" t="s">
         <v>95</v>
@@ -2183,55 +2183,55 @@
         <v>67</v>
       </c>
       <c r="AP9">
-        <v>0.5322</v>
+        <v>0.6258</v>
       </c>
       <c r="AQ9">
-        <v>-6.439999999999998</v>
+        <v>-25.16000000000001</v>
       </c>
       <c r="AR9">
-        <v>3.836178559911713</v>
+        <v>5.773811240447463</v>
       </c>
       <c r="AS9">
-        <v>2.276178559911711</v>
+        <v>20.93381124044748</v>
       </c>
       <c r="AT9">
-        <v>3.056178559911712</v>
+        <v>13.35381124044747</v>
       </c>
       <c r="AU9">
-        <v>0.7640446399779279</v>
+        <v>3.338452810111868</v>
       </c>
       <c r="AV9">
-        <v>5.314982794026658</v>
+        <v>4.390437171606355</v>
       </c>
       <c r="AW9">
-        <v>4.602075819872517</v>
+        <v>5.032171060126636</v>
       </c>
       <c r="AX9">
-        <v>5.307634490167654</v>
+        <v>5.684595641533177</v>
       </c>
       <c r="AY9">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.906296723190152</v>
       </c>
       <c r="BB9">
-        <v>-0.3706239798868902</v>
+        <v>-1.372324784465838</v>
       </c>
       <c r="BC9">
-        <v>5.000892084631056</v>
+        <v>5.414780435479317</v>
       </c>
       <c r="BD9">
-        <v>17.64705882352941</v>
+        <v>0</v>
       </c>
       <c r="BE9">
-        <v>8.823529411764707</v>
+        <v>0</v>
       </c>
       <c r="BF9">
-        <v>0.9238036867710117</v>
+        <v>0.9325238981752073</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block5B_Senate_Competitive_Races.xlsx
+++ b/outputs/Block5B_Senate_Competitive_Races.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="99">
   <si>
     <t>STATE</t>
   </si>
@@ -193,15 +193,15 @@
     <t>Michigan</t>
   </si>
   <si>
+    <t>Ohio</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
     <t>Alaska</t>
   </si>
   <si>
-    <t>Ohio</t>
-  </si>
-  <si>
-    <t>Texas</t>
-  </si>
-  <si>
     <t>Maine</t>
   </si>
   <si>
@@ -232,6 +232,9 @@
     <t>RSenLeanPollH (&gt;1&lt;=5%)</t>
   </si>
   <si>
+    <t>RSenLikPollH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
     <t>D Lean</t>
   </si>
   <si>
@@ -241,9 +244,15 @@
     <t>R Lean</t>
   </si>
   <si>
+    <t>R Likely</t>
+  </si>
+  <si>
     <t>Lean</t>
   </si>
   <si>
+    <t>Likely</t>
+  </si>
+  <si>
     <t>D Tilt</t>
   </si>
   <si>
@@ -265,12 +274,12 @@
     <t>EVEN</t>
   </si>
   <si>
+    <t>R+5</t>
+  </si>
+  <si>
     <t>R+6</t>
   </si>
   <si>
-    <t>R+5</t>
-  </si>
-  <si>
     <t>D+4</t>
   </si>
   <si>
@@ -283,13 +292,13 @@
     <t>49.90% D</t>
   </si>
   <si>
+    <t>Appointed (2025)[p]</t>
+  </si>
+  <si>
+    <t>53.51% R</t>
+  </si>
+  <si>
     <t>53.90% R</t>
-  </si>
-  <si>
-    <t>Appointed (2025)[p]</t>
-  </si>
-  <si>
-    <t>53.51% R</t>
   </si>
   <si>
     <t>50.98% R</t>
@@ -846,40 +855,40 @@
         <v>66</v>
       </c>
       <c r="C2">
-        <v>48.825</v>
+        <v>48.725</v>
       </c>
       <c r="D2">
-        <v>45.275</v>
+        <v>45.05</v>
       </c>
       <c r="E2">
-        <v>3.55</v>
+        <v>3.675</v>
       </c>
       <c r="F2" t="s">
         <v>68</v>
       </c>
       <c r="G2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I2">
-        <v>51.88629117959618</v>
+        <v>51.95947747267395</v>
       </c>
       <c r="J2">
-        <v>48.11370882040383</v>
+        <v>48.04052252732605</v>
       </c>
       <c r="K2">
-        <v>3.772582359192349</v>
+        <v>3.918954945347906</v>
       </c>
       <c r="L2">
-        <v>2.784312428859241</v>
+        <v>2.590328418627033</v>
       </c>
       <c r="M2">
-        <v>6.55689478805159</v>
+        <v>6.509283363974939</v>
       </c>
       <c r="N2">
-        <v>6.55689478805159</v>
+        <v>6.509283363974939</v>
       </c>
       <c r="O2">
         <v>0.25</v>
@@ -888,49 +897,49 @@
         <v>0.75</v>
       </c>
       <c r="Q2">
-        <v>52.93040834041839</v>
+        <v>52.93085062965909</v>
       </c>
       <c r="R2">
-        <v>47.06959165958161</v>
+        <v>47.06914937034091</v>
       </c>
       <c r="S2">
-        <v>2.088234321644431</v>
+        <v>1.942746313970275</v>
       </c>
       <c r="T2">
-        <v>5.86081668083678</v>
+        <v>5.861701259318181</v>
       </c>
       <c r="U2">
-        <v>5.86081668083678</v>
+        <v>5.861701259318181</v>
       </c>
       <c r="V2">
-        <v>86.78566705347262</v>
+        <v>86.85847000210781</v>
       </c>
       <c r="W2">
-        <v>13.21433294652739</v>
+        <v>13.1415299978922</v>
       </c>
       <c r="X2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Y2" t="s">
         <v>66</v>
       </c>
       <c r="Z2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="AA2" t="s">
         <v>66</v>
       </c>
       <c r="AB2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="AC2">
-        <v>13.21433294652739</v>
+        <v>13.1415299978922</v>
       </c>
       <c r="AD2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AE2">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF2">
         <v>0</v>
@@ -948,16 +957,16 @@
         <v>-0</v>
       </c>
       <c r="AK2">
-        <v>1.205642647732428</v>
+        <v>1.121645107337891</v>
       </c>
       <c r="AL2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AM2">
         <v>0</v>
       </c>
       <c r="AN2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AO2" t="s">
         <v>66</v>
@@ -969,25 +978,25 @@
         <v>-0.2000000000000028</v>
       </c>
       <c r="AR2">
-        <v>5.86081668083678</v>
+        <v>5.861701259318181</v>
       </c>
       <c r="AS2">
-        <v>6.060816680836782</v>
+        <v>6.061701259318184</v>
       </c>
       <c r="AT2">
-        <v>5.960816680836781</v>
+        <v>5.961701259318183</v>
       </c>
       <c r="AU2">
-        <v>1.490204170209195</v>
+        <v>1.490425314829546</v>
       </c>
       <c r="AV2">
         <v>4.890566271054463</v>
       </c>
       <c r="AW2">
-        <v>4.535644811700211</v>
+        <v>4.518046915456435</v>
       </c>
       <c r="AX2">
-        <v>5.250138654099052</v>
+        <v>5.234943166800129</v>
       </c>
       <c r="AY2">
         <v>0.8436468628413508</v>
@@ -1022,40 +1031,40 @@
         <v>67</v>
       </c>
       <c r="C3">
-        <v>50.55</v>
+        <v>47.825</v>
       </c>
       <c r="D3">
-        <v>48.25</v>
+        <v>43.7</v>
       </c>
       <c r="E3">
-        <v>2.3</v>
+        <v>4.125</v>
       </c>
       <c r="F3" t="s">
         <v>69</v>
       </c>
       <c r="G3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I3">
-        <v>51.16396761133603</v>
+        <v>52.25348265501229</v>
       </c>
       <c r="J3">
-        <v>48.83603238866397</v>
+        <v>47.74651734498771</v>
       </c>
       <c r="K3">
-        <v>2.327935222672068</v>
+        <v>4.506965310024583</v>
       </c>
       <c r="L3">
-        <v>1.046950541341876</v>
+        <v>-2.638289777369295</v>
       </c>
       <c r="M3">
-        <v>3.374885764013944</v>
+        <v>1.868675532655288</v>
       </c>
       <c r="N3">
-        <v>3.374885764013944</v>
+        <v>1.868675532655288</v>
       </c>
       <c r="O3">
         <v>0.25</v>
@@ -1064,49 +1073,49 @@
         <v>0.75</v>
       </c>
       <c r="Q3">
-        <v>51.55657406433924</v>
+        <v>51.26412398849881</v>
       </c>
       <c r="R3">
-        <v>48.44342593566076</v>
+        <v>48.73587601150119</v>
       </c>
       <c r="S3">
-        <v>0.7852129060064073</v>
+        <v>-1.978717333026971</v>
       </c>
       <c r="T3">
-        <v>3.113148128678475</v>
+        <v>2.528247976997612</v>
       </c>
       <c r="U3">
-        <v>3.113148128678475</v>
+        <v>2.528247976997612</v>
       </c>
       <c r="V3">
-        <v>69.21939506969498</v>
+        <v>68.62056620003455</v>
       </c>
       <c r="W3">
-        <v>30.78060493030502</v>
+        <v>31.37943379996545</v>
       </c>
       <c r="X3" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="Y3" t="s">
         <v>66</v>
       </c>
       <c r="Z3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA3" t="s">
         <v>66</v>
       </c>
       <c r="AB3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AC3">
-        <v>69.21939506969498</v>
+        <v>68.62056620003455</v>
       </c>
       <c r="AD3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AE3">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -1124,70 +1133,58 @@
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>0.4533428826539674</v>
+        <v>1.1424129848733</v>
       </c>
       <c r="AL3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AM3">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="AN3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AP3">
-        <v>0.539</v>
-      </c>
-      <c r="AQ3">
-        <v>-7.800000000000011</v>
+        <v>92</v>
       </c>
       <c r="AR3">
-        <v>9.113148128678475</v>
-      </c>
-      <c r="AS3">
-        <v>10.91314812867849</v>
+        <v>7.528247976997612</v>
       </c>
       <c r="AT3">
-        <v>10.01314812867848</v>
+        <v>7.528247976997612</v>
       </c>
       <c r="AU3">
-        <v>2.50328703216962</v>
+        <v>1.882061994249403</v>
       </c>
       <c r="AV3">
-        <v>5.898436507750732</v>
+        <v>4.567515257270437</v>
       </c>
       <c r="AW3">
-        <v>5.60843385395642</v>
+        <v>4.490926033506978</v>
       </c>
       <c r="AX3">
-        <v>6.200517101304247</v>
+        <v>5.211554342784182</v>
       </c>
       <c r="AY3">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA3">
-        <v>1.541161542643699</v>
+        <v>2.797261014127842</v>
       </c>
       <c r="BB3">
-        <v>-4.006524474852094</v>
+        <v>0.1730167113317724</v>
       </c>
       <c r="BC3">
-        <v>11.41694912221213</v>
+        <v>2.956526743070407</v>
       </c>
       <c r="BD3">
-        <v>42.06393827345702</v>
+        <v>17.4915896825486</v>
       </c>
       <c r="BE3">
-        <v>23.63541255450272</v>
+        <v>0</v>
       </c>
       <c r="BF3">
-        <v>0.6873186760847522</v>
+        <v>0.956231216651788</v>
       </c>
     </row>
     <row r="4" spans="1:58">
@@ -1198,40 +1195,40 @@
         <v>67</v>
       </c>
       <c r="C4">
-        <v>47.8</v>
+        <v>48.9</v>
       </c>
       <c r="D4">
-        <v>43.7</v>
+        <v>46.175</v>
       </c>
       <c r="E4">
-        <v>4.100000000000001</v>
+        <v>2.725</v>
       </c>
       <c r="F4" t="s">
         <v>69</v>
       </c>
       <c r="G4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I4">
-        <v>52.24043715846994</v>
+        <v>51.43307914804102</v>
       </c>
       <c r="J4">
-        <v>47.75956284153006</v>
+        <v>48.56692085195898</v>
       </c>
       <c r="K4">
-        <v>4.480874316939889</v>
+        <v>2.866158296082041</v>
       </c>
       <c r="L4">
-        <v>-2.617231028609809</v>
+        <v>-0.9522874185159853</v>
       </c>
       <c r="M4">
-        <v>1.86364328833008</v>
+        <v>1.913870877566056</v>
       </c>
       <c r="N4">
-        <v>1.86364328833008</v>
+        <v>1.913870877566056</v>
       </c>
       <c r="O4">
         <v>0.25</v>
@@ -1240,49 +1237,49 @@
         <v>0.75</v>
       </c>
       <c r="Q4">
-        <v>51.25897552274127</v>
+        <v>51.07597136609753</v>
       </c>
       <c r="R4">
-        <v>48.74102447725873</v>
+        <v>48.92402863390247</v>
       </c>
       <c r="S4">
-        <v>-1.962923271457357</v>
+        <v>-0.7142155638869889</v>
       </c>
       <c r="T4">
-        <v>2.517951045482532</v>
+        <v>2.151942732195052</v>
       </c>
       <c r="U4">
-        <v>2.517951045482532</v>
+        <v>2.151942732195052</v>
       </c>
       <c r="V4">
-        <v>68.55458229868631</v>
+        <v>66.42247604555808</v>
       </c>
       <c r="W4">
-        <v>31.44541770131368</v>
+        <v>33.57752395444192</v>
       </c>
       <c r="X4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Y4" t="s">
         <v>66</v>
       </c>
       <c r="Z4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA4" t="s">
         <v>66</v>
       </c>
       <c r="AB4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AC4">
-        <v>68.55458229868631</v>
+        <v>66.42247604555808</v>
       </c>
       <c r="AD4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AE4">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF4">
         <v>0</v>
@@ -1300,58 +1297,70 @@
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.133294279174486</v>
+        <v>0.4123525480695734</v>
       </c>
       <c r="AL4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AM4">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="AN4" t="s">
-        <v>90</v>
+        <v>93</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AP4">
+        <v>0.5351</v>
+      </c>
+      <c r="AQ4">
+        <v>-7.02000000000001</v>
       </c>
       <c r="AR4">
-        <v>7.517951045482532</v>
+        <v>8.151942732195053</v>
+      </c>
+      <c r="AS4">
+        <v>9.171942732195063</v>
       </c>
       <c r="AT4">
-        <v>7.517951045482532</v>
+        <v>8.661942732195058</v>
       </c>
       <c r="AU4">
-        <v>1.879487761370633</v>
+        <v>2.165485683048765</v>
       </c>
       <c r="AV4">
-        <v>4.567515257270437</v>
+        <v>4.345503062353619</v>
       </c>
       <c r="AW4">
-        <v>4.489472846184185</v>
+        <v>4.331813166230072</v>
       </c>
       <c r="AX4">
-        <v>5.210302147283503</v>
+        <v>5.075084958548591</v>
       </c>
       <c r="AY4">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA4">
-        <v>2.797261014127842</v>
+        <v>1.930645252303767</v>
       </c>
       <c r="BB4">
-        <v>0.1730167113317724</v>
+        <v>1.354753062157686</v>
       </c>
       <c r="BC4">
-        <v>2.956526743070407</v>
+        <v>5.754964092348529</v>
       </c>
       <c r="BD4">
-        <v>17.4915896825486</v>
+        <v>0</v>
       </c>
       <c r="BE4">
         <v>0</v>
       </c>
       <c r="BF4">
-        <v>0.956231216651788</v>
+        <v>0.9442145399410329</v>
       </c>
     </row>
     <row r="5" spans="1:58">
@@ -1362,40 +1371,40 @@
         <v>67</v>
       </c>
       <c r="C5">
-        <v>48.675</v>
+        <v>49.475</v>
       </c>
       <c r="D5">
-        <v>46.1</v>
+        <v>46.775</v>
       </c>
       <c r="E5">
-        <v>2.575</v>
+        <v>2.7</v>
       </c>
       <c r="F5" t="s">
         <v>69</v>
       </c>
       <c r="G5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I5">
-        <v>51.35848061197573</v>
+        <v>51.4025974025974</v>
       </c>
       <c r="J5">
-        <v>48.64151938802426</v>
+        <v>48.5974025974026</v>
       </c>
       <c r="K5">
-        <v>2.716961223951465</v>
+        <v>2.805194805194802</v>
       </c>
       <c r="L5">
-        <v>-1.102239597745279</v>
+        <v>-0.3163895128283701</v>
       </c>
       <c r="M5">
-        <v>1.614721626206186</v>
+        <v>2.488805292366432</v>
       </c>
       <c r="N5">
-        <v>1.614721626206186</v>
+        <v>2.488805292366432</v>
       </c>
       <c r="O5">
         <v>0.25</v>
@@ -1404,49 +1413,49 @@
         <v>0.75</v>
       </c>
       <c r="Q5">
-        <v>50.94514076282125</v>
+        <v>51.28395133528676</v>
       </c>
       <c r="R5">
-        <v>49.05485923717875</v>
+        <v>48.71604866471324</v>
       </c>
       <c r="S5">
-        <v>-0.8266796983089593</v>
+        <v>-0.2372921346212777</v>
       </c>
       <c r="T5">
-        <v>1.890281525642506</v>
+        <v>2.567902670573524</v>
       </c>
       <c r="U5">
-        <v>1.890281525642506</v>
+        <v>2.567902670573524</v>
       </c>
       <c r="V5">
-        <v>64.5725196739622</v>
+        <v>66.19625489789294</v>
       </c>
       <c r="W5">
-        <v>35.4274803260378</v>
+        <v>33.80374510210705</v>
       </c>
       <c r="X5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Y5" t="s">
         <v>66</v>
       </c>
       <c r="Z5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA5" t="s">
         <v>66</v>
       </c>
       <c r="AB5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AC5">
-        <v>64.5725196739622</v>
+        <v>66.19625489789294</v>
       </c>
       <c r="AD5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AE5">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -1464,46 +1473,46 @@
         <v>0</v>
       </c>
       <c r="AK5">
-        <v>0.4772837463522762</v>
+        <v>0.1370006778001755</v>
       </c>
       <c r="AL5" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AM5">
         <v>-6</v>
       </c>
       <c r="AN5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AO5" t="s">
         <v>67</v>
       </c>
       <c r="AP5">
-        <v>0.5351</v>
+        <v>0.539</v>
       </c>
       <c r="AQ5">
-        <v>-7.02000000000001</v>
+        <v>-7.800000000000011</v>
       </c>
       <c r="AR5">
-        <v>7.890281525642505</v>
+        <v>8.567902670573524</v>
       </c>
       <c r="AS5">
-        <v>8.910281525642516</v>
+        <v>10.36790267057354</v>
       </c>
       <c r="AT5">
-        <v>8.400281525642511</v>
+        <v>9.46790267057353</v>
       </c>
       <c r="AU5">
-        <v>2.100070381410628</v>
+        <v>2.366975667643382</v>
       </c>
       <c r="AV5">
-        <v>4.345503062353619</v>
+        <v>5.898436507750732</v>
       </c>
       <c r="AW5">
-        <v>4.310457345837744</v>
+        <v>5.547966090444774</v>
       </c>
       <c r="AX5">
-        <v>5.056869047112899</v>
+        <v>6.145877461362781</v>
       </c>
       <c r="AY5">
         <v>0.8436468628413508</v>
@@ -1512,22 +1521,22 @@
         <v>3</v>
       </c>
       <c r="BA5">
-        <v>1.930645252303767</v>
+        <v>1.541161542643699</v>
       </c>
       <c r="BB5">
-        <v>1.354753062157686</v>
+        <v>-4.006524474852094</v>
       </c>
       <c r="BC5">
-        <v>5.754964092348529</v>
+        <v>11.41694912221213</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>42.06393827345702</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>23.63541255450272</v>
       </c>
       <c r="BF5">
-        <v>0.9442145399410329</v>
+        <v>0.6873186760847522</v>
       </c>
     </row>
     <row r="6" spans="1:58">
@@ -1538,40 +1547,40 @@
         <v>67</v>
       </c>
       <c r="C6">
-        <v>48.825</v>
+        <v>48.85</v>
       </c>
       <c r="D6">
-        <v>47.5</v>
+        <v>47.55</v>
       </c>
       <c r="E6">
-        <v>1.325</v>
+        <v>1.3</v>
       </c>
       <c r="F6" t="s">
         <v>69</v>
       </c>
       <c r="G6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I6">
-        <v>50.68777575914871</v>
+        <v>50.67427385892116</v>
       </c>
       <c r="J6">
-        <v>49.31222424085129</v>
+        <v>49.32572614107884</v>
       </c>
       <c r="K6">
-        <v>1.375551518297428</v>
+        <v>1.348547717842322</v>
       </c>
       <c r="L6">
-        <v>-0.4670255429338032</v>
+        <v>-0.4691798583288631</v>
       </c>
       <c r="M6">
-        <v>0.9085259753636247</v>
+        <v>0.8793678595134593</v>
       </c>
       <c r="N6">
-        <v>0.9085259753636247</v>
+        <v>0.8793678595134593</v>
       </c>
       <c r="O6">
         <v>0.25</v>
@@ -1580,49 +1589,49 @@
         <v>0.75</v>
       </c>
       <c r="Q6">
-        <v>50.51264118054853</v>
+        <v>50.49833141204784</v>
       </c>
       <c r="R6">
-        <v>49.48735881945147</v>
+        <v>49.50166858795216</v>
       </c>
       <c r="S6">
-        <v>-0.3502691572003522</v>
+        <v>-0.3518848937466473</v>
       </c>
       <c r="T6">
-        <v>1.025282361097076</v>
+        <v>0.9966628240956751</v>
       </c>
       <c r="U6">
-        <v>1.025282361097076</v>
+        <v>0.9966628240956751</v>
       </c>
       <c r="V6">
-        <v>56.86396059822987</v>
+        <v>56.67502366776529</v>
       </c>
       <c r="W6">
-        <v>43.13603940177013</v>
+        <v>43.32497633223471</v>
       </c>
       <c r="X6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Y6" t="s">
         <v>66</v>
       </c>
       <c r="Z6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA6" t="s">
         <v>66</v>
       </c>
       <c r="AB6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AC6">
-        <v>56.86396059822987</v>
+        <v>56.67502366776529</v>
       </c>
       <c r="AD6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AE6">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -1640,16 +1649,16 @@
         <v>0</v>
       </c>
       <c r="AK6">
-        <v>0.2022279921984468</v>
+        <v>0.2031608381283897</v>
       </c>
       <c r="AL6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AM6">
         <v>4</v>
       </c>
       <c r="AN6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AO6" t="s">
         <v>67</v>
@@ -1661,10 +1670,10 @@
         <v>-1.95999999999998</v>
       </c>
       <c r="AR6">
-        <v>2.974717638902924</v>
+        <v>3.003337175904325</v>
       </c>
       <c r="AS6">
-        <v>2.985282361097055</v>
+        <v>2.956662824095655</v>
       </c>
       <c r="AT6">
         <v>2.97999999999999</v>
@@ -1676,10 +1685,10 @@
         <v>6.166256775636249</v>
       </c>
       <c r="AW6">
-        <v>5.307280945654573</v>
+        <v>5.306440474313349</v>
       </c>
       <c r="AX6">
-        <v>5.929512042779748</v>
+        <v>5.92875978066179</v>
       </c>
       <c r="AY6">
         <v>0.8436468628413508</v>
@@ -1714,40 +1723,40 @@
         <v>67</v>
       </c>
       <c r="C7">
-        <v>47.025</v>
+        <v>47.125</v>
       </c>
       <c r="D7">
-        <v>46.55</v>
+        <v>46.6</v>
       </c>
       <c r="E7">
-        <v>0.475</v>
+        <v>0.525</v>
       </c>
       <c r="F7" t="s">
         <v>70</v>
       </c>
       <c r="G7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I7">
-        <v>50.25380710659898</v>
+        <v>50.28007468658309</v>
       </c>
       <c r="J7">
-        <v>49.74619289340102</v>
+        <v>49.71992531341692</v>
       </c>
       <c r="K7">
-        <v>0.507614213197968</v>
+        <v>0.5601493731661762</v>
       </c>
       <c r="L7">
-        <v>-2.118496098593954</v>
+        <v>-2.066588514966667</v>
       </c>
       <c r="M7">
-        <v>-1.610881885395986</v>
+        <v>-1.506439141800491</v>
       </c>
       <c r="N7">
-        <v>-1.610881885395986</v>
+        <v>-1.506439141800491</v>
       </c>
       <c r="O7">
         <v>0.25</v>
@@ -1756,49 +1765,49 @@
         <v>0.75</v>
       </c>
       <c r="Q7">
-        <v>49.45937106962625</v>
+        <v>49.50510399347059</v>
       </c>
       <c r="R7">
-        <v>50.54062893037375</v>
+        <v>50.49489600652941</v>
       </c>
       <c r="S7">
-        <v>-1.588872073945465</v>
+        <v>-1.549941386225</v>
       </c>
       <c r="T7">
-        <v>-1.081257860747497</v>
+        <v>-0.989792013058824</v>
       </c>
       <c r="U7">
-        <v>-1.081257860747497</v>
+        <v>-0.989792013058824</v>
       </c>
       <c r="V7">
-        <v>42.55353044592097</v>
+        <v>43.17452577301096</v>
       </c>
       <c r="W7">
-        <v>57.44646955407903</v>
+        <v>56.82547422698904</v>
       </c>
       <c r="X7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Y7" t="s">
         <v>67</v>
       </c>
       <c r="Z7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AA7" t="s">
         <v>66</v>
       </c>
       <c r="AB7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AC7">
-        <v>42.55353044592097</v>
+        <v>43.17452577301096</v>
       </c>
       <c r="AD7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AE7">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF7">
         <v>0</v>
@@ -1816,16 +1825,16 @@
         <v>0</v>
       </c>
       <c r="AK7">
-        <v>0.9173357196002934</v>
+        <v>0.8948590765651455</v>
       </c>
       <c r="AL7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AM7">
         <v>-6</v>
       </c>
       <c r="AN7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AO7" t="s">
         <v>67</v>
@@ -1837,25 +1846,25 @@
         <v>-3.47999999999999</v>
       </c>
       <c r="AR7">
-        <v>4.918742139252503</v>
+        <v>5.010207986941176</v>
       </c>
       <c r="AS7">
-        <v>2.398742139252493</v>
+        <v>2.490207986941166</v>
       </c>
       <c r="AT7">
-        <v>3.658742139252498</v>
+        <v>3.750207986941171</v>
       </c>
       <c r="AU7">
-        <v>0.9146855348131244</v>
+        <v>0.9375519967352928</v>
       </c>
       <c r="AV7">
         <v>5.775280601260435</v>
       </c>
       <c r="AW7">
-        <v>5.116017109818188</v>
+        <v>5.113664173968316</v>
       </c>
       <c r="AX7">
-        <v>5.758950694120796</v>
+        <v>5.756860543168386</v>
       </c>
       <c r="AY7">
         <v>0.8436468628413508</v>
@@ -1890,40 +1899,40 @@
         <v>67</v>
       </c>
       <c r="C8">
-        <v>46.025</v>
+        <v>45.925</v>
       </c>
       <c r="D8">
-        <v>49.52500000000001</v>
+        <v>47.09999999999999</v>
       </c>
       <c r="E8">
-        <v>-3.5</v>
+        <v>-1.175</v>
       </c>
       <c r="F8" t="s">
         <v>71</v>
       </c>
       <c r="G8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I8">
-        <v>48.16849816849816</v>
+        <v>49.36844934157485</v>
       </c>
       <c r="J8">
-        <v>51.83150183150183</v>
+        <v>50.63155065842515</v>
       </c>
       <c r="K8">
-        <v>-3.663003663003671</v>
+        <v>-1.263101316850296</v>
       </c>
       <c r="L8">
-        <v>-0.319579423669317</v>
+        <v>-2.267434889907832</v>
       </c>
       <c r="M8">
-        <v>-3.982583086672988</v>
+        <v>-3.530536206758129</v>
       </c>
       <c r="N8">
-        <v>-3.982583086672988</v>
+        <v>-3.530536206758129</v>
       </c>
       <c r="O8">
         <v>0.25</v>
@@ -1932,49 +1941,49 @@
         <v>0.75</v>
       </c>
       <c r="Q8">
-        <v>48.04865588462217</v>
+        <v>48.51816125785942</v>
       </c>
       <c r="R8">
-        <v>51.95134411537783</v>
+        <v>51.48183874214058</v>
       </c>
       <c r="S8">
-        <v>-0.2396845677519877</v>
+        <v>-1.700576167430874</v>
       </c>
       <c r="T8">
-        <v>-3.902688230755659</v>
+        <v>-2.96367748428117</v>
       </c>
       <c r="U8">
-        <v>-3.902688230755659</v>
+        <v>-2.96367748428117</v>
       </c>
       <c r="V8">
-        <v>23.15815969257593</v>
+        <v>29.4052758159271</v>
       </c>
       <c r="W8">
-        <v>76.84184030742406</v>
+        <v>70.5947241840729</v>
       </c>
       <c r="X8" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Y8" t="s">
         <v>67</v>
       </c>
       <c r="Z8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AA8" t="s">
         <v>67</v>
       </c>
       <c r="AB8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AC8">
-        <v>23.15815969257593</v>
+        <v>29.4052758159271</v>
       </c>
       <c r="AD8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AE8">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF8">
         <v>0</v>
@@ -1992,16 +2001,16 @@
         <v>0</v>
       </c>
       <c r="AK8">
-        <v>0.1383819497122092</v>
+        <v>0.9818281080436774</v>
       </c>
       <c r="AL8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AM8">
         <v>-8</v>
       </c>
       <c r="AN8" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AO8" t="s">
         <v>67</v>
@@ -2013,25 +2022,25 @@
         <v>-6.439999999999998</v>
       </c>
       <c r="AR8">
-        <v>4.097311769244341</v>
+        <v>5.03632251571883</v>
       </c>
       <c r="AS8">
-        <v>2.537311769244339</v>
+        <v>3.476322515718827</v>
       </c>
       <c r="AT8">
-        <v>3.317311769244339</v>
+        <v>4.256322515718828</v>
       </c>
       <c r="AU8">
-        <v>0.8293279423110849</v>
+        <v>1.064080628929707</v>
       </c>
       <c r="AV8">
         <v>5.314982794026658</v>
       </c>
       <c r="AW8">
-        <v>4.615828922128182</v>
+        <v>4.790990486816234</v>
       </c>
       <c r="AX8">
-        <v>5.319563766674573</v>
+        <v>5.472245597021904</v>
       </c>
       <c r="AY8">
         <v>0.8436468628413508</v>
@@ -2066,40 +2075,40 @@
         <v>67</v>
       </c>
       <c r="C9">
-        <v>46.3</v>
+        <v>46.03333333</v>
       </c>
       <c r="D9">
-        <v>51.16666667000001</v>
+        <v>51.26666667000001</v>
       </c>
       <c r="E9">
-        <v>-4.866666667</v>
+        <v>-5.233333333</v>
       </c>
       <c r="F9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I9">
-        <v>47.50341997101561</v>
+        <v>47.31072284686535</v>
       </c>
       <c r="J9">
-        <v>52.49658002898438</v>
+        <v>52.68927715313463</v>
       </c>
       <c r="K9">
-        <v>-4.993160057968772</v>
+        <v>-5.37855430626928</v>
       </c>
       <c r="L9">
-        <v>1.022628397888314</v>
+        <v>0.9757182060598102</v>
       </c>
       <c r="M9">
-        <v>-3.970531660080458</v>
+        <v>-4.40283610020947</v>
       </c>
       <c r="N9">
-        <v>-3.970531660080458</v>
+        <v>-4.40283610020947</v>
       </c>
       <c r="O9">
         <v>0.25</v>
@@ -2108,49 +2117,49 @@
         <v>0.75</v>
       </c>
       <c r="Q9">
-        <v>47.88690562022373</v>
+        <v>47.67661717413779</v>
       </c>
       <c r="R9">
-        <v>52.11309437977627</v>
+        <v>52.32338282586221</v>
       </c>
       <c r="S9">
-        <v>0.7669712984162356</v>
+        <v>0.7317886545448573</v>
       </c>
       <c r="T9">
-        <v>-4.226188759552537</v>
+        <v>-4.646765651724422</v>
       </c>
       <c r="U9">
-        <v>-4.226188759552537</v>
+        <v>-4.646765651724422</v>
       </c>
       <c r="V9">
-        <v>22.86059118815288</v>
+        <v>20.42376415676219</v>
       </c>
       <c r="W9">
-        <v>77.13940881184712</v>
+        <v>79.57623584323781</v>
       </c>
       <c r="X9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y9" t="s">
         <v>67</v>
       </c>
       <c r="Z9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AA9" t="s">
         <v>67</v>
       </c>
       <c r="AB9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AC9">
-        <v>22.86059118815288</v>
+        <v>20.42376415676219</v>
       </c>
       <c r="AD9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AE9">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF9">
         <v>0</v>
@@ -2168,16 +2177,16 @@
         <v>0</v>
       </c>
       <c r="AK9">
-        <v>0.4428110856013305</v>
+        <v>0.4224983766913874</v>
       </c>
       <c r="AL9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AM9">
         <v>-10</v>
       </c>
       <c r="AN9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AO9" t="s">
         <v>67</v>
@@ -2189,25 +2198,25 @@
         <v>-25.16000000000001</v>
       </c>
       <c r="AR9">
-        <v>5.773811240447463</v>
+        <v>5.353234348275578</v>
       </c>
       <c r="AS9">
-        <v>20.93381124044748</v>
+        <v>20.51323434827559</v>
       </c>
       <c r="AT9">
-        <v>13.35381124044747</v>
+        <v>12.93323434827558</v>
       </c>
       <c r="AU9">
-        <v>3.338452810111868</v>
+        <v>3.233308587068896</v>
       </c>
       <c r="AV9">
         <v>4.390437171606355</v>
       </c>
       <c r="AW9">
-        <v>5.032171060126636</v>
+        <v>4.960986351892614</v>
       </c>
       <c r="AX9">
-        <v>5.684595641533177</v>
+        <v>5.621678362644624</v>
       </c>
       <c r="AY9">
         <v>0.8436468628413508</v>

--- a/outputs/Block5B_Senate_Competitive_Races.xlsx
+++ b/outputs/Block5B_Senate_Competitive_Races.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="96">
   <si>
     <t>STATE</t>
   </si>
@@ -196,21 +196,21 @@
     <t>Ohio</t>
   </si>
   <si>
+    <t>Alaska</t>
+  </si>
+  <si>
     <t>Texas</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
     <t>Maine</t>
   </si>
   <si>
+    <t>Kansas</t>
+  </si>
+  <si>
     <t>Iowa</t>
   </si>
   <si>
-    <t>Kansas</t>
-  </si>
-  <si>
     <t>Nebraska</t>
   </si>
   <si>
@@ -232,9 +232,6 @@
     <t>RSenLeanPollH (&gt;1&lt;=5%)</t>
   </si>
   <si>
-    <t>RSenLikPollH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
     <t>D Lean</t>
   </si>
   <si>
@@ -244,15 +241,9 @@
     <t>R Lean</t>
   </si>
   <si>
-    <t>R Likely</t>
-  </si>
-  <si>
     <t>Lean</t>
   </si>
   <si>
-    <t>Likely</t>
-  </si>
-  <si>
     <t>D Tilt</t>
   </si>
   <si>
@@ -295,19 +286,19 @@
     <t>Appointed (2025)[p]</t>
   </si>
   <si>
+    <t>53.90% R</t>
+  </si>
+  <si>
     <t>53.51% R</t>
   </si>
   <si>
-    <t>53.90% R</t>
-  </si>
-  <si>
     <t>50.98% R</t>
   </si>
   <si>
+    <t>53.22% R</t>
+  </si>
+  <si>
     <t>51.74% R</t>
-  </si>
-  <si>
-    <t>53.22% R</t>
   </si>
   <si>
     <t>62.58% R (2024 sp.)[o]</t>
@@ -855,40 +846,40 @@
         <v>66</v>
       </c>
       <c r="C2">
-        <v>48.725</v>
+        <v>48.15</v>
       </c>
       <c r="D2">
-        <v>45.05</v>
+        <v>45.325</v>
       </c>
       <c r="E2">
-        <v>3.675</v>
+        <v>2.825</v>
       </c>
       <c r="F2" t="s">
         <v>68</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I2">
-        <v>51.95947747267395</v>
+        <v>51.51109922439155</v>
       </c>
       <c r="J2">
-        <v>48.04052252732605</v>
+        <v>48.48890077560846</v>
       </c>
       <c r="K2">
-        <v>3.918954945347906</v>
+        <v>3.022198448783094</v>
       </c>
       <c r="L2">
-        <v>2.590328418627033</v>
+        <v>2.375074950791695</v>
       </c>
       <c r="M2">
-        <v>6.509283363974939</v>
+        <v>5.397273399574789</v>
       </c>
       <c r="N2">
-        <v>6.509283363974939</v>
+        <v>5.397273399574789</v>
       </c>
       <c r="O2">
         <v>0.25</v>
@@ -897,49 +888,49 @@
         <v>0.75</v>
       </c>
       <c r="Q2">
-        <v>52.93085062965909</v>
+        <v>52.40175233093844</v>
       </c>
       <c r="R2">
-        <v>47.06914937034091</v>
+        <v>47.59824766906156</v>
       </c>
       <c r="S2">
-        <v>1.942746313970275</v>
+        <v>1.781306213093772</v>
       </c>
       <c r="T2">
-        <v>5.861701259318181</v>
+        <v>4.803504661876866</v>
       </c>
       <c r="U2">
-        <v>5.861701259318181</v>
+        <v>4.803504661876866</v>
       </c>
       <c r="V2">
-        <v>86.85847000210781</v>
+        <v>82.43962590954837</v>
       </c>
       <c r="W2">
-        <v>13.1415299978922</v>
+        <v>17.56037409045163</v>
       </c>
       <c r="X2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Y2" t="s">
         <v>66</v>
       </c>
       <c r="Z2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AA2" t="s">
         <v>66</v>
       </c>
       <c r="AB2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC2">
+        <v>17.56037409045163</v>
+      </c>
+      <c r="AD2" t="s">
         <v>81</v>
       </c>
-      <c r="AC2">
-        <v>13.1415299978922</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>84</v>
-      </c>
       <c r="AE2">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF2">
         <v>0</v>
@@ -957,16 +948,16 @@
         <v>-0</v>
       </c>
       <c r="AK2">
-        <v>1.121645107337891</v>
+        <v>1.028437621638842</v>
       </c>
       <c r="AL2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AM2">
         <v>0</v>
       </c>
       <c r="AN2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AO2" t="s">
         <v>66</v>
@@ -978,25 +969,25 @@
         <v>-0.2000000000000028</v>
       </c>
       <c r="AR2">
-        <v>5.861701259318181</v>
+        <v>4.803504661876866</v>
       </c>
       <c r="AS2">
-        <v>6.061701259318184</v>
+        <v>5.003504661876868</v>
       </c>
       <c r="AT2">
-        <v>5.961701259318183</v>
+        <v>4.903504661876867</v>
       </c>
       <c r="AU2">
-        <v>1.490425314829546</v>
+        <v>1.225876165469217</v>
       </c>
       <c r="AV2">
         <v>4.890566271054463</v>
       </c>
       <c r="AW2">
-        <v>4.518046915456435</v>
+        <v>4.422368858589397</v>
       </c>
       <c r="AX2">
-        <v>5.234943166800129</v>
+        <v>5.152594332060622</v>
       </c>
       <c r="AY2">
         <v>0.8436468628413508</v>
@@ -1031,40 +1022,40 @@
         <v>67</v>
       </c>
       <c r="C3">
-        <v>47.825</v>
+        <v>47.675</v>
       </c>
       <c r="D3">
         <v>43.7</v>
       </c>
       <c r="E3">
-        <v>4.125</v>
+        <v>3.975</v>
       </c>
       <c r="F3" t="s">
         <v>69</v>
       </c>
       <c r="G3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I3">
-        <v>52.25348265501229</v>
+        <v>52.1751025991792</v>
       </c>
       <c r="J3">
-        <v>47.74651734498771</v>
+        <v>47.8248974008208</v>
       </c>
       <c r="K3">
-        <v>4.506965310024583</v>
+        <v>4.35020519835841</v>
       </c>
       <c r="L3">
-        <v>-2.638289777369295</v>
+        <v>-2.651610263822058</v>
       </c>
       <c r="M3">
-        <v>1.868675532655288</v>
+        <v>1.698594934536351</v>
       </c>
       <c r="N3">
-        <v>1.868675532655288</v>
+        <v>1.698594934536351</v>
       </c>
       <c r="O3">
         <v>0.25</v>
@@ -1073,49 +1064,49 @@
         <v>0.75</v>
       </c>
       <c r="Q3">
-        <v>51.26412398849881</v>
+        <v>51.18074875024593</v>
       </c>
       <c r="R3">
-        <v>48.73587601150119</v>
+        <v>48.81925124975407</v>
       </c>
       <c r="S3">
-        <v>-1.978717333026971</v>
+        <v>-1.988707697866544</v>
       </c>
       <c r="T3">
-        <v>2.528247976997612</v>
+        <v>2.361497500491866</v>
       </c>
       <c r="U3">
-        <v>2.528247976997612</v>
+        <v>2.361497500491866</v>
       </c>
       <c r="V3">
-        <v>68.62056620003455</v>
+        <v>67.5043909927755</v>
       </c>
       <c r="W3">
-        <v>31.37943379996545</v>
+        <v>32.4956090072245</v>
       </c>
       <c r="X3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Y3" t="s">
         <v>66</v>
       </c>
       <c r="Z3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AA3" t="s">
         <v>66</v>
       </c>
       <c r="AB3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AC3">
-        <v>68.62056620003455</v>
+        <v>67.5043909927755</v>
       </c>
       <c r="AD3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AE3">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -1133,34 +1124,34 @@
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>1.1424129848733</v>
+        <v>1.14818092470273</v>
       </c>
       <c r="AL3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AM3">
         <v>-5</v>
       </c>
       <c r="AN3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="AR3">
-        <v>7.528247976997612</v>
+        <v>7.361497500491866</v>
       </c>
       <c r="AT3">
-        <v>7.528247976997612</v>
+        <v>7.361497500491866</v>
       </c>
       <c r="AU3">
-        <v>1.882061994249403</v>
+        <v>1.840374375122966</v>
       </c>
       <c r="AV3">
         <v>4.567515257270437</v>
       </c>
       <c r="AW3">
-        <v>4.490926033506978</v>
+        <v>4.480837687014714</v>
       </c>
       <c r="AX3">
-        <v>5.211554342784182</v>
+        <v>5.202863481462234</v>
       </c>
       <c r="AY3">
         <v>0.8436468628413508</v>
@@ -1195,40 +1186,40 @@
         <v>67</v>
       </c>
       <c r="C4">
-        <v>48.9</v>
+        <v>49.225</v>
       </c>
       <c r="D4">
-        <v>46.175</v>
+        <v>47.025</v>
       </c>
       <c r="E4">
-        <v>2.725</v>
+        <v>2.2</v>
       </c>
       <c r="F4" t="s">
         <v>69</v>
       </c>
       <c r="G4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I4">
-        <v>51.43307914804102</v>
+        <v>51.14285714285715</v>
       </c>
       <c r="J4">
-        <v>48.56692085195898</v>
+        <v>48.85714285714285</v>
       </c>
       <c r="K4">
-        <v>2.866158296082041</v>
+        <v>2.285714285714292</v>
       </c>
       <c r="L4">
-        <v>-0.9522874185159853</v>
+        <v>-0.3058484137633198</v>
       </c>
       <c r="M4">
-        <v>1.913870877566056</v>
+        <v>1.979865871950972</v>
       </c>
       <c r="N4">
-        <v>1.913870877566056</v>
+        <v>1.979865871950972</v>
       </c>
       <c r="O4">
         <v>0.25</v>
@@ -1237,106 +1228,106 @@
         <v>0.75</v>
       </c>
       <c r="Q4">
-        <v>51.07597136609753</v>
+        <v>51.0281639876959</v>
       </c>
       <c r="R4">
-        <v>48.92402863390247</v>
+        <v>48.9718360123041</v>
       </c>
       <c r="S4">
-        <v>-0.7142155638869889</v>
+        <v>-0.2293863103224898</v>
       </c>
       <c r="T4">
-        <v>2.151942732195052</v>
+        <v>2.056327975391802</v>
       </c>
       <c r="U4">
-        <v>2.151942732195052</v>
+        <v>2.056327975391802</v>
       </c>
       <c r="V4">
-        <v>66.42247604555808</v>
+        <v>63.19398747980172</v>
       </c>
       <c r="W4">
-        <v>33.57752395444192</v>
+        <v>36.80601252019828</v>
       </c>
       <c r="X4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Y4" t="s">
         <v>66</v>
       </c>
       <c r="Z4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AA4" t="s">
         <v>66</v>
       </c>
       <c r="AB4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AC4">
-        <v>66.42247604555808</v>
+        <v>63.19398747980172</v>
       </c>
       <c r="AD4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE4">
+        <v>9.098901098901106</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0.1324362480131045</v>
+      </c>
+      <c r="AL4" t="s">
         <v>84</v>
-      </c>
-      <c r="AE4">
-        <v>8.452880158905305</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <v>0.4123525480695734</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>87</v>
       </c>
       <c r="AM4">
         <v>-6</v>
       </c>
       <c r="AN4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="AO4" t="s">
         <v>67</v>
       </c>
       <c r="AP4">
-        <v>0.5351</v>
+        <v>0.539</v>
       </c>
       <c r="AQ4">
-        <v>-7.02000000000001</v>
+        <v>-7.800000000000011</v>
       </c>
       <c r="AR4">
-        <v>8.151942732195053</v>
+        <v>8.056327975391802</v>
       </c>
       <c r="AS4">
-        <v>9.171942732195063</v>
+        <v>9.856327975391814</v>
       </c>
       <c r="AT4">
-        <v>8.661942732195058</v>
+        <v>8.956327975391808</v>
       </c>
       <c r="AU4">
-        <v>2.165485683048765</v>
+        <v>2.239081993847952</v>
       </c>
       <c r="AV4">
-        <v>4.345503062353619</v>
+        <v>5.898436507750732</v>
       </c>
       <c r="AW4">
-        <v>4.331813166230072</v>
+        <v>5.499257889098187</v>
       </c>
       <c r="AX4">
-        <v>5.075084958548591</v>
+        <v>6.101943900116634</v>
       </c>
       <c r="AY4">
         <v>0.8436468628413508</v>
@@ -1345,22 +1336,22 @@
         <v>3</v>
       </c>
       <c r="BA4">
-        <v>1.930645252303767</v>
+        <v>1.541161542643699</v>
       </c>
       <c r="BB4">
-        <v>1.354753062157686</v>
+        <v>-4.006524474852094</v>
       </c>
       <c r="BC4">
-        <v>5.754964092348529</v>
+        <v>11.41694912221213</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>42.06393827345702</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>23.63541255450272</v>
       </c>
       <c r="BF4">
-        <v>0.9442145399410329</v>
+        <v>0.6873186760847522</v>
       </c>
     </row>
     <row r="5" spans="1:58">
@@ -1371,40 +1362,40 @@
         <v>67</v>
       </c>
       <c r="C5">
-        <v>49.475</v>
+        <v>48.575</v>
       </c>
       <c r="D5">
-        <v>46.775</v>
+        <v>46.3</v>
       </c>
       <c r="E5">
-        <v>2.7</v>
+        <v>2.275</v>
       </c>
       <c r="F5" t="s">
         <v>69</v>
       </c>
       <c r="G5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I5">
-        <v>51.4025974025974</v>
+        <v>51.19894598155468</v>
       </c>
       <c r="J5">
-        <v>48.5974025974026</v>
+        <v>48.80105401844532</v>
       </c>
       <c r="K5">
-        <v>2.805194805194802</v>
+        <v>2.397891963109359</v>
       </c>
       <c r="L5">
-        <v>-0.3163895128283701</v>
+        <v>-1.043389660304166</v>
       </c>
       <c r="M5">
-        <v>2.488805292366432</v>
+        <v>1.354502302805193</v>
       </c>
       <c r="N5">
-        <v>2.488805292366432</v>
+        <v>1.354502302805193</v>
       </c>
       <c r="O5">
         <v>0.25</v>
@@ -1413,106 +1404,106 @@
         <v>0.75</v>
       </c>
       <c r="Q5">
-        <v>51.28395133528676</v>
+        <v>50.80767485894062</v>
       </c>
       <c r="R5">
-        <v>48.71604866471324</v>
+        <v>49.19232514105938</v>
       </c>
       <c r="S5">
-        <v>-0.2372921346212777</v>
+        <v>-0.7825422452281245</v>
       </c>
       <c r="T5">
-        <v>2.567902670573524</v>
+        <v>1.615349717881234</v>
       </c>
       <c r="U5">
-        <v>2.567902670573524</v>
+        <v>1.615349717881234</v>
       </c>
       <c r="V5">
-        <v>66.19625489789294</v>
+        <v>62.59604325003473</v>
       </c>
       <c r="W5">
-        <v>33.80374510210705</v>
+        <v>37.40395674996527</v>
       </c>
       <c r="X5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Y5" t="s">
         <v>66</v>
       </c>
       <c r="Z5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AA5" t="s">
         <v>66</v>
       </c>
       <c r="AB5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AC5">
-        <v>66.19625489789294</v>
+        <v>62.59604325003473</v>
       </c>
       <c r="AD5" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE5">
+        <v>9.098901098901106</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0.4518009759347119</v>
+      </c>
+      <c r="AL5" t="s">
         <v>84</v>
-      </c>
-      <c r="AE5">
-        <v>8.452880158905305</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>0.1370006778001755</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>87</v>
       </c>
       <c r="AM5">
         <v>-6</v>
       </c>
       <c r="AN5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="AO5" t="s">
         <v>67</v>
       </c>
       <c r="AP5">
-        <v>0.539</v>
+        <v>0.5351</v>
       </c>
       <c r="AQ5">
-        <v>-7.800000000000011</v>
+        <v>-7.02000000000001</v>
       </c>
       <c r="AR5">
-        <v>8.567902670573524</v>
+        <v>7.615349717881235</v>
       </c>
       <c r="AS5">
-        <v>10.36790267057354</v>
+        <v>8.635349717881244</v>
       </c>
       <c r="AT5">
-        <v>9.46790267057353</v>
+        <v>8.125349717881239</v>
       </c>
       <c r="AU5">
-        <v>2.366975667643382</v>
+        <v>2.03133742947031</v>
       </c>
       <c r="AV5">
-        <v>5.898436507750732</v>
+        <v>4.345503062353619</v>
       </c>
       <c r="AW5">
-        <v>5.547966090444774</v>
+        <v>4.278349256582922</v>
       </c>
       <c r="AX5">
-        <v>6.145877461362781</v>
+        <v>5.029528247327535</v>
       </c>
       <c r="AY5">
         <v>0.8436468628413508</v>
@@ -1521,22 +1512,22 @@
         <v>3</v>
       </c>
       <c r="BA5">
-        <v>1.541161542643699</v>
+        <v>1.930645252303767</v>
       </c>
       <c r="BB5">
-        <v>-4.006524474852094</v>
+        <v>1.354753062157686</v>
       </c>
       <c r="BC5">
-        <v>11.41694912221213</v>
+        <v>5.754964092348529</v>
       </c>
       <c r="BD5">
-        <v>42.06393827345702</v>
+        <v>0</v>
       </c>
       <c r="BE5">
-        <v>23.63541255450272</v>
+        <v>0</v>
       </c>
       <c r="BF5">
-        <v>0.6873186760847522</v>
+        <v>0.9442145399410329</v>
       </c>
     </row>
     <row r="6" spans="1:58">
@@ -1547,40 +1538,40 @@
         <v>67</v>
       </c>
       <c r="C6">
-        <v>48.85</v>
+        <v>49.125</v>
       </c>
       <c r="D6">
-        <v>47.55</v>
+        <v>47.175</v>
       </c>
       <c r="E6">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="F6" t="s">
         <v>69</v>
       </c>
       <c r="G6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I6">
-        <v>50.67427385892116</v>
+        <v>51.01246105919003</v>
       </c>
       <c r="J6">
-        <v>49.32572614107884</v>
+        <v>48.98753894080997</v>
       </c>
       <c r="K6">
-        <v>1.348547717842322</v>
+        <v>2.024922118380061</v>
       </c>
       <c r="L6">
-        <v>-0.4691798583288631</v>
+        <v>-0.3204838353402772</v>
       </c>
       <c r="M6">
-        <v>0.8793678595134593</v>
+        <v>1.704438283039784</v>
       </c>
       <c r="N6">
-        <v>0.8793678595134593</v>
+        <v>1.704438283039784</v>
       </c>
       <c r="O6">
         <v>0.25</v>
@@ -1589,49 +1580,49 @@
         <v>0.75</v>
       </c>
       <c r="Q6">
-        <v>50.49833141204784</v>
+        <v>50.89227962093743</v>
       </c>
       <c r="R6">
-        <v>49.50166858795216</v>
+        <v>49.10772037906257</v>
       </c>
       <c r="S6">
-        <v>-0.3518848937466473</v>
+        <v>-0.2403628765052079</v>
       </c>
       <c r="T6">
-        <v>0.9966628240956751</v>
+        <v>1.784559241874853</v>
       </c>
       <c r="U6">
-        <v>0.9966628240956751</v>
+        <v>1.784559241874853</v>
       </c>
       <c r="V6">
-        <v>56.67502366776529</v>
+        <v>61.83849093383414</v>
       </c>
       <c r="W6">
-        <v>43.32497633223471</v>
+        <v>38.16150906616586</v>
       </c>
       <c r="X6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y6" t="s">
         <v>66</v>
       </c>
       <c r="Z6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AA6" t="s">
         <v>66</v>
       </c>
       <c r="AB6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AC6">
-        <v>56.67502366776529</v>
+        <v>61.83849093383414</v>
       </c>
       <c r="AD6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AE6">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -1649,16 +1640,16 @@
         <v>0</v>
       </c>
       <c r="AK6">
-        <v>0.2031608381283897</v>
+        <v>0.1387735714534746</v>
       </c>
       <c r="AL6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AM6">
         <v>4</v>
       </c>
       <c r="AN6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="AO6" t="s">
         <v>67</v>
@@ -1670,10 +1661,10 @@
         <v>-1.95999999999998</v>
       </c>
       <c r="AR6">
-        <v>3.003337175904325</v>
+        <v>2.215440758125147</v>
       </c>
       <c r="AS6">
-        <v>2.956662824095655</v>
+        <v>3.744559241874833</v>
       </c>
       <c r="AT6">
         <v>2.97999999999999</v>
@@ -1685,10 +1676,10 @@
         <v>6.166256775636249</v>
       </c>
       <c r="AW6">
-        <v>5.306440474313349</v>
+        <v>5.301134249610259</v>
       </c>
       <c r="AX6">
-        <v>5.92875978066179</v>
+        <v>5.924011002838607</v>
       </c>
       <c r="AY6">
         <v>0.8436468628413508</v>
@@ -1723,40 +1714,40 @@
         <v>67</v>
       </c>
       <c r="C7">
-        <v>47.125</v>
+        <v>46.25</v>
       </c>
       <c r="D7">
-        <v>46.6</v>
+        <v>45.775</v>
       </c>
       <c r="E7">
-        <v>0.525</v>
+        <v>0.475</v>
       </c>
       <c r="F7" t="s">
         <v>70</v>
       </c>
       <c r="G7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I7">
-        <v>50.28007468658309</v>
+        <v>50.25808204292311</v>
       </c>
       <c r="J7">
-        <v>49.71992531341692</v>
+        <v>49.74191795707688</v>
       </c>
       <c r="K7">
-        <v>0.5601493731661762</v>
+        <v>0.5161640858462349</v>
       </c>
       <c r="L7">
-        <v>-2.066588514966667</v>
+        <v>-2.913528240380083</v>
       </c>
       <c r="M7">
-        <v>-1.506439141800491</v>
+        <v>-2.397364154533848</v>
       </c>
       <c r="N7">
-        <v>-1.506439141800491</v>
+        <v>-2.397364154533848</v>
       </c>
       <c r="O7">
         <v>0.25</v>
@@ -1765,49 +1756,49 @@
         <v>0.75</v>
       </c>
       <c r="Q7">
-        <v>49.50510399347059</v>
+        <v>49.16550895278058</v>
       </c>
       <c r="R7">
-        <v>50.49489600652941</v>
+        <v>50.83449104721942</v>
       </c>
       <c r="S7">
-        <v>-1.549941386225</v>
+        <v>-2.185146180285062</v>
       </c>
       <c r="T7">
-        <v>-0.989792013058824</v>
+        <v>-1.668982094438827</v>
       </c>
       <c r="U7">
-        <v>-0.989792013058824</v>
+        <v>-1.668982094438827</v>
       </c>
       <c r="V7">
-        <v>43.17452577301096</v>
+        <v>38.30178365229862</v>
       </c>
       <c r="W7">
-        <v>56.82547422698904</v>
+        <v>61.69821634770138</v>
       </c>
       <c r="X7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="Y7" t="s">
         <v>67</v>
       </c>
       <c r="Z7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AA7" t="s">
         <v>66</v>
       </c>
       <c r="AB7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AC7">
-        <v>43.17452577301096</v>
+        <v>38.30178365229862</v>
       </c>
       <c r="AD7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AE7">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF7">
         <v>0</v>
@@ -1825,70 +1816,70 @@
         <v>0</v>
       </c>
       <c r="AK7">
-        <v>0.8948590765651455</v>
+        <v>1.261594735406263</v>
       </c>
       <c r="AL7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AM7">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="AN7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="AO7" t="s">
         <v>67</v>
       </c>
       <c r="AP7">
-        <v>0.5174</v>
+        <v>0.5322</v>
       </c>
       <c r="AQ7">
-        <v>-3.47999999999999</v>
+        <v>-6.439999999999998</v>
       </c>
       <c r="AR7">
-        <v>5.010207986941176</v>
+        <v>6.331017905561173</v>
       </c>
       <c r="AS7">
-        <v>2.490207986941166</v>
+        <v>4.771017905561171</v>
       </c>
       <c r="AT7">
-        <v>3.750207986941171</v>
+        <v>5.551017905561172</v>
       </c>
       <c r="AU7">
-        <v>0.9375519967352928</v>
+        <v>1.387754476390293</v>
       </c>
       <c r="AV7">
-        <v>5.775280601260435</v>
+        <v>5.314982794026658</v>
       </c>
       <c r="AW7">
-        <v>5.113664173968316</v>
+        <v>4.946399794780316</v>
       </c>
       <c r="AX7">
-        <v>5.756860543168386</v>
+        <v>5.608810298019065</v>
       </c>
       <c r="AY7">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA7">
-        <v>2.193175026846863</v>
+        <v>0</v>
       </c>
       <c r="BB7">
-        <v>-2.886112316484782</v>
+        <v>-0.3706239798868902</v>
       </c>
       <c r="BC7">
-        <v>6.837360120673064</v>
+        <v>5.000892084631056</v>
       </c>
       <c r="BD7">
-        <v>30.49114883433812</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>8.823529411764707</v>
       </c>
       <c r="BF7">
-        <v>0.9513390040572299</v>
+        <v>0.9238036867710117</v>
       </c>
     </row>
     <row r="8" spans="1:58">
@@ -1899,40 +1890,40 @@
         <v>67</v>
       </c>
       <c r="C8">
-        <v>45.925</v>
+        <v>45.975</v>
       </c>
       <c r="D8">
-        <v>47.09999999999999</v>
+        <v>46.425</v>
       </c>
       <c r="E8">
-        <v>-1.175</v>
+        <v>-0.45</v>
       </c>
       <c r="F8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I8">
-        <v>49.36844934157485</v>
+        <v>49.75649350649351</v>
       </c>
       <c r="J8">
-        <v>50.63155065842515</v>
+        <v>50.24350649350649</v>
       </c>
       <c r="K8">
-        <v>-1.263101316850296</v>
+        <v>-0.4870129870129816</v>
       </c>
       <c r="L8">
-        <v>-2.267434889907832</v>
+        <v>-2.685028376207439</v>
       </c>
       <c r="M8">
-        <v>-3.530536206758129</v>
+        <v>-3.172041363220421</v>
       </c>
       <c r="N8">
-        <v>-3.530536206758129</v>
+        <v>-3.172041363220421</v>
       </c>
       <c r="O8">
         <v>0.25</v>
@@ -1941,130 +1932,130 @@
         <v>0.75</v>
       </c>
       <c r="Q8">
-        <v>48.51816125785942</v>
+        <v>48.74960786541572</v>
       </c>
       <c r="R8">
-        <v>51.48183874214058</v>
+        <v>51.25039213458428</v>
       </c>
       <c r="S8">
-        <v>-1.700576167430874</v>
+        <v>-2.01377128215558</v>
       </c>
       <c r="T8">
-        <v>-2.96367748428117</v>
+        <v>-2.500784269168561</v>
       </c>
       <c r="U8">
-        <v>-2.96367748428117</v>
+        <v>-2.500784269168561</v>
       </c>
       <c r="V8">
-        <v>29.4052758159271</v>
+        <v>33.22591425492713</v>
       </c>
       <c r="W8">
-        <v>70.5947241840729</v>
+        <v>66.77408574507287</v>
       </c>
       <c r="X8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="Y8" t="s">
         <v>67</v>
       </c>
       <c r="Z8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AA8" t="s">
         <v>67</v>
       </c>
       <c r="AB8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AC8">
-        <v>29.4052758159271</v>
+        <v>33.22591425492713</v>
       </c>
       <c r="AD8" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE8">
+        <v>9.098901098901106</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>1.162651391838862</v>
+      </c>
+      <c r="AL8" t="s">
         <v>84</v>
       </c>
-      <c r="AE8">
-        <v>8.452880158905305</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>0</v>
-      </c>
-      <c r="AH8">
-        <v>0</v>
-      </c>
-      <c r="AI8">
-        <v>0</v>
-      </c>
-      <c r="AJ8">
-        <v>0</v>
-      </c>
-      <c r="AK8">
-        <v>0.9818281080436774</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>89</v>
-      </c>
       <c r="AM8">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AN8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AO8" t="s">
         <v>67</v>
       </c>
       <c r="AP8">
-        <v>0.5322</v>
+        <v>0.5174</v>
       </c>
       <c r="AQ8">
-        <v>-6.439999999999998</v>
+        <v>-3.47999999999999</v>
       </c>
       <c r="AR8">
-        <v>5.03632251571883</v>
+        <v>3.499215730831439</v>
       </c>
       <c r="AS8">
-        <v>3.476322515718827</v>
+        <v>0.9792157308314287</v>
       </c>
       <c r="AT8">
-        <v>4.256322515718828</v>
+        <v>2.239215730831434</v>
       </c>
       <c r="AU8">
-        <v>1.064080628929707</v>
+        <v>0.5598039327078584</v>
       </c>
       <c r="AV8">
-        <v>5.314982794026658</v>
+        <v>5.775280601260435</v>
       </c>
       <c r="AW8">
-        <v>4.790990486816234</v>
+        <v>5.12437958111547</v>
       </c>
       <c r="AX8">
-        <v>5.472245597021904</v>
+        <v>5.766380851167837</v>
       </c>
       <c r="AY8">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>2.193175026846863</v>
       </c>
       <c r="BB8">
-        <v>-0.3706239798868902</v>
+        <v>-2.886112316484782</v>
       </c>
       <c r="BC8">
-        <v>5.000892084631056</v>
+        <v>6.837360120673064</v>
       </c>
       <c r="BD8">
-        <v>17.64705882352941</v>
+        <v>30.49114883433812</v>
       </c>
       <c r="BE8">
-        <v>8.823529411764707</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>0.9238036867710117</v>
+        <v>0.9513390040572299</v>
       </c>
     </row>
     <row r="9" spans="1:58">
@@ -2075,40 +2066,40 @@
         <v>67</v>
       </c>
       <c r="C9">
-        <v>46.03333333</v>
+        <v>46.1</v>
       </c>
       <c r="D9">
-        <v>51.26666667000001</v>
+        <v>48.7</v>
       </c>
       <c r="E9">
-        <v>-5.233333333</v>
+        <v>-2.6</v>
       </c>
       <c r="F9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I9">
-        <v>47.31072284686535</v>
+        <v>48.62869198312237</v>
       </c>
       <c r="J9">
-        <v>52.68927715313463</v>
+        <v>51.37130801687764</v>
       </c>
       <c r="K9">
-        <v>-5.37855430626928</v>
+        <v>-2.742616033755276</v>
       </c>
       <c r="L9">
-        <v>0.9757182060598102</v>
+        <v>-0.8762175158523855</v>
       </c>
       <c r="M9">
-        <v>-4.40283610020947</v>
+        <v>-3.618833549607661</v>
       </c>
       <c r="N9">
-        <v>-4.40283610020947</v>
+        <v>-3.618833549607661</v>
       </c>
       <c r="O9">
         <v>0.25</v>
@@ -2117,49 +2108,49 @@
         <v>0.75</v>
       </c>
       <c r="Q9">
-        <v>47.67661717413779</v>
+        <v>48.30011041467772</v>
       </c>
       <c r="R9">
-        <v>52.32338282586221</v>
+        <v>51.69988958532228</v>
       </c>
       <c r="S9">
-        <v>0.7317886545448573</v>
+        <v>-0.657163136889289</v>
       </c>
       <c r="T9">
-        <v>-4.646765651724422</v>
+        <v>-3.399779170644565</v>
       </c>
       <c r="U9">
-        <v>-4.646765651724422</v>
+        <v>-3.399779170644565</v>
       </c>
       <c r="V9">
-        <v>20.42376415676219</v>
+        <v>28.00039720000291</v>
       </c>
       <c r="W9">
-        <v>79.57623584323781</v>
+        <v>71.99960279999709</v>
       </c>
       <c r="X9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Y9" t="s">
         <v>67</v>
       </c>
       <c r="Z9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AA9" t="s">
         <v>67</v>
       </c>
       <c r="AB9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AC9">
-        <v>20.42376415676219</v>
+        <v>28.00039720000291</v>
       </c>
       <c r="AD9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AE9">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF9">
         <v>0</v>
@@ -2177,16 +2168,16 @@
         <v>0</v>
       </c>
       <c r="AK9">
-        <v>0.4224983766913874</v>
+        <v>0.3794133139845298</v>
       </c>
       <c r="AL9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AM9">
         <v>-10</v>
       </c>
       <c r="AN9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AO9" t="s">
         <v>67</v>
@@ -2198,25 +2189,25 @@
         <v>-25.16000000000001</v>
       </c>
       <c r="AR9">
-        <v>5.353234348275578</v>
+        <v>6.600220829355435</v>
       </c>
       <c r="AS9">
-        <v>20.51323434827559</v>
+        <v>21.76022082935545</v>
       </c>
       <c r="AT9">
-        <v>12.93323434827558</v>
+        <v>14.18022082935544</v>
       </c>
       <c r="AU9">
-        <v>3.233308587068896</v>
+        <v>3.54505520733886</v>
       </c>
       <c r="AV9">
         <v>4.390437171606355</v>
       </c>
       <c r="AW9">
-        <v>4.960986351892614</v>
+        <v>5.199488328800901</v>
       </c>
       <c r="AX9">
-        <v>5.621678362644624</v>
+        <v>5.833229029508334</v>
       </c>
       <c r="AY9">
         <v>0.8436468628413508</v>

--- a/outputs/Block5B_Senate_Competitive_Races.xlsx
+++ b/outputs/Block5B_Senate_Competitive_Races.xlsx
@@ -1890,13 +1890,13 @@
         <v>67</v>
       </c>
       <c r="C8">
-        <v>45.975</v>
+        <v>46.225</v>
       </c>
       <c r="D8">
-        <v>46.425</v>
+        <v>46.125</v>
       </c>
       <c r="E8">
-        <v>-0.45</v>
+        <v>0.1</v>
       </c>
       <c r="F8" t="s">
         <v>70</v>
@@ -1908,22 +1908,22 @@
         <v>73</v>
       </c>
       <c r="I8">
-        <v>49.75649350649351</v>
+        <v>50.05414185165133</v>
       </c>
       <c r="J8">
-        <v>50.24350649350649</v>
+        <v>49.94585814834868</v>
       </c>
       <c r="K8">
-        <v>-0.4870129870129816</v>
+        <v>0.1082837033026536</v>
       </c>
       <c r="L8">
-        <v>-2.685028376207439</v>
+        <v>-2.800784857330001</v>
       </c>
       <c r="M8">
-        <v>-3.172041363220421</v>
+        <v>-2.692501154027347</v>
       </c>
       <c r="N8">
-        <v>-3.172041363220421</v>
+        <v>-2.692501154027347</v>
       </c>
       <c r="O8">
         <v>0.25</v>
@@ -1932,25 +1932,25 @@
         <v>0.75</v>
       </c>
       <c r="Q8">
-        <v>48.74960786541572</v>
+        <v>49.00384753015258</v>
       </c>
       <c r="R8">
-        <v>51.25039213458428</v>
+        <v>50.99615246984742</v>
       </c>
       <c r="S8">
-        <v>-2.01377128215558</v>
+        <v>-2.100588642997501</v>
       </c>
       <c r="T8">
-        <v>-2.500784269168561</v>
+        <v>-1.992304939694847</v>
       </c>
       <c r="U8">
-        <v>-2.500784269168561</v>
+        <v>-1.992304939694847</v>
       </c>
       <c r="V8">
-        <v>33.22591425492713</v>
+        <v>36.54288608991354</v>
       </c>
       <c r="W8">
-        <v>66.77408574507287</v>
+        <v>63.45711391008646</v>
       </c>
       <c r="X8" t="s">
         <v>77</v>
@@ -1962,13 +1962,13 @@
         <v>80</v>
       </c>
       <c r="AA8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AB8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC8">
-        <v>33.22591425492713</v>
+        <v>36.54288608991354</v>
       </c>
       <c r="AD8" t="s">
         <v>81</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="AK8">
-        <v>1.162651391838862</v>
+        <v>1.212775418491278</v>
       </c>
       <c r="AL8" t="s">
         <v>84</v>
@@ -2013,25 +2013,25 @@
         <v>-3.47999999999999</v>
       </c>
       <c r="AR8">
-        <v>3.499215730831439</v>
+        <v>4.007695060305153</v>
       </c>
       <c r="AS8">
-        <v>0.9792157308314287</v>
+        <v>1.487695060305143</v>
       </c>
       <c r="AT8">
-        <v>2.239215730831434</v>
+        <v>2.747695060305148</v>
       </c>
       <c r="AU8">
-        <v>0.5598039327078584</v>
+        <v>0.6869237650762869</v>
       </c>
       <c r="AV8">
         <v>5.775280601260435</v>
       </c>
       <c r="AW8">
-        <v>5.12437958111547</v>
+        <v>5.153011767448446</v>
       </c>
       <c r="AX8">
-        <v>5.766380851167837</v>
+        <v>5.791840148417783</v>
       </c>
       <c r="AY8">
         <v>0.8436468628413508</v>
@@ -2066,13 +2066,13 @@
         <v>67</v>
       </c>
       <c r="C9">
-        <v>46.1</v>
+        <v>45.6</v>
       </c>
       <c r="D9">
-        <v>48.7</v>
+        <v>46.93333333</v>
       </c>
       <c r="E9">
-        <v>-2.6</v>
+        <v>-1.333333333</v>
       </c>
       <c r="F9" t="s">
         <v>71</v>
@@ -2084,22 +2084,22 @@
         <v>75</v>
       </c>
       <c r="I9">
-        <v>48.62869198312237</v>
+        <v>49.27953890667433</v>
       </c>
       <c r="J9">
-        <v>51.37130801687764</v>
+        <v>50.72046109332566</v>
       </c>
       <c r="K9">
-        <v>-2.742616033755276</v>
+        <v>-1.440922186651328</v>
       </c>
       <c r="L9">
-        <v>-0.8762175158523855</v>
+        <v>-2.404592995100077</v>
       </c>
       <c r="M9">
-        <v>-3.618833549607661</v>
+        <v>-3.845515181751405</v>
       </c>
       <c r="N9">
-        <v>-3.618833549607661</v>
+        <v>-3.845515181751405</v>
       </c>
       <c r="O9">
         <v>0.25</v>
@@ -2108,25 +2108,25 @@
         <v>0.75</v>
       </c>
       <c r="Q9">
-        <v>48.30011041467772</v>
+        <v>48.3778165335118</v>
       </c>
       <c r="R9">
-        <v>51.69988958532228</v>
+        <v>51.6221834664882</v>
       </c>
       <c r="S9">
-        <v>-0.657163136889289</v>
+        <v>-1.803444746325058</v>
       </c>
       <c r="T9">
-        <v>-3.399779170644565</v>
+        <v>-3.244366932976385</v>
       </c>
       <c r="U9">
-        <v>-3.399779170644565</v>
+        <v>-3.244366932976385</v>
       </c>
       <c r="V9">
-        <v>28.00039720000291</v>
+        <v>29.28823179916958</v>
       </c>
       <c r="W9">
-        <v>71.99960279999709</v>
+        <v>70.71176820083042</v>
       </c>
       <c r="X9" t="s">
         <v>74</v>
@@ -2144,7 +2144,7 @@
         <v>80</v>
       </c>
       <c r="AC9">
-        <v>28.00039720000291</v>
+        <v>29.28823179916958</v>
       </c>
       <c r="AD9" t="s">
         <v>81</v>
@@ -2168,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="AK9">
-        <v>0.3794133139845298</v>
+        <v>1.041219309759388</v>
       </c>
       <c r="AL9" t="s">
         <v>87</v>
@@ -2189,25 +2189,25 @@
         <v>-25.16000000000001</v>
       </c>
       <c r="AR9">
-        <v>6.600220829355435</v>
+        <v>6.755633067023615</v>
       </c>
       <c r="AS9">
-        <v>21.76022082935545</v>
+        <v>21.91563306702363</v>
       </c>
       <c r="AT9">
-        <v>14.18022082935544</v>
+        <v>14.33563306702362</v>
       </c>
       <c r="AU9">
-        <v>3.54505520733886</v>
+        <v>3.583908266755905</v>
       </c>
       <c r="AV9">
         <v>4.390437171606355</v>
       </c>
       <c r="AW9">
-        <v>5.199488328800901</v>
+        <v>5.33366990827579</v>
       </c>
       <c r="AX9">
-        <v>5.833229029508334</v>
+        <v>5.95314343181891</v>
       </c>
       <c r="AY9">
         <v>0.8436468628413508</v>

--- a/outputs/Block5B_Senate_Competitive_Races.xlsx
+++ b/outputs/Block5B_Senate_Competitive_Races.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="101">
   <si>
     <t>STATE</t>
   </si>
@@ -193,6 +193,9 @@
     <t>Michigan</t>
   </si>
   <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
     <t>Ohio</t>
   </si>
   <si>
@@ -214,6 +217,9 @@
     <t>Nebraska</t>
   </si>
   <si>
+    <t>South Carolina</t>
+  </si>
+  <si>
     <t>D</t>
   </si>
   <si>
@@ -265,6 +271,9 @@
     <t>EVEN</t>
   </si>
   <si>
+    <t>D+3</t>
+  </si>
+  <si>
     <t>R+5</t>
   </si>
   <si>
@@ -283,6 +292,9 @@
     <t>49.90% D</t>
   </si>
   <si>
+    <t>48.74% D</t>
+  </si>
+  <si>
     <t>Appointed (2025)[p]</t>
   </si>
   <si>
@@ -302,6 +314,9 @@
   </si>
   <si>
     <t>62.58% R (2024 sp.)[o]</t>
+  </si>
+  <si>
+    <t>Appointed (2026)[r]</t>
   </si>
 </sst>
 </file>
@@ -659,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BF9"/>
+  <dimension ref="A1:BF11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:58">
@@ -843,43 +858,43 @@
         <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2">
-        <v>48.15</v>
+        <v>47.95</v>
       </c>
       <c r="D2">
-        <v>45.325</v>
+        <v>45.7</v>
       </c>
       <c r="E2">
-        <v>2.825</v>
+        <v>2.25</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I2">
-        <v>51.51109922439155</v>
+        <v>51.20128136679124</v>
       </c>
       <c r="J2">
-        <v>48.48890077560846</v>
+        <v>48.79871863320875</v>
       </c>
       <c r="K2">
-        <v>3.022198448783094</v>
+        <v>2.402562733582492</v>
       </c>
       <c r="L2">
-        <v>2.375074950791695</v>
+        <v>2.325407102330715</v>
       </c>
       <c r="M2">
-        <v>5.397273399574789</v>
+        <v>4.727969835913207</v>
       </c>
       <c r="N2">
-        <v>5.397273399574789</v>
+        <v>4.727969835913207</v>
       </c>
       <c r="O2">
         <v>0.25</v>
@@ -888,49 +903,49 @@
         <v>0.75</v>
       </c>
       <c r="Q2">
-        <v>52.40175233093844</v>
+        <v>52.07330903016526</v>
       </c>
       <c r="R2">
-        <v>47.59824766906156</v>
+        <v>47.92669096983474</v>
       </c>
       <c r="S2">
-        <v>1.781306213093772</v>
+        <v>1.744055326748036</v>
       </c>
       <c r="T2">
-        <v>4.803504661876866</v>
+        <v>4.146618060330528</v>
       </c>
       <c r="U2">
-        <v>4.803504661876866</v>
+        <v>4.146618060330528</v>
       </c>
       <c r="V2">
-        <v>82.43962590954837</v>
+        <v>79.12552443815213</v>
       </c>
       <c r="W2">
-        <v>17.56037409045163</v>
+        <v>20.87447556184787</v>
       </c>
       <c r="X2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Z2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AA2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AB2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AC2">
-        <v>17.56037409045163</v>
+        <v>20.87447556184787</v>
       </c>
       <c r="AD2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE2">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF2">
         <v>0</v>
@@ -948,19 +963,19 @@
         <v>-0</v>
       </c>
       <c r="AK2">
-        <v>1.028437621638842</v>
+        <v>1.006930812379579</v>
       </c>
       <c r="AL2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AM2">
         <v>0</v>
       </c>
       <c r="AN2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AO2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AP2">
         <v>0.499</v>
@@ -969,25 +984,25 @@
         <v>-0.2000000000000028</v>
       </c>
       <c r="AR2">
-        <v>4.803504661876866</v>
+        <v>4.146618060330528</v>
       </c>
       <c r="AS2">
-        <v>5.003504661876868</v>
+        <v>4.346618060330531</v>
       </c>
       <c r="AT2">
-        <v>4.903504661876867</v>
+        <v>4.24661806033053</v>
       </c>
       <c r="AU2">
-        <v>1.225876165469217</v>
+        <v>1.061654515082632</v>
       </c>
       <c r="AV2">
         <v>4.890566271054463</v>
       </c>
       <c r="AW2">
-        <v>4.422368858589397</v>
+        <v>4.377725388203625</v>
       </c>
       <c r="AX2">
-        <v>5.152594332060622</v>
+        <v>5.114329047283185</v>
       </c>
       <c r="AY2">
         <v>0.8436468628413508</v>
@@ -1019,43 +1034,43 @@
         <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3">
-        <v>47.675</v>
+        <v>46.575</v>
       </c>
       <c r="D3">
-        <v>43.7</v>
+        <v>43.27500000000001</v>
       </c>
       <c r="E3">
-        <v>3.975</v>
+        <v>3.3</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I3">
-        <v>52.1751025991792</v>
+        <v>51.8363939899833</v>
       </c>
       <c r="J3">
-        <v>47.8248974008208</v>
+        <v>48.1636060100167</v>
       </c>
       <c r="K3">
-        <v>4.35020519835841</v>
+        <v>3.6727879799666</v>
       </c>
       <c r="L3">
-        <v>-2.651610263822058</v>
+        <v>0.4421695923481876</v>
       </c>
       <c r="M3">
-        <v>1.698594934536351</v>
+        <v>4.114957572314788</v>
       </c>
       <c r="N3">
-        <v>1.698594934536351</v>
+        <v>4.114957572314788</v>
       </c>
       <c r="O3">
         <v>0.25</v>
@@ -1064,49 +1079,49 @@
         <v>0.75</v>
       </c>
       <c r="Q3">
-        <v>51.18074875024593</v>
+        <v>52.00220758711387</v>
       </c>
       <c r="R3">
-        <v>48.81925124975407</v>
+        <v>47.99779241288613</v>
       </c>
       <c r="S3">
-        <v>-1.988707697866544</v>
+        <v>0.3316271942611415</v>
       </c>
       <c r="T3">
-        <v>2.361497500491866</v>
+        <v>4.004415174227741</v>
       </c>
       <c r="U3">
-        <v>2.361497500491866</v>
+        <v>4.004415174227741</v>
       </c>
       <c r="V3">
-        <v>67.5043909927755</v>
+        <v>77.42997567231396</v>
       </c>
       <c r="W3">
-        <v>32.4956090072245</v>
+        <v>22.57002432768605</v>
       </c>
       <c r="X3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Y3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Z3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AB3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC3">
-        <v>67.5043909927755</v>
+        <v>22.57002432768605</v>
       </c>
       <c r="AD3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE3">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -1121,61 +1136,73 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK3">
-        <v>1.14818092470273</v>
+        <v>0.1914650498772701</v>
       </c>
       <c r="AL3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AM3">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="AN3" t="s">
-        <v>89</v>
+        <v>92</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP3">
+        <v>0.4874</v>
+      </c>
+      <c r="AQ3">
+        <v>-2.519999999999996</v>
       </c>
       <c r="AR3">
-        <v>7.361497500491866</v>
+        <v>1.004415174227741</v>
+      </c>
+      <c r="AS3">
+        <v>6.524415174227737</v>
       </c>
       <c r="AT3">
-        <v>7.361497500491866</v>
+        <v>3.764415174227739</v>
       </c>
       <c r="AU3">
-        <v>1.840374375122966</v>
+        <v>0.9411037935569349</v>
       </c>
       <c r="AV3">
-        <v>4.567515257270437</v>
+        <v>5.314982794026658</v>
       </c>
       <c r="AW3">
-        <v>4.480837687014714</v>
+        <v>4.613297734483568</v>
       </c>
       <c r="AX3">
-        <v>5.202863481462234</v>
+        <v>5.317367583339822</v>
       </c>
       <c r="AY3">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA3">
-        <v>2.797261014127842</v>
+        <v>0</v>
       </c>
       <c r="BB3">
-        <v>0.1730167113317724</v>
+        <v>-0.3706239798868902</v>
       </c>
       <c r="BC3">
-        <v>2.956526743070407</v>
+        <v>5.000892084631056</v>
       </c>
       <c r="BD3">
-        <v>17.4915896825486</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>8.823529411764707</v>
       </c>
       <c r="BF3">
-        <v>0.956231216651788</v>
+        <v>0.9238036867710117</v>
       </c>
     </row>
     <row r="4" spans="1:58">
@@ -1183,43 +1210,43 @@
         <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C4">
-        <v>49.225</v>
+        <v>48.125</v>
       </c>
       <c r="D4">
-        <v>47.025</v>
+        <v>43.7</v>
       </c>
       <c r="E4">
-        <v>2.2</v>
+        <v>4.425</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I4">
-        <v>51.14285714285715</v>
+        <v>52.40947454396951</v>
       </c>
       <c r="J4">
-        <v>48.85714285714285</v>
+        <v>47.59052545603049</v>
       </c>
       <c r="K4">
-        <v>2.285714285714292</v>
+        <v>4.818949087939018</v>
       </c>
       <c r="L4">
-        <v>-0.3058484137633198</v>
+        <v>-2.374390711518226</v>
       </c>
       <c r="M4">
-        <v>1.979865871950972</v>
+        <v>2.444558376420792</v>
       </c>
       <c r="N4">
-        <v>1.979865871950972</v>
+        <v>2.444558376420792</v>
       </c>
       <c r="O4">
         <v>0.25</v>
@@ -1228,49 +1255,49 @@
         <v>0.75</v>
       </c>
       <c r="Q4">
-        <v>51.0281639876959</v>
+        <v>51.51907802715017</v>
       </c>
       <c r="R4">
-        <v>48.9718360123041</v>
+        <v>48.48092197284983</v>
       </c>
       <c r="S4">
-        <v>-0.2293863103224898</v>
+        <v>-1.78079303363867</v>
       </c>
       <c r="T4">
-        <v>2.056327975391802</v>
+        <v>3.038156054300348</v>
       </c>
       <c r="U4">
-        <v>2.056327975391802</v>
+        <v>3.038156054300348</v>
       </c>
       <c r="V4">
-        <v>63.19398747980172</v>
+        <v>71.91900153246786</v>
       </c>
       <c r="W4">
-        <v>36.80601252019828</v>
+        <v>28.08099846753214</v>
       </c>
       <c r="X4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Y4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Z4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AA4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AB4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC4">
-        <v>63.19398747980172</v>
+        <v>71.91900153246786</v>
       </c>
       <c r="AD4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE4">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF4">
         <v>0</v>
@@ -1288,70 +1315,58 @@
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>0.1324362480131045</v>
+        <v>1.028141337342296</v>
       </c>
       <c r="AL4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AM4">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="AN4" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AP4">
-        <v>0.539</v>
-      </c>
-      <c r="AQ4">
-        <v>-7.800000000000011</v>
+        <v>93</v>
       </c>
       <c r="AR4">
-        <v>8.056327975391802</v>
-      </c>
-      <c r="AS4">
-        <v>9.856327975391814</v>
+        <v>8.038156054300348</v>
       </c>
       <c r="AT4">
-        <v>8.956327975391808</v>
+        <v>8.038156054300348</v>
       </c>
       <c r="AU4">
-        <v>2.239081993847952</v>
+        <v>2.009539013575087</v>
       </c>
       <c r="AV4">
-        <v>5.898436507750732</v>
+        <v>4.567515257270437</v>
       </c>
       <c r="AW4">
-        <v>5.499257889098187</v>
+        <v>4.517251250195202</v>
       </c>
       <c r="AX4">
-        <v>6.101943900116634</v>
+        <v>5.234256478885237</v>
       </c>
       <c r="AY4">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA4">
-        <v>1.541161542643699</v>
+        <v>2.797261014127842</v>
       </c>
       <c r="BB4">
-        <v>-4.006524474852094</v>
+        <v>0.1730167113317724</v>
       </c>
       <c r="BC4">
-        <v>11.41694912221213</v>
+        <v>2.956526743070407</v>
       </c>
       <c r="BD4">
-        <v>42.06393827345702</v>
+        <v>17.4915896825486</v>
       </c>
       <c r="BE4">
-        <v>23.63541255450272</v>
+        <v>0</v>
       </c>
       <c r="BF4">
-        <v>0.6873186760847522</v>
+        <v>0.956231216651788</v>
       </c>
     </row>
     <row r="5" spans="1:58">
@@ -1359,43 +1374,43 @@
         <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C5">
-        <v>48.575</v>
+        <v>49.45</v>
       </c>
       <c r="D5">
-        <v>46.3</v>
+        <v>47.625</v>
       </c>
       <c r="E5">
-        <v>2.275</v>
+        <v>1.825</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I5">
-        <v>51.19894598155468</v>
+        <v>50.93999484934329</v>
       </c>
       <c r="J5">
-        <v>48.80105401844532</v>
+        <v>49.06000515065671</v>
       </c>
       <c r="K5">
-        <v>2.397891963109359</v>
+        <v>1.879989698686586</v>
       </c>
       <c r="L5">
-        <v>-1.043389660304166</v>
+        <v>0.03624629882810737</v>
       </c>
       <c r="M5">
-        <v>1.354502302805193</v>
+        <v>1.916235997514693</v>
       </c>
       <c r="N5">
-        <v>1.354502302805193</v>
+        <v>1.916235997514693</v>
       </c>
       <c r="O5">
         <v>0.25</v>
@@ -1404,49 +1419,49 @@
         <v>0.75</v>
       </c>
       <c r="Q5">
-        <v>50.80767485894062</v>
+        <v>50.95358721140384</v>
       </c>
       <c r="R5">
-        <v>49.19232514105938</v>
+        <v>49.04641278859616</v>
       </c>
       <c r="S5">
-        <v>-0.7825422452281245</v>
+        <v>0.02718472412108053</v>
       </c>
       <c r="T5">
-        <v>1.615349717881234</v>
+        <v>1.907174422807667</v>
       </c>
       <c r="U5">
-        <v>1.615349717881234</v>
+        <v>1.907174422807667</v>
       </c>
       <c r="V5">
-        <v>62.59604325003473</v>
+        <v>62.30433719532572</v>
       </c>
       <c r="W5">
-        <v>37.40395674996527</v>
+        <v>37.69566280467428</v>
       </c>
       <c r="X5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Y5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Z5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AA5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AB5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC5">
-        <v>62.59604325003473</v>
+        <v>62.30433719532572</v>
       </c>
       <c r="AD5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE5">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -1464,46 +1479,46 @@
         <v>0</v>
       </c>
       <c r="AK5">
-        <v>0.4518009759347119</v>
+        <v>0.01569510778915155</v>
       </c>
       <c r="AL5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AM5">
         <v>-6</v>
       </c>
       <c r="AN5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AO5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AP5">
-        <v>0.5351</v>
+        <v>0.539</v>
       </c>
       <c r="AQ5">
-        <v>-7.02000000000001</v>
+        <v>-7.800000000000011</v>
       </c>
       <c r="AR5">
-        <v>7.615349717881235</v>
+        <v>7.907174422807667</v>
       </c>
       <c r="AS5">
-        <v>8.635349717881244</v>
+        <v>9.707174422807679</v>
       </c>
       <c r="AT5">
-        <v>8.125349717881239</v>
+        <v>8.807174422807673</v>
       </c>
       <c r="AU5">
-        <v>2.03133742947031</v>
+        <v>2.201793605701918</v>
       </c>
       <c r="AV5">
-        <v>4.345503062353619</v>
+        <v>5.898436507750732</v>
       </c>
       <c r="AW5">
-        <v>4.278349256582922</v>
+        <v>5.479128204442785</v>
       </c>
       <c r="AX5">
-        <v>5.029528247327535</v>
+        <v>6.083808668102767</v>
       </c>
       <c r="AY5">
         <v>0.8436468628413508</v>
@@ -1512,22 +1527,22 @@
         <v>3</v>
       </c>
       <c r="BA5">
-        <v>1.930645252303767</v>
+        <v>1.541161542643699</v>
       </c>
       <c r="BB5">
-        <v>1.354753062157686</v>
+        <v>-4.006524474852094</v>
       </c>
       <c r="BC5">
-        <v>5.754964092348529</v>
+        <v>11.41694912221213</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>42.06393827345702</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>23.63541255450272</v>
       </c>
       <c r="BF5">
-        <v>0.9442145399410329</v>
+        <v>0.6873186760847522</v>
       </c>
     </row>
     <row r="6" spans="1:58">
@@ -1535,43 +1550,43 @@
         <v>62</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6">
-        <v>49.125</v>
+        <v>48.525</v>
       </c>
       <c r="D6">
-        <v>47.175</v>
+        <v>46.225</v>
       </c>
       <c r="E6">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I6">
-        <v>51.01246105919003</v>
+        <v>51.21372031662269</v>
       </c>
       <c r="J6">
-        <v>48.98753894080997</v>
+        <v>48.78627968337731</v>
       </c>
       <c r="K6">
-        <v>2.024922118380061</v>
+        <v>2.427440633245382</v>
       </c>
       <c r="L6">
-        <v>-0.3204838353402772</v>
+        <v>-1.153094892366958</v>
       </c>
       <c r="M6">
-        <v>1.704438283039784</v>
+        <v>1.274345740878424</v>
       </c>
       <c r="N6">
-        <v>1.704438283039784</v>
+        <v>1.274345740878424</v>
       </c>
       <c r="O6">
         <v>0.25</v>
@@ -1580,49 +1595,49 @@
         <v>0.75</v>
       </c>
       <c r="Q6">
-        <v>50.89227962093743</v>
+        <v>50.78130973198508</v>
       </c>
       <c r="R6">
-        <v>49.10772037906257</v>
+        <v>49.21869026801492</v>
       </c>
       <c r="S6">
-        <v>-0.2403628765052079</v>
+        <v>-0.8648211692752186</v>
       </c>
       <c r="T6">
-        <v>1.784559241874853</v>
+        <v>1.562619463970164</v>
       </c>
       <c r="U6">
-        <v>1.784559241874853</v>
+        <v>1.562619463970164</v>
       </c>
       <c r="V6">
-        <v>61.83849093383414</v>
+        <v>62.20127145762546</v>
       </c>
       <c r="W6">
-        <v>38.16150906616586</v>
+        <v>37.79872854237454</v>
       </c>
       <c r="X6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Y6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Z6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AA6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AB6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC6">
-        <v>61.83849093383414</v>
+        <v>62.20127145762546</v>
       </c>
       <c r="AD6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE6">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -1640,46 +1655,46 @@
         <v>0</v>
       </c>
       <c r="AK6">
-        <v>0.1387735714534746</v>
+        <v>0.4993047348819343</v>
       </c>
       <c r="AL6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AM6">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="AN6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AO6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AP6">
-        <v>0.5097999999999999</v>
+        <v>0.5351</v>
       </c>
       <c r="AQ6">
-        <v>-1.95999999999998</v>
+        <v>-7.02000000000001</v>
       </c>
       <c r="AR6">
-        <v>2.215440758125147</v>
+        <v>7.562619463970163</v>
       </c>
       <c r="AS6">
-        <v>3.744559241874833</v>
+        <v>8.582619463970174</v>
       </c>
       <c r="AT6">
-        <v>2.97999999999999</v>
+        <v>8.072619463970168</v>
       </c>
       <c r="AU6">
-        <v>0.7449999999999974</v>
+        <v>2.018154865992542</v>
       </c>
       <c r="AV6">
-        <v>6.166256775636249</v>
+        <v>4.345503062353619</v>
       </c>
       <c r="AW6">
-        <v>5.301134249610259</v>
+        <v>4.276786783839438</v>
       </c>
       <c r="AX6">
-        <v>5.924011002838607</v>
+        <v>5.02819920287429</v>
       </c>
       <c r="AY6">
         <v>0.8436468628413508</v>
@@ -1688,13 +1703,13 @@
         <v>3</v>
       </c>
       <c r="BA6">
-        <v>1.878161728442779</v>
+        <v>1.930645252303767</v>
       </c>
       <c r="BB6">
-        <v>1.021885173756878</v>
+        <v>1.354753062157686</v>
       </c>
       <c r="BC6">
-        <v>7.445671083211828</v>
+        <v>5.754964092348529</v>
       </c>
       <c r="BD6">
         <v>0</v>
@@ -1703,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="BF6">
-        <v>0.9207631564477893</v>
+        <v>0.9442145399410329</v>
       </c>
     </row>
     <row r="7" spans="1:58">
@@ -1711,43 +1726,43 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C7">
-        <v>46.25</v>
+        <v>49.075</v>
       </c>
       <c r="D7">
-        <v>45.775</v>
+        <v>47.525</v>
       </c>
       <c r="E7">
-        <v>0.475</v>
+        <v>1.55</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I7">
-        <v>50.25808204292311</v>
+        <v>50.80227743271222</v>
       </c>
       <c r="J7">
-        <v>49.74191795707688</v>
+        <v>49.19772256728779</v>
       </c>
       <c r="K7">
-        <v>0.5161640858462349</v>
+        <v>1.604554865424426</v>
       </c>
       <c r="L7">
-        <v>-2.913528240380083</v>
+        <v>-0.2692769494406259</v>
       </c>
       <c r="M7">
-        <v>-2.397364154533848</v>
+        <v>1.3352779159838</v>
       </c>
       <c r="N7">
-        <v>-2.397364154533848</v>
+        <v>1.3352779159838</v>
       </c>
       <c r="O7">
         <v>0.25</v>
@@ -1756,49 +1771,49 @@
         <v>0.75</v>
       </c>
       <c r="Q7">
-        <v>49.16550895278058</v>
+        <v>50.70129857667198</v>
       </c>
       <c r="R7">
-        <v>50.83449104721942</v>
+        <v>49.29870142332802</v>
       </c>
       <c r="S7">
-        <v>-2.185146180285062</v>
+        <v>-0.2019577120804694</v>
       </c>
       <c r="T7">
-        <v>-1.668982094438827</v>
+        <v>1.402597153343956</v>
       </c>
       <c r="U7">
-        <v>-1.668982094438827</v>
+        <v>1.402597153343956</v>
       </c>
       <c r="V7">
-        <v>38.30178365229862</v>
+        <v>59.35812758782153</v>
       </c>
       <c r="W7">
-        <v>61.69821634770138</v>
+        <v>40.64187241217847</v>
       </c>
       <c r="X7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Z7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AA7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AB7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC7">
-        <v>38.30178365229862</v>
+        <v>59.35812758782153</v>
       </c>
       <c r="AD7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE7">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF7">
         <v>0</v>
@@ -1816,70 +1831,70 @@
         <v>0</v>
       </c>
       <c r="AK7">
-        <v>1.261594735406263</v>
+        <v>0.11660033943458</v>
       </c>
       <c r="AL7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AM7">
-        <v>-8</v>
+        <v>4</v>
       </c>
       <c r="AN7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AO7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AP7">
-        <v>0.5322</v>
+        <v>0.5097999999999999</v>
       </c>
       <c r="AQ7">
-        <v>-6.439999999999998</v>
+        <v>-1.95999999999998</v>
       </c>
       <c r="AR7">
-        <v>6.331017905561173</v>
+        <v>2.597402846656044</v>
       </c>
       <c r="AS7">
-        <v>4.771017905561171</v>
+        <v>3.362597153343936</v>
       </c>
       <c r="AT7">
-        <v>5.551017905561172</v>
+        <v>2.97999999999999</v>
       </c>
       <c r="AU7">
-        <v>1.387754476390293</v>
+        <v>0.7449999999999974</v>
       </c>
       <c r="AV7">
-        <v>5.314982794026658</v>
+        <v>6.166256775636249</v>
       </c>
       <c r="AW7">
-        <v>4.946399794780316</v>
+        <v>5.30106833087324</v>
       </c>
       <c r="AX7">
-        <v>5.608810298019065</v>
+        <v>5.923952015162611</v>
       </c>
       <c r="AY7">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>1.878161728442779</v>
       </c>
       <c r="BB7">
-        <v>-0.3706239798868902</v>
+        <v>1.021885173756878</v>
       </c>
       <c r="BC7">
-        <v>5.000892084631056</v>
+        <v>7.445671083211828</v>
       </c>
       <c r="BD7">
-        <v>17.64705882352941</v>
+        <v>0</v>
       </c>
       <c r="BE7">
-        <v>8.823529411764707</v>
+        <v>0</v>
       </c>
       <c r="BF7">
-        <v>0.9238036867710117</v>
+        <v>0.9207631564477893</v>
       </c>
     </row>
     <row r="8" spans="1:58">
@@ -1887,43 +1902,43 @@
         <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C8">
-        <v>46.225</v>
+        <v>46.075</v>
       </c>
       <c r="D8">
-        <v>46.125</v>
+        <v>45.625</v>
       </c>
       <c r="E8">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="F8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I8">
-        <v>50.05414185165133</v>
+        <v>50.2453653217012</v>
       </c>
       <c r="J8">
-        <v>49.94585814834868</v>
+        <v>49.7546346782988</v>
       </c>
       <c r="K8">
-        <v>0.1082837033026536</v>
+        <v>0.4907306434024008</v>
       </c>
       <c r="L8">
-        <v>-2.800784857330001</v>
+        <v>-3.142025843164147</v>
       </c>
       <c r="M8">
-        <v>-2.692501154027347</v>
+        <v>-2.651295199761746</v>
       </c>
       <c r="N8">
-        <v>-2.692501154027347</v>
+        <v>-2.651295199761746</v>
       </c>
       <c r="O8">
         <v>0.25</v>
@@ -1932,49 +1947,49 @@
         <v>0.75</v>
       </c>
       <c r="Q8">
-        <v>49.00384753015258</v>
+        <v>49.06710563051465</v>
       </c>
       <c r="R8">
-        <v>50.99615246984742</v>
+        <v>50.93289436948535</v>
       </c>
       <c r="S8">
-        <v>-2.100588642997501</v>
+        <v>-2.35651938237311</v>
       </c>
       <c r="T8">
-        <v>-1.992304939694847</v>
+        <v>-1.865788738970709</v>
       </c>
       <c r="U8">
-        <v>-1.992304939694847</v>
+        <v>-1.865788738970709</v>
       </c>
       <c r="V8">
-        <v>36.54288608991354</v>
+        <v>36.99320565632153</v>
       </c>
       <c r="W8">
-        <v>63.45711391008646</v>
+        <v>63.00679434367846</v>
       </c>
       <c r="X8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Y8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Z8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AB8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC8">
-        <v>36.54288608991354</v>
+        <v>36.99320565632153</v>
       </c>
       <c r="AD8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE8">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF8">
         <v>0</v>
@@ -1992,70 +2007,70 @@
         <v>0</v>
       </c>
       <c r="AK8">
-        <v>1.212775418491278</v>
+        <v>1.360537099763686</v>
       </c>
       <c r="AL8" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AM8">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="AN8" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AO8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AP8">
-        <v>0.5174</v>
+        <v>0.5322</v>
       </c>
       <c r="AQ8">
-        <v>-3.47999999999999</v>
+        <v>-6.439999999999998</v>
       </c>
       <c r="AR8">
-        <v>4.007695060305153</v>
+        <v>6.134211261029291</v>
       </c>
       <c r="AS8">
-        <v>1.487695060305143</v>
+        <v>4.574211261029289</v>
       </c>
       <c r="AT8">
-        <v>2.747695060305148</v>
+        <v>5.35421126102929</v>
       </c>
       <c r="AU8">
-        <v>0.6869237650762869</v>
+        <v>1.338552815257323</v>
       </c>
       <c r="AV8">
-        <v>5.775280601260435</v>
+        <v>5.314982794026658</v>
       </c>
       <c r="AW8">
-        <v>5.153011767448446</v>
+        <v>4.958270629623712</v>
       </c>
       <c r="AX8">
-        <v>5.791840148417783</v>
+        <v>5.619281952878951</v>
       </c>
       <c r="AY8">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA8">
-        <v>2.193175026846863</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>-2.886112316484782</v>
+        <v>-0.3706239798868902</v>
       </c>
       <c r="BC8">
-        <v>6.837360120673064</v>
+        <v>5.000892084631056</v>
       </c>
       <c r="BD8">
-        <v>30.49114883433812</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>8.823529411764707</v>
       </c>
       <c r="BF8">
-        <v>0.9513390040572299</v>
+        <v>0.9238036867710117</v>
       </c>
     </row>
     <row r="9" spans="1:58">
@@ -2063,43 +2078,43 @@
         <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C9">
-        <v>45.6</v>
+        <v>45.85</v>
       </c>
       <c r="D9">
-        <v>46.93333333</v>
+        <v>46.15000000000001</v>
       </c>
       <c r="E9">
-        <v>-1.333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="F9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s">
         <v>75</v>
       </c>
       <c r="I9">
-        <v>49.27953890667433</v>
+        <v>49.83695652173913</v>
       </c>
       <c r="J9">
-        <v>50.72046109332566</v>
+        <v>50.16304347826088</v>
       </c>
       <c r="K9">
-        <v>-1.440922186651328</v>
+        <v>-0.326086956521749</v>
       </c>
       <c r="L9">
-        <v>-2.404592995100077</v>
+        <v>-2.985584654428823</v>
       </c>
       <c r="M9">
-        <v>-3.845515181751405</v>
+        <v>-3.311671610950572</v>
       </c>
       <c r="N9">
-        <v>-3.845515181751405</v>
+        <v>-3.311671610950572</v>
       </c>
       <c r="O9">
         <v>0.25</v>
@@ -2108,49 +2123,49 @@
         <v>0.75</v>
       </c>
       <c r="Q9">
-        <v>48.3778165335118</v>
+        <v>48.71736227632832</v>
       </c>
       <c r="R9">
-        <v>51.6221834664882</v>
+        <v>51.28263772367168</v>
       </c>
       <c r="S9">
-        <v>-1.803444746325058</v>
+        <v>-2.239188490821618</v>
       </c>
       <c r="T9">
-        <v>-3.244366932976385</v>
+        <v>-2.565275447343367</v>
       </c>
       <c r="U9">
-        <v>-3.244366932976385</v>
+        <v>-2.565275447343367</v>
       </c>
       <c r="V9">
-        <v>29.28823179916958</v>
+        <v>32.89408151901587</v>
       </c>
       <c r="W9">
-        <v>70.71176820083042</v>
+        <v>67.10591848098413</v>
       </c>
       <c r="X9" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="Y9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Z9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AA9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AB9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AC9">
-        <v>29.28823179916958</v>
+        <v>32.89408151901587</v>
       </c>
       <c r="AD9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AE9">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF9">
         <v>0</v>
@@ -2168,46 +2183,46 @@
         <v>0</v>
       </c>
       <c r="AK9">
-        <v>1.041219309759388</v>
+        <v>1.292796077942173</v>
       </c>
       <c r="AL9" t="s">
         <v>87</v>
       </c>
       <c r="AM9">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="AN9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AO9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AP9">
-        <v>0.6258</v>
+        <v>0.5174</v>
       </c>
       <c r="AQ9">
-        <v>-25.16000000000001</v>
+        <v>-3.47999999999999</v>
       </c>
       <c r="AR9">
-        <v>6.755633067023615</v>
+        <v>3.434724552656633</v>
       </c>
       <c r="AS9">
-        <v>21.91563306702363</v>
+        <v>0.9147245526566232</v>
       </c>
       <c r="AT9">
-        <v>14.33563306702362</v>
+        <v>2.174724552656628</v>
       </c>
       <c r="AU9">
-        <v>3.583908266755905</v>
+        <v>0.5436811381641571</v>
       </c>
       <c r="AV9">
-        <v>4.390437171606355</v>
+        <v>5.775280601260435</v>
       </c>
       <c r="AW9">
-        <v>5.33366990827579</v>
+        <v>5.154073308979592</v>
       </c>
       <c r="AX9">
-        <v>5.95314343181891</v>
+        <v>5.792784624314786</v>
       </c>
       <c r="AY9">
         <v>0.8436468628413508</v>
@@ -2216,22 +2231,362 @@
         <v>3</v>
       </c>
       <c r="BA9">
+        <v>2.193175026846863</v>
+      </c>
+      <c r="BB9">
+        <v>-2.886112316484782</v>
+      </c>
+      <c r="BC9">
+        <v>6.837360120673064</v>
+      </c>
+      <c r="BD9">
+        <v>30.49114883433812</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0.9513390040572299</v>
+      </c>
+    </row>
+    <row r="10" spans="1:58">
+      <c r="A10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10">
+        <v>45.7</v>
+      </c>
+      <c r="D10">
+        <v>47.3</v>
+      </c>
+      <c r="E10">
+        <v>-1.6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10">
+        <v>49.13978494623656</v>
+      </c>
+      <c r="J10">
+        <v>50.86021505376344</v>
+      </c>
+      <c r="K10">
+        <v>-1.72043010752688</v>
+      </c>
+      <c r="L10">
+        <v>-2.133208235829057</v>
+      </c>
+      <c r="M10">
+        <v>-3.853638343355938</v>
+      </c>
+      <c r="N10">
+        <v>-3.853638343355938</v>
+      </c>
+      <c r="O10">
+        <v>0.25</v>
+      </c>
+      <c r="P10">
+        <v>0.75</v>
+      </c>
+      <c r="Q10">
+        <v>48.33983185780066</v>
+      </c>
+      <c r="R10">
+        <v>51.66016814219934</v>
+      </c>
+      <c r="S10">
+        <v>-1.599906176871793</v>
+      </c>
+      <c r="T10">
+        <v>-3.320336284398673</v>
+      </c>
+      <c r="U10">
+        <v>-3.320336284398673</v>
+      </c>
+      <c r="V10">
+        <v>28.73738453916303</v>
+      </c>
+      <c r="W10">
+        <v>71.26261546083697</v>
+      </c>
+      <c r="X10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC10">
+        <v>28.73738453916303</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE10">
+        <v>8.785698713756254</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0.9237062618950747</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM10">
+        <v>-10</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AP10">
+        <v>0.6258</v>
+      </c>
+      <c r="AQ10">
+        <v>-25.16000000000001</v>
+      </c>
+      <c r="AR10">
+        <v>6.679663715601327</v>
+      </c>
+      <c r="AS10">
+        <v>21.83966371560134</v>
+      </c>
+      <c r="AT10">
+        <v>14.25966371560133</v>
+      </c>
+      <c r="AU10">
+        <v>3.564915928900333</v>
+      </c>
+      <c r="AV10">
+        <v>4.390437171606355</v>
+      </c>
+      <c r="AW10">
+        <v>5.294227952408996</v>
+      </c>
+      <c r="AX10">
+        <v>5.917831667209765</v>
+      </c>
+      <c r="AY10">
+        <v>0.8436468628413508</v>
+      </c>
+      <c r="AZ10">
+        <v>3</v>
+      </c>
+      <c r="BA10">
         <v>1.906296723190152</v>
       </c>
-      <c r="BB9">
+      <c r="BB10">
         <v>-1.372324784465838</v>
       </c>
-      <c r="BC9">
+      <c r="BC10">
         <v>5.414780435479317</v>
       </c>
-      <c r="BD9">
-        <v>0</v>
-      </c>
-      <c r="BE9">
-        <v>0</v>
-      </c>
-      <c r="BF9">
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
         <v>0.9325238981752073</v>
+      </c>
+    </row>
+    <row r="11" spans="1:58">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11">
+        <v>44.975</v>
+      </c>
+      <c r="D11">
+        <v>46.1</v>
+      </c>
+      <c r="E11">
+        <v>-1.125</v>
+      </c>
+      <c r="F11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11">
+        <v>49.38237716167993</v>
+      </c>
+      <c r="J11">
+        <v>50.61762283832007</v>
+      </c>
+      <c r="K11">
+        <v>-1.235245676640133</v>
+      </c>
+      <c r="L11">
+        <v>-3.296493962154622</v>
+      </c>
+      <c r="M11">
+        <v>-4.531739638794756</v>
+      </c>
+      <c r="N11">
+        <v>-4.531739638794756</v>
+      </c>
+      <c r="O11">
+        <v>0.25</v>
+      </c>
+      <c r="P11">
+        <v>0.75</v>
+      </c>
+      <c r="Q11">
+        <v>48.14619192587195</v>
+      </c>
+      <c r="R11">
+        <v>51.85380807412805</v>
+      </c>
+      <c r="S11">
+        <v>-2.472370471615967</v>
+      </c>
+      <c r="T11">
+        <v>-3.7076161482561</v>
+      </c>
+      <c r="U11">
+        <v>-3.7076161482561</v>
+      </c>
+      <c r="V11">
+        <v>25.3176033774056</v>
+      </c>
+      <c r="W11">
+        <v>74.6823966225944</v>
+      </c>
+      <c r="X11" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC11">
+        <v>25.3176033774056</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE11">
+        <v>8.785698713756254</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>1.42742375732396</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM11">
+        <v>-8</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>100</v>
+      </c>
+      <c r="AR11">
+        <v>4.292383851743899</v>
+      </c>
+      <c r="AT11">
+        <v>4.292383851743899</v>
+      </c>
+      <c r="AU11">
+        <v>1.073095962935975</v>
+      </c>
+      <c r="AV11">
+        <v>5.314982794026658</v>
+      </c>
+      <c r="AW11">
+        <v>4.912932521054522</v>
+      </c>
+      <c r="AX11">
+        <v>5.579317878181624</v>
+      </c>
+      <c r="AY11">
+        <v>0.8436468628413508</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>-0.3706239798868902</v>
+      </c>
+      <c r="BC11">
+        <v>5.000892084631056</v>
+      </c>
+      <c r="BD11">
+        <v>17.64705882352941</v>
+      </c>
+      <c r="BE11">
+        <v>8.823529411764707</v>
+      </c>
+      <c r="BF11">
+        <v>0.9238036867710117</v>
       </c>
     </row>
   </sheetData>
